--- a/output/15_매입판매가_제시안.xlsx
+++ b/output/15_매입판매가_제시안.xlsx
@@ -508,7 +508,7 @@
   <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -647,12 +647,12 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>고객 제시가(버퍼) 열(2026-09-11 추가)</t>
+          <t>고객 제시가(버퍼) 열(2026-09-11 추가, 2026-09-14 조정)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>돈현님 요청: 고객사와의 협상 여유를 위해 처음부터 목표가보다 조금 높게 부른다. '제시 판매가(목표가)'는 기존과 동일하게 KT 표준 마진을 유지하는 협상 마지노선이고, 여기에 8%p를 얹은 '고객 제시가(최초견적)'를 새로 추가했다 - 이 금액을 먼저 제시하고, 고객사가 인하를 요청하면 목표가 선까지 내려가며 마무리하는 구조다. 버퍼 크기는 ANCHOR_BUFFER 상수 하나만 바꾸면 전체 시트에 일괄 반영된다(권장 범위 5~10%p 중 중간값 채택 - 너무 크면 시장 감각과 멀어지고 너무 작으면 협상 카드로서 의미가 없다).</t>
+          <t>돈현님 요청: 고객사와의 협상 여유를 위해 처음부터 목표가보다 조금 높게 부른다. '제시 판매가(목표가)'는 기존과 동일하게 KT 표준 마진을 유지하는 협상 마지노선이고, 여기에 3%p를 얹은 '고객 제시가(최초견적)'를 추가했다 - 고객사가 인하를 요청하면 목표가 선까지 내려가며 마무리하는 구조다. 처음엔 8%p로 시작했으나, 고객사가 협상 없이 최초 제시가를 그대로 수락할 가능성도 있고, 그 경우 표준 마진(2~5%) 위에 버퍼까지 그대로 이익으로 굳어져 폭리로 비칠 수 있다는 지적에 따라 3%p로 낮췄다 - 그대로 수락돼도 '표준 마진 범위 내 약간의 여유'로 보일 정도만 남긴 것이다. 버퍼 크기는 ANCHOR_BUFFER 상수 하나만 바꾸면 전체 시트에 일괄 반영된다.</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1366359.084</v>
@@ -775,7 +775,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
     </row>
     <row r="3">
@@ -797,7 +797,7 @@
         <v>1162748.081632651</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>62788396.40816326</v>
+        <v>59881526.20408163</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>57410772.8</v>
@@ -812,7 +812,7 @@
         <v>1171648.424489796</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>63269014.92244898</v>
+        <v>60339893.86122449</v>
       </c>
     </row>
     <row r="4">
@@ -834,7 +834,7 @@
         <v>264484.4927346949</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>14282162.60767347</v>
+        <v>13620951.37583674</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>13488196.144</v>
@@ -849,7 +849,7 @@
         <v>275269.3090612255</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14864542.68930612</v>
+        <v>14176369.41665306</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>113772.6122448985</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6143721.06122449</v>
+        <v>5859289.530612245</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>11149716</v>
@@ -886,7 +886,7 @@
         <v>227545.2244897969</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>12287442.12244898</v>
+        <v>11718579.06122449</v>
       </c>
     </row>
     <row r="6">
@@ -908,7 +908,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -923,7 +923,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -945,7 +945,7 @@
         <v>55557.48489795905</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3000104.184489796</v>
+        <v>2861210.472244898</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2634757.52</v>
@@ -960,7 +960,7 @@
         <v>53770.56163265323</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2903610.328163266</v>
+        <v>2769183.924081633</v>
       </c>
     </row>
     <row r="8">
@@ -982,7 +982,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>141290.422</v>
@@ -997,7 +997,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
     </row>
     <row r="9">
@@ -1019,7 +1019,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>786592.324</v>
@@ -1034,7 +1034,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
     </row>
     <row r="10">
@@ -1056,7 +1056,7 @@
         <v>51888.0063673472</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2801952.343836735</v>
+        <v>2672232.327918368</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>5085024.624000001</v>
@@ -1071,7 +1071,7 @@
         <v>103776.0127346944</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5603904.687673471</v>
+        <v>5344464.655836736</v>
       </c>
     </row>
     <row r="11">
@@ -1093,7 +1093,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -1108,7 +1108,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -1130,7 +1130,7 @@
         <v>49962.69473684218</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1079194.20631579</v>
+        <v>1029231.511578948</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>2373148.8</v>
@@ -1145,7 +1145,7 @@
         <v>124902.5684210528</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2697895.477894737</v>
+        <v>2572992.909473685</v>
       </c>
     </row>
     <row r="13">
@@ -1167,7 +1167,7 @@
         <v>14797.50321649486</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>532710.1157938145</v>
+        <v>508047.6104329897</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>584987.7320000001</v>
@@ -1182,7 +1182,7 @@
         <v>18092.4040824743</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>651326.5469690723</v>
+        <v>621172.5401649487</v>
       </c>
     </row>
     <row r="14">
@@ -1202,7 +1202,7 @@
         <v>1903159.336198226</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>100885457.7873341</v>
+        <v>96214834.74162416</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>103905950.198</v>
@@ -1215,7 +1215,7 @@
         <v>2203154.435074955</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>114597833.003721</v>
+        <v>109292377.7720672</v>
       </c>
     </row>
   </sheetData>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 최초견적(버퍼 8%p)</t>
+          <t>Non_SD 고객 최초견적(버퍼 3%p)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 최초견적(버퍼 8%p)</t>
+          <t>SD 고객 최초견적(버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
         <v>742005.3058664128</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>39258011.50401574</v>
+        <v>37440510.9714224</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>47710885.87800001</v>
@@ -1319,7 +1319,7 @@
         <v>1000753.435218245</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>52608570.45827571</v>
+        <v>50172988.4926148</v>
       </c>
     </row>
     <row r="3">
@@ -1338,7 +1338,7 @@
         <v>1158391.871093653</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>61411890.90502114</v>
+        <v>58568747.80756646</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>65924718.84</v>
@@ -1350,7 +1350,7 @@
         <v>1390469.511389159</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>72700403.41950029</v>
+        <v>69334644.00193083</v>
       </c>
     </row>
     <row r="4">
@@ -1369,7 +1369,7 @@
         <v>1572774.384073049</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>83375665.49383889</v>
+        <v>79515680.98023523</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>83890988.12600002</v>
@@ -1381,7 +1381,7 @@
         <v>1776680.621965274</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>92521082.24780251</v>
+        <v>88237698.81040421</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1400,7 @@
         <v>1903248.661585987</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>100890281.3582729</v>
+        <v>96219434.99909355</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>103910327.142</v>
@@ -1412,7 +1412,7 @@
         <v>2203243.760462701</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>114602656.5746597</v>
+        <v>109296978.0295366</v>
       </c>
     </row>
     <row r="6">
@@ -1431,7 +1431,7 @@
         <v>742005.3058664128</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>39258011.50401574</v>
+        <v>37440510.9714224</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>47709791.642</v>
@@ -1443,7 +1443,7 @@
         <v>1000731.103871301</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>52607364.56554101</v>
+        <v>50171838.42824745</v>
       </c>
     </row>
     <row r="7">
@@ -1462,7 +1462,7 @@
         <v>1158347.208399773</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>61409479.11955174</v>
+        <v>58566447.67883177</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>65922530.36799999</v>
@@ -1474,7 +1474,7 @@
         <v>1390424.848695286</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>72697991.63403089</v>
+        <v>69332343.87319614</v>
       </c>
     </row>
     <row r="8">
@@ -1493,7 +1493,7 @@
         <v>1572707.390032217</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>83372047.8156348</v>
+        <v>79512230.78713319</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>83887705.41800001</v>
@@ -1505,7 +1505,7 @@
         <v>1776613.627924457</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>92517464.56959842</v>
+        <v>88234248.61730218</v>
       </c>
     </row>
     <row r="9">
@@ -1524,7 +1524,7 @@
         <v>1903159.336198226</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>100885457.7873341</v>
+        <v>96214834.74162416</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>103905950.198</v>
@@ -1536,7 +1536,7 @@
         <v>2203154.435074955</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>114597833.003721</v>
+        <v>109292377.7720672</v>
       </c>
     </row>
   </sheetData>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>고객 제시단가(최초견적, 버퍼 8%p)</t>
+          <t>고객 제시단가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -1633,7 +1633,7 @@
         <v>44883.47368421053</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>48474.15157894738</v>
+        <v>46229.97789473685</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>27324</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>29509.92</v>
+        <v>28143.72</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1711,7 +1711,7 @@
         <v>48791.36842105263</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>52694.67789473685</v>
+        <v>50255.10947368421</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>4454670.156122449</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4811043.768612245</v>
+        <v>4588310.260806123</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -1789,7 +1789,7 @@
         <v>7272857.936734693</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>7854686.571673469</v>
+        <v>7491043.674836734</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>3446613.434693878</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3722342.509469389</v>
+        <v>3550011.837734695</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>4721413.580612245</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>5099126.667061225</v>
+        <v>4863055.988030612</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>2377787.755102041</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>2568010.775510204</v>
+        <v>2449121.387755102</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>1773732.653061225</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1915631.265306123</v>
+        <v>1826944.632653061</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>875510.2040816327</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>945551.0204081633</v>
+        <v>901775.5102040817</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
         <v>317410.2040816327</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>342803.0204081633</v>
+        <v>326932.5102040817</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>152928.5714285714</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>165162.8571428571</v>
+        <v>157516.4285714286</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>152928.5714285714</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>165162.8571428571</v>
+        <v>157516.4285714286</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>173945.3489795919</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>187860.9768979592</v>
+        <v>179163.7094489796</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>86589.65000000001</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>93516.82200000001</v>
+        <v>89187.33950000002</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -2218,7 +2218,7 @@
         <v>86589.65000000001</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>93516.82200000001</v>
+        <v>89187.33950000002</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>161054.5918367347</v>
       </c>
       <c r="F18" s="3" t="n">
-        <v>173938.9591836735</v>
+        <v>165886.2295918367</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
         <v>161054.5918367347</v>
       </c>
       <c r="F19" s="3" t="n">
-        <v>173938.9591836735</v>
+        <v>165886.2295918367</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>1653586.363265306</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1785873.272326531</v>
+        <v>1703193.954163265</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>67405.10204081633</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>72797.51020408164</v>
+        <v>69427.25510204083</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>1653586.363265306</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1785873.272326531</v>
+        <v>1703193.954163265</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
@@ -2452,7 +2452,7 @@
         <v>67405.10204081633</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>72797.51020408164</v>
+        <v>69427.25510204083</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>1653586.363265306</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>1785873.272326531</v>
+        <v>1703193.954163265</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>67405.10204081633</v>
       </c>
       <c r="F25" s="3" t="n">
-        <v>72797.51020408164</v>
+        <v>69427.25510204083</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
@@ -2569,7 +2569,7 @@
         <v>1652469.795918367</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>1784667.379591837</v>
+        <v>1702043.889795918</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>67405.10204081633</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>72797.51020408164</v>
+        <v>69427.25510204083</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -2647,7 +2647,7 @@
         <v>2623143.218367347</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>2832994.675836735</v>
+        <v>2701837.514918367</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
         <v>57967.27448979591</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>62604.65644897959</v>
+        <v>59706.29272448979</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         <v>72086.95</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>77853.906</v>
+        <v>74249.5585</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>257140.0091836735</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>277711.2099183674</v>
+        <v>264854.2094591837</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2803,7 +2803,7 @@
         <v>200661.3071428571</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>216714.2117142857</v>
+        <v>206681.1463571429</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>1422157.653061225</v>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1535930.265306123</v>
+        <v>1464822.382653061</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2881,7 +2881,7 @@
         <v>454092.9428571428</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>490420.3782857143</v>
+        <v>467715.7311428571</v>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>697121.981632653</v>
       </c>
       <c r="F35" s="3" t="n">
-        <v>752891.7401632654</v>
+        <v>718035.6410816327</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         <v>7267175.510204081</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>7848549.551020408</v>
+        <v>7485190.775510204</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>55627.14285714295</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>60077.31428571439</v>
+        <v>57295.95714285724</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>7267175.510204081</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>7848549.551020408</v>
+        <v>7485190.775510204</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>55627.14285714295</v>
       </c>
       <c r="F39" s="3" t="n">
-        <v>60077.31428571439</v>
+        <v>57295.95714285724</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>256713.4591836735</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>277250.5359183674</v>
+        <v>264414.8629591837</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>477518.3724489796</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>515719.842244898</v>
+        <v>491843.923622449</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>477518.3724489796</v>
       </c>
       <c r="F42" s="3" t="n">
-        <v>515719.842244898</v>
+        <v>491843.923622449</v>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>42888.48</v>
       </c>
       <c r="F43" s="3" t="n">
-        <v>46319.5584</v>
+        <v>44175.1344</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
@@ -3271,7 +3271,7 @@
         <v>322929.78</v>
       </c>
       <c r="F44" s="3" t="n">
-        <v>348764.1624</v>
+        <v>332617.6734</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>70636.68000000001</v>
       </c>
       <c r="F45" s="3" t="n">
-        <v>76287.61440000002</v>
+        <v>72755.7804</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -3349,7 +3349,7 @@
         <v>20178.06</v>
       </c>
       <c r="F46" s="3" t="n">
-        <v>21792.3048</v>
+        <v>20783.4018</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -3388,7 +3388,7 @@
         <v>3298197.766326531</v>
       </c>
       <c r="F47" s="3" t="n">
-        <v>3562053.587632654</v>
+        <v>3397143.699316327</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>3163677.824489796</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3416772.05044898</v>
+        <v>3258588.15922449</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
         <v>3245209.810204082</v>
       </c>
       <c r="F49" s="3" t="n">
-        <v>3504826.595020408</v>
+        <v>3342566.104510204</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>1225173.471428572</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>1323187.349142857</v>
+        <v>1261928.675571429</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>1225173.471428572</v>
       </c>
       <c r="F51" s="3" t="n">
-        <v>1323187.349142857</v>
+        <v>1261928.675571429</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3583,7 +3583,7 @@
         <v>1225173.471428572</v>
       </c>
       <c r="F52" s="3" t="n">
-        <v>1323187.349142857</v>
+        <v>1261928.675571429</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3622,7 +3622,7 @@
         <v>1225173.471428572</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1323187.349142857</v>
+        <v>1261928.675571429</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>819315.4989795919</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>884860.7388979592</v>
+        <v>843894.9639489796</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3700,7 +3700,7 @@
         <v>176199.9704081633</v>
       </c>
       <c r="F55" s="3" t="n">
-        <v>190295.9680408163</v>
+        <v>181485.9695204082</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3739,7 +3739,7 @@
         <v>247573.1020408163</v>
       </c>
       <c r="F56" s="3" t="n">
-        <v>267378.9502040817</v>
+        <v>255000.2951020408</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
         <v>318946.2336734694</v>
       </c>
       <c r="F57" s="3" t="n">
-        <v>344461.9323673469</v>
+        <v>328514.6206836735</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>390319.3653061225</v>
       </c>
       <c r="F58" s="3" t="n">
-        <v>421544.9145306123</v>
+        <v>402028.9462653061</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3856,7 +3856,7 @@
         <v>461701.2020408164</v>
       </c>
       <c r="F59" s="3" t="n">
-        <v>498637.2982040817</v>
+        <v>475552.2381020409</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>533074.3336734694</v>
       </c>
       <c r="F60" s="3" t="n">
-        <v>575720.2803673469</v>
+        <v>549066.5636836735</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>605187.3989795918</v>
       </c>
       <c r="F61" s="3" t="n">
-        <v>653602.3908979591</v>
+        <v>623343.0209489795</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3973,7 +3973,7 @@
         <v>676560.5306122449</v>
       </c>
       <c r="F62" s="3" t="n">
-        <v>730685.3730612245</v>
+        <v>696857.3465306122</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -4012,7 +4012,7 @@
         <v>747933.662244898</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>807768.3552244899</v>
+        <v>770371.672112245</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>202219.5204081633</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>218397.0820408164</v>
+        <v>208286.1060204082</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>280286.8755102041</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>302709.8255510204</v>
+        <v>288695.4817755102</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>358354.2306122449</v>
       </c>
       <c r="F66" s="3" t="n">
-        <v>387022.5690612245</v>
+        <v>369104.8575306123</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -4168,7 +4168,7 @@
         <v>436421.5857142857</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>471335.3125714286</v>
+        <v>449514.2332857143</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>515228.8744897959</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>556447.1844489797</v>
+        <v>530685.7407244898</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>593296.2295918367</v>
       </c>
       <c r="F69" s="3" t="n">
-        <v>640759.9279591837</v>
+        <v>611095.1164795918</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>45411.86</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>49044.80880000001</v>
+        <v>46774.21580000001</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>80730.20000000001</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>87188.61600000002</v>
+        <v>83152.10600000001</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>60543.16</v>
       </c>
       <c r="F72" s="3" t="n">
-        <v>65386.61280000001</v>
+        <v>62359.45480000001</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4402,7 +4402,7 @@
         <v>99229.00000000001</v>
       </c>
       <c r="F73" s="3" t="n">
-        <v>107167.32</v>
+        <v>102205.87</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>60543.16</v>
       </c>
       <c r="F74" s="3" t="n">
-        <v>65386.61280000001</v>
+        <v>62359.45480000001</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4480,7 +4480,7 @@
         <v>99229.00000000001</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>107167.32</v>
+        <v>102205.87</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4519,7 +4519,7 @@
         <v>54433.00306122449</v>
       </c>
       <c r="F76" s="3" t="n">
-        <v>58787.64330612245</v>
+        <v>56065.99315306122</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>27725.75</v>
       </c>
       <c r="F77" s="3" t="n">
-        <v>29943.81</v>
+        <v>28557.5225</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4597,7 +4597,7 @@
         <v>27725.75</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>29943.81</v>
+        <v>28557.5225</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
         <v>7669.194897959183</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>8282.730489795918</v>
+        <v>7899.270744897959</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>8720545.154639177</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>9418188.767010313</v>
+        <v>8982161.509278353</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>8720545.154639177</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>9418188.767010313</v>
+        <v>8982161.509278353</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>11039669.69072165</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>11922843.26597938</v>
+        <v>11370859.7814433</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>11039669.69072165</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>11922843.26597938</v>
+        <v>11370859.7814433</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -4831,7 +4831,7 @@
         <v>14309141.64948454</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>15453872.9814433</v>
+        <v>14738415.89896907</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>14309141.64948454</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>15453872.9814433</v>
+        <v>14738415.89896907</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -4909,7 +4909,7 @@
         <v>3530798.556701031</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>3813262.441237114</v>
+        <v>3636722.513402062</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
         <v>3530798.556701031</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3813262.441237114</v>
+        <v>3636722.513402062</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>4969903.298969072</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>5367495.562886599</v>
+        <v>5119000.397938144</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5026,7 +5026,7 @@
         <v>4969903.298969072</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>5367495.562886599</v>
+        <v>5119000.397938144</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5065,7 +5065,7 @@
         <v>6609796.907216495</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>7138580.659793815</v>
+        <v>6808090.81443299</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5104,7 +5104,7 @@
         <v>6609796.907216495</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>7138580.659793815</v>
+        <v>6808090.81443299</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5143,7 +5143,7 @@
         <v>1500359.157142857</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>1620387.889714286</v>
+        <v>1545369.931857143</v>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         <v>133299.12</v>
       </c>
       <c r="F93" s="3" t="n">
-        <v>143963.0496</v>
+        <v>137298.0936</v>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>63973.52</v>
       </c>
       <c r="F94" s="3" t="n">
-        <v>69091.4016</v>
+        <v>65892.72560000001</v>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
         <v>46211.08</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>49907.9664</v>
+        <v>47597.4124</v>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>242953.9</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>262390.212</v>
+        <v>250242.517</v>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>565.74</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>610.9992000000001</v>
+        <v>582.7122000000001</v>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
@@ -5377,7 +5377,7 @@
         <v>10359.07142857143</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>11187.79714285714</v>
+        <v>10669.84357142857</v>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>50158.79795918368</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>54171.50179591838</v>
+        <v>51663.56189795919</v>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
@@ -5455,7 +5455,7 @@
         <v>20065.26020408163</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>21670.48102040817</v>
+        <v>20667.21801020408</v>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
@@ -5494,7 +5494,7 @@
         <v>20698.9</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>22354.812</v>
+        <v>21319.867</v>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
@@ -5533,7 +5533,7 @@
         <v>100073.8530612245</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>108079.7613061225</v>
+        <v>103076.0686530612</v>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
@@ -5572,7 +5572,7 @@
         <v>50158.79795918368</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>54171.50179591838</v>
+        <v>51663.56189795919</v>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
         <v>1475540.91122449</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>1593584.184122449</v>
+        <v>1519807.138561225</v>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
@@ -5689,7 +5689,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
@@ -5728,7 +5728,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
@@ -5767,7 +5767,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
@@ -5845,7 +5845,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
@@ -5884,7 +5884,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         <v>685596.4265306123</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>740444.1406530613</v>
+        <v>706164.3193265307</v>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>1190422.704081633</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>1285656.520408163</v>
+        <v>1226135.385204082</v>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>1190422.704081633</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>1285656.520408163</v>
+        <v>1226135.385204082</v>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>682558.3459183674</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>737163.0135918368</v>
+        <v>703035.0962959185</v>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>682558.3459183674</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>737163.0135918368</v>
+        <v>703035.0962959185</v>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>130453.9412371134</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>140890.2565360825</v>
+        <v>134367.5594742268</v>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>130453.9412371134</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>140890.2565360825</v>
+        <v>134367.5594742268</v>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
@@ -6196,7 +6196,7 @@
         <v>177049.0319587629</v>
       </c>
       <c r="F119" s="3" t="n">
-        <v>191212.9545154639</v>
+        <v>182360.5029175258</v>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
@@ -6235,7 +6235,7 @@
         <v>1497913.023469388</v>
       </c>
       <c r="F120" s="3" t="n">
-        <v>1617746.065346939</v>
+        <v>1542850.414173469</v>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
@@ -6274,7 +6274,7 @@
         <v>1497913.023469388</v>
       </c>
       <c r="F121" s="3" t="n">
-        <v>1617746.065346939</v>
+        <v>1542850.414173469</v>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>1055676.429591837</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>1140130.543959184</v>
+        <v>1087346.722479592</v>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
@@ -6352,7 +6352,7 @@
         <v>1055676.429591837</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>1140130.543959184</v>
+        <v>1087346.722479592</v>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>1055676.429591837</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>1140130.543959184</v>
+        <v>1087346.722479592</v>
       </c>
       <c r="G124" s="2" t="inlineStr">
         <is>
@@ -6430,7 +6430,7 @@
         <v>1055676.429591837</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>1140130.543959184</v>
+        <v>1087346.722479592</v>
       </c>
       <c r="G125" s="2" t="inlineStr">
         <is>
@@ -6469,7 +6469,7 @@
         <v>303092.7835051547</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>327340.2061855671</v>
+        <v>312185.5670103093</v>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>9247422.680412371</v>
       </c>
       <c r="F127" s="3" t="n">
-        <v>9987216.494845361</v>
+        <v>9524845.360824741</v>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
@@ -6547,7 +6547,7 @@
         <v>303092.7835051547</v>
       </c>
       <c r="F128" s="3" t="n">
-        <v>327340.2061855671</v>
+        <v>312185.5670103093</v>
       </c>
       <c r="G128" s="2" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>37005.3887755102</v>
       </c>
       <c r="F129" s="3" t="n">
-        <v>39965.81987755102</v>
+        <v>38115.55043877551</v>
       </c>
       <c r="G129" s="2" t="inlineStr">
         <is>
@@ -6625,7 +6625,7 @@
         <v>40544.23711340207</v>
       </c>
       <c r="F130" s="3" t="n">
-        <v>43787.77608247424</v>
+        <v>41760.56422680413</v>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>60059.99896907217</v>
       </c>
       <c r="F131" s="3" t="n">
-        <v>64864.79888659795</v>
+        <v>61861.79893814434</v>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
@@ -6703,7 +6703,7 @@
         <v>310097.4525773196</v>
       </c>
       <c r="F132" s="3" t="n">
-        <v>334905.2487835052</v>
+        <v>319400.3761546392</v>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>34332.9224489796</v>
       </c>
       <c r="F133" s="3" t="n">
-        <v>37079.55624489797</v>
+        <v>35362.91012244899</v>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>39787.88041237113</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>42970.91084536082</v>
+        <v>40981.51682474226</v>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>60059.99896907217</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>64864.79888659795</v>
+        <v>61861.79893814434</v>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>298840.0505154639</v>
       </c>
       <c r="F136" s="3" t="n">
-        <v>322747.2545567011</v>
+        <v>307805.2520309279</v>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>33140.32346938775</v>
       </c>
       <c r="F137" s="3" t="n">
-        <v>35791.54934693877</v>
+        <v>34134.53317346939</v>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>39040.31855670103</v>
       </c>
       <c r="F138" s="3" t="n">
-        <v>42163.54404123712</v>
+        <v>40211.52811340206</v>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
         <v>60059.99896907217</v>
       </c>
       <c r="F139" s="3" t="n">
-        <v>64864.79888659795</v>
+        <v>61861.79893814434</v>
       </c>
       <c r="G139" s="2" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>295832.2134020618</v>
       </c>
       <c r="F140" s="3" t="n">
-        <v>319498.7904742268</v>
+        <v>304707.1798041237</v>
       </c>
       <c r="G140" s="2" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>16505.24</v>
       </c>
       <c r="F141" s="3" t="n">
-        <v>17825.6592</v>
+        <v>17000.3972</v>
       </c>
       <c r="G141" s="2" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>14574.54</v>
       </c>
       <c r="F142" s="3" t="n">
-        <v>15740.5032</v>
+        <v>15011.7762</v>
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>2424.6</v>
       </c>
       <c r="F143" s="3" t="n">
-        <v>2618.568</v>
+        <v>2497.338</v>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
@@ -7171,7 +7171,7 @@
         <v>4858.18</v>
       </c>
       <c r="F144" s="3" t="n">
-        <v>5246.834400000001</v>
+        <v>5003.9254</v>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
@@ -7210,7 +7210,7 @@
         <v>8090.98</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>8738.258400000001</v>
+        <v>8333.7094</v>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>726436.637113402</v>
       </c>
       <c r="F146" s="3" t="n">
-        <v>784551.5680824742</v>
+        <v>748229.7362268041</v>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
@@ -7288,7 +7288,7 @@
         <v>726436.637113402</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>784551.5680824742</v>
+        <v>748229.7362268041</v>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
@@ -7327,7 +7327,7 @@
         <v>1815945.221428572</v>
       </c>
       <c r="F148" s="3" t="n">
-        <v>1961220.839142857</v>
+        <v>1870423.578071429</v>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>1815945.221428572</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>1961220.839142857</v>
+        <v>1870423.578071429</v>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>1741864.803061225</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>1881213.987306123</v>
+        <v>1794120.747153061</v>
       </c>
       <c r="G150" s="2" t="inlineStr">
         <is>
@@ -7444,7 +7444,7 @@
         <v>1741864.803061225</v>
       </c>
       <c r="F151" s="3" t="n">
-        <v>1881213.987306123</v>
+        <v>1794120.747153061</v>
       </c>
       <c r="G151" s="2" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>15857.10618556701</v>
       </c>
       <c r="F152" s="3" t="n">
-        <v>17125.67468041237</v>
+        <v>16332.81937113402</v>
       </c>
       <c r="G152" s="2" t="inlineStr">
         <is>
@@ -7522,7 +7522,7 @@
         <v>65941.14795918367</v>
       </c>
       <c r="F153" s="3" t="n">
-        <v>71216.43979591837</v>
+        <v>67919.38239795918</v>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>11099.09484536083</v>
       </c>
       <c r="F154" s="3" t="n">
-        <v>11987.02243298969</v>
+        <v>11432.06769072165</v>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         <v>8966.255102040817</v>
       </c>
       <c r="F155" s="3" t="n">
-        <v>9683.555510204083</v>
+        <v>9235.242755102043</v>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         <v>54424.29795918367</v>
       </c>
       <c r="F156" s="3" t="n">
-        <v>58778.24179591837</v>
+        <v>56057.02689795918</v>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         <v>22293.76632653061</v>
       </c>
       <c r="F157" s="3" t="n">
-        <v>24077.26763265306</v>
+        <v>22962.57931632653</v>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
@@ -7717,7 +7717,7 @@
         <v>37153.37551020408</v>
       </c>
       <c r="F158" s="3" t="n">
-        <v>40125.64555102041</v>
+        <v>38267.97677551021</v>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
@@ -7756,7 +7756,7 @@
         <v>1084107.292857143</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>1170835.876285715</v>
+        <v>1116630.511642857</v>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>1404655.265306122</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>1517027.686530612</v>
+        <v>1446794.923265306</v>
       </c>
       <c r="G160" s="2" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>836098.9357142857</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>902986.8505714287</v>
+        <v>861181.9037857143</v>
       </c>
       <c r="G161" s="2" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>1367971.965306123</v>
       </c>
       <c r="F162" s="3" t="n">
-        <v>1477409.722530612</v>
+        <v>1409011.124265306</v>
       </c>
       <c r="G162" s="2" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>593069.8969387754</v>
       </c>
       <c r="F163" s="3" t="n">
-        <v>640515.4886938775</v>
+        <v>610861.9938469387</v>
       </c>
       <c r="G163" s="2" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>593069.8969387754</v>
       </c>
       <c r="F164" s="3" t="n">
-        <v>640515.4886938775</v>
+        <v>610861.9938469387</v>
       </c>
       <c r="G164" s="2" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>3401649.198979592</v>
       </c>
       <c r="F165" s="3" t="n">
-        <v>3673781.134897959</v>
+        <v>3503698.67494898</v>
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
@@ -8029,7 +8029,7 @@
         <v>3401649.198979592</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>3673781.134897959</v>
+        <v>3503698.67494898</v>
       </c>
       <c r="G166" s="2" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>4083545.957142857</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>4410229.633714287</v>
+        <v>4206052.335857144</v>
       </c>
       <c r="G167" s="2" t="inlineStr">
         <is>
@@ -8107,7 +8107,7 @@
         <v>66141.36530612245</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>71432.67453061225</v>
+        <v>68125.60626530612</v>
       </c>
       <c r="G168" s="2" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
         <v>144678.7959183673</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>156253.0995918367</v>
+        <v>149019.1597959184</v>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
@@ -8185,7 +8185,7 @@
         <v>144678.7959183673</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>156253.0995918367</v>
+        <v>149019.1597959184</v>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         <v>157649.3979591837</v>
       </c>
       <c r="F171" s="3" t="n">
-        <v>170261.3497959184</v>
+        <v>162378.8798979592</v>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
@@ -8263,7 +8263,7 @@
         <v>441191.981632653</v>
       </c>
       <c r="F172" s="3" t="n">
-        <v>476487.3401632653</v>
+        <v>454427.7410816327</v>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         <v>187499.1928571429</v>
       </c>
       <c r="F173" s="3" t="n">
-        <v>202499.1282857143</v>
+        <v>193124.1686428571</v>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
@@ -8341,7 +8341,7 @@
         <v>622850.0510204082</v>
       </c>
       <c r="F174" s="3" t="n">
-        <v>672678.0551020409</v>
+        <v>641535.5525510204</v>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>128452.4857142857</v>
       </c>
       <c r="F175" s="3" t="n">
-        <v>138728.6845714286</v>
+        <v>132306.0602857143</v>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
@@ -8419,7 +8419,7 @@
         <v>223825.5836734694</v>
       </c>
       <c r="F176" s="3" t="n">
-        <v>241731.630367347</v>
+        <v>230540.3511836735</v>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
@@ -8458,7 +8458,7 @@
         <v>2624701.431632653</v>
       </c>
       <c r="F177" s="3" t="n">
-        <v>2834677.546163265</v>
+        <v>2703442.474581633</v>
       </c>
       <c r="G177" s="2" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>860943.2969387755</v>
       </c>
       <c r="F178" s="3" t="n">
-        <v>929818.7606938776</v>
+        <v>886771.5958469388</v>
       </c>
       <c r="G178" s="2" t="inlineStr">
         <is>
@@ -8536,7 +8536,7 @@
         <v>181405.6214285714</v>
       </c>
       <c r="F179" s="3" t="n">
-        <v>195918.0711428571</v>
+        <v>186847.7900714285</v>
       </c>
       <c r="G179" s="2" t="inlineStr">
         <is>
@@ -8575,7 +8575,7 @@
         <v>257235.7653061225</v>
       </c>
       <c r="F180" s="3" t="n">
-        <v>277814.6265306123</v>
+        <v>264952.8382653061</v>
       </c>
       <c r="G180" s="2" t="inlineStr">
         <is>
@@ -8614,7 +8614,7 @@
         <v>333074.6142857143</v>
       </c>
       <c r="F181" s="3" t="n">
-        <v>359720.5834285715</v>
+        <v>343066.8527142857</v>
       </c>
       <c r="G181" s="2" t="inlineStr">
         <is>
@@ -8653,7 +8653,7 @@
         <v>408164.8244897959</v>
       </c>
       <c r="F182" s="3" t="n">
-        <v>440818.0104489796</v>
+        <v>420409.7692244898</v>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>484003.6734693878</v>
       </c>
       <c r="F183" s="3" t="n">
-        <v>522723.9673469388</v>
+        <v>498523.7836734694</v>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
@@ -8731,7 +8731,7 @@
         <v>559093.8836734694</v>
       </c>
       <c r="F184" s="3" t="n">
-        <v>603821.394367347</v>
+        <v>575866.7001836735</v>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
@@ -8770,7 +8770,7 @@
         <v>634924.0275510205</v>
       </c>
       <c r="F185" s="3" t="n">
-        <v>685717.9497551022</v>
+        <v>653971.7483775511</v>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>710022.9428571428</v>
       </c>
       <c r="F186" s="3" t="n">
-        <v>766824.7782857142</v>
+        <v>731323.631142857</v>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
@@ -8848,7 +8848,7 @@
         <v>785113.1530612245</v>
       </c>
       <c r="F187" s="3" t="n">
-        <v>847922.2053061225</v>
+        <v>808666.5476530612</v>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
@@ -8887,7 +8887,7 @@
         <v>208173.8102040816</v>
       </c>
       <c r="F188" s="3" t="n">
-        <v>224827.7150204082</v>
+        <v>214419.0245102041</v>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
@@ -8926,7 +8926,7 @@
         <v>290698.1775510204</v>
       </c>
       <c r="F189" s="3" t="n">
-        <v>313954.031755102</v>
+        <v>299419.122877551</v>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
@@ -8965,7 +8965,7 @@
         <v>372473.906122449</v>
       </c>
       <c r="F190" s="3" t="n">
-        <v>402271.818612245</v>
+        <v>383648.1233061225</v>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F191" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F192" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
@@ -9082,7 +9082,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F193" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
@@ -9121,7 +9121,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F194" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
@@ -9160,7 +9160,7 @@
         <v>10550000.43163265</v>
       </c>
       <c r="F195" s="3" t="n">
-        <v>11394000.46616327</v>
+        <v>10866500.44458163</v>
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>10550000.43163265</v>
       </c>
       <c r="F196" s="3" t="n">
-        <v>11394000.46616327</v>
+        <v>10866500.44458163</v>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
@@ -9238,7 +9238,7 @@
         <v>103515.3298969072</v>
       </c>
       <c r="F197" s="3" t="n">
-        <v>111796.5562886598</v>
+        <v>106620.7897938144</v>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
@@ -9277,7 +9277,7 @@
         <v>99925.86632653061</v>
       </c>
       <c r="F198" s="3" t="n">
-        <v>107919.9356326531</v>
+        <v>102923.6423163265</v>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
         <v>99908.45612244897</v>
       </c>
       <c r="F199" s="3" t="n">
-        <v>107901.1326122449</v>
+        <v>102905.7098061224</v>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         <v>100926.9530612245</v>
       </c>
       <c r="F200" s="3" t="n">
-        <v>109001.1093061225</v>
+        <v>103954.7616530612</v>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
@@ -9394,7 +9394,7 @@
         <v>3229.592857142858</v>
       </c>
       <c r="F201" s="3" t="n">
-        <v>3487.960285714286</v>
+        <v>3326.480642857143</v>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
@@ -9433,7 +9433,7 @@
         <v>1005656.913265306</v>
       </c>
       <c r="F202" s="3" t="n">
-        <v>1086109.466326531</v>
+        <v>1035826.620663265</v>
       </c>
       <c r="G202" s="2" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>1005656.913265306</v>
       </c>
       <c r="F203" s="3" t="n">
-        <v>1086109.466326531</v>
+        <v>1035826.620663265</v>
       </c>
       <c r="G203" s="2" t="inlineStr">
         <is>
@@ -9511,7 +9511,7 @@
         <v>811184.9336734693</v>
       </c>
       <c r="F204" s="3" t="n">
-        <v>876079.7283673469</v>
+        <v>835520.4816836735</v>
       </c>
       <c r="G204" s="2" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>811184.9336734693</v>
       </c>
       <c r="F205" s="3" t="n">
-        <v>876079.7283673469</v>
+        <v>835520.4816836735</v>
       </c>
       <c r="G205" s="2" t="inlineStr">
         <is>
@@ -9589,7 +9589,7 @@
         <v>1004429.493877551</v>
       </c>
       <c r="F206" s="3" t="n">
-        <v>1084783.853387755</v>
+        <v>1034562.378693878</v>
       </c>
       <c r="G206" s="2" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>220108.5051020408</v>
       </c>
       <c r="F207" s="3" t="n">
-        <v>237717.1855102041</v>
+        <v>226711.760255102</v>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
@@ -9667,7 +9667,7 @@
         <v>552713.0438775511</v>
       </c>
       <c r="F208" s="3" t="n">
-        <v>596930.0873877553</v>
+        <v>569294.4351938777</v>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>552713.0438775511</v>
       </c>
       <c r="F209" s="3" t="n">
-        <v>596930.0873877553</v>
+        <v>569294.4351938777</v>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>890218.5551020409</v>
       </c>
       <c r="F210" s="3" t="n">
-        <v>961436.0395102042</v>
+        <v>916925.1117551022</v>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
@@ -9784,7 +9784,7 @@
         <v>4277295.413265307</v>
       </c>
       <c r="F211" s="3" t="n">
-        <v>4619479.046326531</v>
+        <v>4405614.275663266</v>
       </c>
       <c r="G211" s="2" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>296234.6224489796</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>319933.392244898</v>
+        <v>305121.661122449</v>
       </c>
       <c r="G212" s="2" t="inlineStr">
         <is>
@@ -9862,7 +9862,7 @@
         <v>368922.224489796</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>398436.0024489797</v>
+        <v>379989.8912244898</v>
       </c>
       <c r="G213" s="2" t="inlineStr">
         <is>
@@ -9901,7 +9901,7 @@
         <v>395603.3622448979</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>427251.6312244898</v>
+        <v>407471.4631122449</v>
       </c>
       <c r="G214" s="2" t="inlineStr">
         <is>
@@ -9940,7 +9940,7 @@
         <v>25413.4</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>27446.472</v>
+        <v>26175.802</v>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
@@ -9979,7 +9979,7 @@
         <v>57094.84</v>
       </c>
       <c r="F216" s="3" t="n">
-        <v>61662.42720000001</v>
+        <v>58807.68520000001</v>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
@@ -10018,7 +10018,7 @@
         <v>28538.44</v>
       </c>
       <c r="F217" s="3" t="n">
-        <v>30821.51520000001</v>
+        <v>29394.5932</v>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>14260.24</v>
       </c>
       <c r="F218" s="3" t="n">
-        <v>15401.0592</v>
+        <v>14688.0472</v>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
@@ -10096,7 +10096,7 @@
         <v>61378.3</v>
       </c>
       <c r="F219" s="3" t="n">
-        <v>66288.56400000001</v>
+        <v>63219.649</v>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
@@ -10135,7 +10135,7 @@
         <v>165214.1316326531</v>
       </c>
       <c r="F220" s="3" t="n">
-        <v>178431.2621632653</v>
+        <v>170170.5555816327</v>
       </c>
       <c r="G220" s="2" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>242219.4642857143</v>
       </c>
       <c r="F221" s="3" t="n">
-        <v>261597.0214285715</v>
+        <v>249486.0482142857</v>
       </c>
       <c r="G221" s="2" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>346027.806122449</v>
       </c>
       <c r="F222" s="3" t="n">
-        <v>373710.0306122449</v>
+        <v>356408.6403061225</v>
       </c>
       <c r="G222" s="2" t="inlineStr">
         <is>
@@ -10252,7 +10252,7 @@
         <v>189658.0581632653</v>
       </c>
       <c r="F223" s="3" t="n">
-        <v>204830.7028163265</v>
+        <v>195347.7999081633</v>
       </c>
       <c r="G223" s="2" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>6276.378571428571</v>
       </c>
       <c r="F224" s="3" t="n">
-        <v>6778.488857142857</v>
+        <v>6464.669928571428</v>
       </c>
       <c r="G224" s="2" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>35325.30408163265</v>
       </c>
       <c r="F225" s="3" t="n">
-        <v>38151.32840816327</v>
+        <v>36385.06320408163</v>
       </c>
       <c r="G225" s="2" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>614867.4724489796</v>
       </c>
       <c r="F226" s="3" t="n">
-        <v>664056.870244898</v>
+        <v>633313.496622449</v>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>115481.8836734694</v>
       </c>
       <c r="F227" s="3" t="n">
-        <v>124720.434367347</v>
+        <v>118946.3401836735</v>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         <v>210854.9816326531</v>
       </c>
       <c r="F228" s="3" t="n">
-        <v>227723.3801632653</v>
+        <v>217180.6310816327</v>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>5666.38</v>
       </c>
       <c r="F229" s="3" t="n">
-        <v>6119.6904</v>
+        <v>5836.3714</v>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>4615.72</v>
       </c>
       <c r="F230" s="3" t="n">
-        <v>4984.9776</v>
+        <v>4754.1916</v>
       </c>
       <c r="G230" s="2" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>51062.87216494845</v>
       </c>
       <c r="F231" s="3" t="n">
-        <v>55147.90193814433</v>
+        <v>52594.7583298969</v>
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
@@ -10603,7 +10603,7 @@
         <v>386053.8653061225</v>
       </c>
       <c r="F232" s="3" t="n">
-        <v>416938.1745306123</v>
+        <v>397635.4812653061</v>
       </c>
       <c r="G232" s="2" t="inlineStr">
         <is>
@@ -10642,7 +10642,7 @@
         <v>538147.7927835052</v>
       </c>
       <c r="F233" s="3" t="n">
-        <v>581199.6162061857</v>
+        <v>554292.2265670103</v>
       </c>
       <c r="G233" s="2" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>494938.7175257732</v>
       </c>
       <c r="F234" s="3" t="n">
-        <v>534533.8149278351</v>
+        <v>509786.8790515464</v>
       </c>
       <c r="G234" s="2" t="inlineStr">
         <is>
@@ -10720,7 +10720,7 @@
         <v>538147.7927835052</v>
       </c>
       <c r="F235" s="3" t="n">
-        <v>581199.6162061857</v>
+        <v>554292.2265670103</v>
       </c>
       <c r="G235" s="2" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>494938.7175257732</v>
       </c>
       <c r="F236" s="3" t="n">
-        <v>534533.8149278351</v>
+        <v>509786.8790515464</v>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
@@ -10798,7 +10798,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F237" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F238" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
@@ -10876,7 +10876,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F239" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
@@ -10915,7 +10915,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F240" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F241" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
@@ -10993,7 +10993,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F242" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
@@ -11032,7 +11032,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F243" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F244" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G244" s="2" t="inlineStr">
         <is>
@@ -11110,7 +11110,7 @@
         <v>47738.77959183673</v>
       </c>
       <c r="F245" s="3" t="n">
-        <v>51557.88195918367</v>
+        <v>49170.94297959184</v>
       </c>
       <c r="G245" s="2" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>47738.77959183673</v>
       </c>
       <c r="F246" s="3" t="n">
-        <v>51557.88195918367</v>
+        <v>49170.94297959184</v>
       </c>
       <c r="G246" s="2" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>470185.7142857143</v>
       </c>
       <c r="F247" s="3" t="n">
-        <v>507800.5714285715</v>
+        <v>484291.2857142857</v>
       </c>
       <c r="G247" s="2" t="inlineStr">
         <is>
@@ -11227,7 +11227,7 @@
         <v>647365.306122449</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>699154.530612245</v>
+        <v>666786.2653061225</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -11266,7 +11266,7 @@
         <v>706481.1329896908</v>
       </c>
       <c r="F249" s="3" t="n">
-        <v>762999.623628866</v>
+        <v>727675.5669793815</v>
       </c>
       <c r="G249" s="2" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>706481.1329896908</v>
       </c>
       <c r="F250" s="3" t="n">
-        <v>762999.623628866</v>
+        <v>727675.5669793815</v>
       </c>
       <c r="G250" s="2" t="inlineStr">
         <is>
@@ -11344,7 +11344,7 @@
         <v>1369278.269072165</v>
       </c>
       <c r="F251" s="3" t="n">
-        <v>1478820.530597938</v>
+        <v>1410356.61714433</v>
       </c>
       <c r="G251" s="2" t="inlineStr">
         <is>
@@ -11383,7 +11383,7 @@
         <v>1369278.269072165</v>
       </c>
       <c r="F252" s="3" t="n">
-        <v>1478820.530597938</v>
+        <v>1410356.61714433</v>
       </c>
       <c r="G252" s="2" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>3055559.175257732</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>3300003.909278351</v>
+        <v>3147225.950515464</v>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>3055559.175257732</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>3300003.909278351</v>
+        <v>3147225.950515464</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>5398274.432989691</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>5830136.387628867</v>
+        <v>5560222.665979383</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -11539,7 +11539,7 @@
         <v>5398274.432989691</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>5830136.387628867</v>
+        <v>5560222.665979383</v>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
@@ -11578,7 +11578,7 @@
         <v>657461.5367346939</v>
       </c>
       <c r="F257" s="3" t="n">
-        <v>710058.4596734694</v>
+        <v>677185.3828367348</v>
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>657461.5367346939</v>
       </c>
       <c r="F258" s="3" t="n">
-        <v>710058.4596734694</v>
+        <v>677185.3828367348</v>
       </c>
       <c r="G258" s="2" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>104878.5309278351</v>
       </c>
       <c r="F259" s="3" t="n">
-        <v>113268.8134020619</v>
+        <v>108024.8868556701</v>
       </c>
       <c r="G259" s="2" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>107255.562244898</v>
       </c>
       <c r="F260" s="3" t="n">
-        <v>115836.0072244898</v>
+        <v>110473.2291122449</v>
       </c>
       <c r="G260" s="2" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>107255.562244898</v>
       </c>
       <c r="F261" s="3" t="n">
-        <v>115836.0072244898</v>
+        <v>110473.2291122449</v>
       </c>
       <c r="G261" s="2" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>6205.18</v>
       </c>
       <c r="F262" s="3" t="n">
-        <v>6701.594400000001</v>
+        <v>6391.335400000001</v>
       </c>
       <c r="G262" s="2" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         <v>104060.24</v>
       </c>
       <c r="F263" s="3" t="n">
-        <v>112385.0592</v>
+        <v>107182.0472</v>
       </c>
       <c r="G263" s="2" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>109744.58</v>
       </c>
       <c r="F264" s="3" t="n">
-        <v>118524.1464</v>
+        <v>113036.9174</v>
       </c>
       <c r="G264" s="2" t="inlineStr">
         <is>
@@ -11890,7 +11890,7 @@
         <v>55129.41122448979</v>
       </c>
       <c r="F265" s="3" t="n">
-        <v>59539.76412244898</v>
+        <v>56783.29356122448</v>
       </c>
       <c r="G265" s="2" t="inlineStr">
         <is>
@@ -11929,7 +11929,7 @@
         <v>209331.5887755102</v>
       </c>
       <c r="F266" s="3" t="n">
-        <v>226078.115877551</v>
+        <v>215611.5364387755</v>
       </c>
       <c r="G266" s="2" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>213494.8711340206</v>
       </c>
       <c r="F267" s="3" t="n">
-        <v>230574.4608247423</v>
+        <v>219899.7172680412</v>
       </c>
       <c r="G267" s="2" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>557213.5816326531</v>
       </c>
       <c r="F268" s="3" t="n">
-        <v>601790.6681632655</v>
+        <v>573929.9890816327</v>
       </c>
       <c r="G268" s="2" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>283444.72</v>
       </c>
       <c r="F269" s="3" t="n">
-        <v>306120.2976</v>
+        <v>291948.0616</v>
       </c>
       <c r="G269" s="2" t="inlineStr">
         <is>
@@ -12085,7 +12085,7 @@
         <v>1922295.453061224</v>
       </c>
       <c r="F270" s="3" t="n">
-        <v>2076079.089306123</v>
+        <v>1979964.316653061</v>
       </c>
       <c r="G270" s="2" t="inlineStr">
         <is>
@@ -12124,7 +12124,7 @@
         <v>2194834.787755102</v>
       </c>
       <c r="F271" s="3" t="n">
-        <v>2370421.570775511</v>
+        <v>2260679.831387755</v>
       </c>
       <c r="G271" s="2" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>20272.11855670103</v>
       </c>
       <c r="F272" s="3" t="n">
-        <v>21893.88804123712</v>
+        <v>20880.28211340206</v>
       </c>
       <c r="G272" s="2" t="inlineStr">
         <is>
@@ -12202,7 +12202,7 @@
         <v>54053.11958762886</v>
       </c>
       <c r="F273" s="3" t="n">
-        <v>58377.36915463918</v>
+        <v>55674.71317525773</v>
       </c>
       <c r="G273" s="2" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         <v>7129.478571428572</v>
       </c>
       <c r="F274" s="3" t="n">
-        <v>7699.836857142858</v>
+        <v>7343.362928571429</v>
       </c>
       <c r="G274" s="2" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>1268707.686734694</v>
       </c>
       <c r="F275" s="3" t="n">
-        <v>1370204.30167347</v>
+        <v>1306768.917336735</v>
       </c>
       <c r="G275" s="2" t="inlineStr">
         <is>
@@ -12319,7 +12319,7 @@
         <v>2883634.691836735</v>
       </c>
       <c r="F276" s="3" t="n">
-        <v>3114325.467183674</v>
+        <v>2970143.732591837</v>
       </c>
       <c r="G276" s="2" t="inlineStr">
         <is>
@@ -12358,7 +12358,7 @@
         <v>2536422.991836735</v>
       </c>
       <c r="F277" s="3" t="n">
-        <v>2739336.831183674</v>
+        <v>2612515.681591837</v>
       </c>
       <c r="G277" s="2" t="inlineStr">
         <is>
@@ -12397,7 +12397,7 @@
         <v>23069138.47040816</v>
       </c>
       <c r="F278" s="3" t="n">
-        <v>24914669.54804082</v>
+        <v>23761212.62452041</v>
       </c>
       <c r="G278" s="2" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>200678.7173469388</v>
       </c>
       <c r="F279" s="3" t="n">
-        <v>216733.0147346939</v>
+        <v>206699.078867347</v>
       </c>
       <c r="G279" s="2" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>200678.7173469388</v>
       </c>
       <c r="F280" s="3" t="n">
-        <v>216733.0147346939</v>
+        <v>206699.078867347</v>
       </c>
       <c r="G280" s="2" t="inlineStr">
         <is>
@@ -12514,7 +12514,7 @@
         <v>200678.7173469388</v>
       </c>
       <c r="F281" s="3" t="n">
-        <v>216733.0147346939</v>
+        <v>206699.078867347</v>
       </c>
       <c r="G281" s="2" t="inlineStr">
         <is>
@@ -12553,7 +12553,7 @@
         <v>200678.7173469388</v>
       </c>
       <c r="F282" s="3" t="n">
-        <v>216733.0147346939</v>
+        <v>206699.078867347</v>
       </c>
       <c r="G282" s="2" t="inlineStr">
         <is>
@@ -12592,7 +12592,7 @@
         <v>280359.1836734694</v>
       </c>
       <c r="F283" s="3" t="n">
-        <v>302787.918367347</v>
+        <v>288769.9591836735</v>
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>280359.1836734694</v>
       </c>
       <c r="F284" s="3" t="n">
-        <v>302787.918367347</v>
+        <v>288769.9591836735</v>
       </c>
       <c r="G284" s="2" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>280359.1836734694</v>
       </c>
       <c r="F285" s="3" t="n">
-        <v>302787.918367347</v>
+        <v>288769.9591836735</v>
       </c>
       <c r="G285" s="2" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>195764.462886598</v>
       </c>
       <c r="F286" s="3" t="n">
-        <v>211425.6199175258</v>
+        <v>201637.3967731959</v>
       </c>
       <c r="G286" s="2" t="inlineStr">
         <is>
@@ -12748,7 +12748,7 @@
         <v>195764.462886598</v>
       </c>
       <c r="F287" s="3" t="n">
-        <v>211425.6199175258</v>
+        <v>201637.3967731959</v>
       </c>
       <c r="G287" s="2" t="inlineStr">
         <is>
@@ -12787,7 +12787,7 @@
         <v>195764.462886598</v>
       </c>
       <c r="F288" s="3" t="n">
-        <v>211425.6199175258</v>
+        <v>201637.3967731959</v>
       </c>
       <c r="G288" s="2" t="inlineStr">
         <is>
@@ -12826,7 +12826,7 @@
         <v>195764.462886598</v>
       </c>
       <c r="F289" s="3" t="n">
-        <v>211425.6199175258</v>
+        <v>201637.3967731959</v>
       </c>
       <c r="G289" s="2" t="inlineStr">
         <is>
@@ -12865,7 +12865,7 @@
         <v>195764.462886598</v>
       </c>
       <c r="F290" s="3" t="n">
-        <v>211425.6199175258</v>
+        <v>201637.3967731959</v>
       </c>
       <c r="G290" s="2" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>195764.462886598</v>
       </c>
       <c r="F291" s="3" t="n">
-        <v>211425.6199175258</v>
+        <v>201637.3967731959</v>
       </c>
       <c r="G291" s="2" t="inlineStr">
         <is>
@@ -12943,7 +12943,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F292" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G292" s="2" t="inlineStr">
         <is>
@@ -12982,7 +12982,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F293" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G293" s="2" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F294" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G294" s="2" t="inlineStr">
         <is>
@@ -13060,7 +13060,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F295" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G295" s="2" t="inlineStr">
         <is>
@@ -13099,7 +13099,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F296" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G296" s="2" t="inlineStr">
         <is>
@@ -13138,7 +13138,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F297" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G297" s="2" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F298" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G298" s="2" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F299" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G299" s="2" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F300" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G300" s="2" t="inlineStr">
         <is>
@@ -13294,7 +13294,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F301" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G301" s="2" t="inlineStr">
         <is>
@@ -13333,7 +13333,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F302" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G302" s="2" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F303" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>664382.0928571429</v>
       </c>
       <c r="F304" s="3" t="n">
-        <v>717532.6602857144</v>
+        <v>684313.5556428572</v>
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
@@ -13450,7 +13450,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F305" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F306" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
@@ -13528,7 +13528,7 @@
         <v>167796.8546391753</v>
       </c>
       <c r="F307" s="3" t="n">
-        <v>181220.6030103093</v>
+        <v>172830.7602783505</v>
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
@@ -13567,7 +13567,7 @@
         <v>941204.337755102</v>
       </c>
       <c r="F308" s="3" t="n">
-        <v>1016500.68477551</v>
+        <v>969440.467887755</v>
       </c>
       <c r="G308" s="2" t="inlineStr">
         <is>
@@ -13606,7 +13606,7 @@
         <v>3017432.110204082</v>
       </c>
       <c r="F309" s="3" t="n">
-        <v>3258826.679020408</v>
+        <v>3107955.073510204</v>
       </c>
       <c r="G309" s="2" t="inlineStr">
         <is>
@@ -13645,7 +13645,7 @@
         <v>3017432.110204082</v>
       </c>
       <c r="F310" s="3" t="n">
-        <v>3258826.679020408</v>
+        <v>3107955.073510204</v>
       </c>
       <c r="G310" s="2" t="inlineStr">
         <is>
@@ -13684,7 +13684,7 @@
         <v>2643713.374489796</v>
       </c>
       <c r="F311" s="3" t="n">
-        <v>2855210.44444898</v>
+        <v>2723024.77572449</v>
       </c>
       <c r="G311" s="2" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>2643713.374489796</v>
       </c>
       <c r="F312" s="3" t="n">
-        <v>2855210.44444898</v>
+        <v>2723024.77572449</v>
       </c>
       <c r="G312" s="2" t="inlineStr">
         <is>
@@ -13762,7 +13762,7 @@
         <v>2643713.374489796</v>
       </c>
       <c r="F313" s="3" t="n">
-        <v>2855210.44444898</v>
+        <v>2723024.77572449</v>
       </c>
       <c r="G313" s="2" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>2643713.374489796</v>
       </c>
       <c r="F314" s="3" t="n">
-        <v>2855210.44444898</v>
+        <v>2723024.77572449</v>
       </c>
       <c r="G314" s="2" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>2643713.374489796</v>
       </c>
       <c r="F315" s="3" t="n">
-        <v>2855210.44444898</v>
+        <v>2723024.77572449</v>
       </c>
       <c r="G315" s="2" t="inlineStr">
         <is>
@@ -13879,7 +13879,7 @@
         <v>2643713.374489796</v>
       </c>
       <c r="F316" s="3" t="n">
-        <v>2855210.44444898</v>
+        <v>2723024.77572449</v>
       </c>
       <c r="G316" s="2" t="inlineStr">
         <is>
@@ -13918,7 +13918,7 @@
         <v>3273492.686734694</v>
       </c>
       <c r="F317" s="3" t="n">
-        <v>3535372.10167347</v>
+        <v>3371697.467336735</v>
       </c>
       <c r="G317" s="2" t="inlineStr">
         <is>
@@ -13957,7 +13957,7 @@
         <v>2955138.4</v>
       </c>
       <c r="F318" s="3" t="n">
-        <v>3191549.472000001</v>
+        <v>3043792.552000001</v>
       </c>
       <c r="G318" s="2" t="inlineStr">
         <is>
@@ -13996,7 +13996,7 @@
         <v>2955138.4</v>
       </c>
       <c r="F319" s="3" t="n">
-        <v>3191549.472000001</v>
+        <v>3043792.552000001</v>
       </c>
       <c r="G319" s="2" t="inlineStr">
         <is>
@@ -14035,7 +14035,7 @@
         <v>2955138.4</v>
       </c>
       <c r="F320" s="3" t="n">
-        <v>3191549.472000001</v>
+        <v>3043792.552000001</v>
       </c>
       <c r="G320" s="2" t="inlineStr">
         <is>
@@ -14074,7 +14074,7 @@
         <v>23521.18571428572</v>
       </c>
       <c r="F321" s="3" t="n">
-        <v>25402.88057142857</v>
+        <v>24226.82128571429</v>
       </c>
       <c r="G321" s="2" t="inlineStr">
         <is>
@@ -14113,7 +14113,7 @@
         <v>23521.18571428572</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>25402.88057142857</v>
+        <v>24226.82128571429</v>
       </c>
       <c r="G322" s="2" t="inlineStr">
         <is>
@@ -14152,7 +14152,7 @@
         <v>23521.18571428572</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>25402.88057142857</v>
+        <v>24226.82128571429</v>
       </c>
       <c r="G323" s="2" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>76117.41224489796</v>
       </c>
       <c r="F324" s="3" t="n">
-        <v>82206.8052244898</v>
+        <v>78400.93461224491</v>
       </c>
       <c r="G324" s="2" t="inlineStr">
         <is>
@@ -14230,7 +14230,7 @@
         <v>76117.41224489796</v>
       </c>
       <c r="F325" s="3" t="n">
-        <v>82206.8052244898</v>
+        <v>78400.93461224491</v>
       </c>
       <c r="G325" s="2" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>76117.41224489796</v>
       </c>
       <c r="F326" s="3" t="n">
-        <v>82206.8052244898</v>
+        <v>78400.93461224491</v>
       </c>
       <c r="G326" s="2" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>1186670.805102041</v>
       </c>
       <c r="F327" s="3" t="n">
-        <v>1281604.469510204</v>
+        <v>1222270.929255102</v>
       </c>
       <c r="G327" s="2" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>1186670.805102041</v>
       </c>
       <c r="F328" s="3" t="n">
-        <v>1281604.469510204</v>
+        <v>1222270.929255102</v>
       </c>
       <c r="G328" s="2" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>384013.2653061225</v>
       </c>
       <c r="F329" s="3" t="n">
-        <v>414734.3265306123</v>
+        <v>395533.6632653062</v>
       </c>
       <c r="G329" s="2" t="inlineStr">
         <is>
@@ -14425,7 +14425,7 @@
         <v>384013.2653061225</v>
       </c>
       <c r="F330" s="3" t="n">
-        <v>414734.3265306123</v>
+        <v>395533.6632653062</v>
       </c>
       <c r="G330" s="2" t="inlineStr">
         <is>
@@ -14464,7 +14464,7 @@
         <v>384013.2653061225</v>
       </c>
       <c r="F331" s="3" t="n">
-        <v>414734.3265306123</v>
+        <v>395533.6632653062</v>
       </c>
       <c r="G331" s="2" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>384013.306122449</v>
       </c>
       <c r="F332" s="3" t="n">
-        <v>414734.3706122449</v>
+        <v>395533.7053061225</v>
       </c>
       <c r="G332" s="2" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>320399.9857142857</v>
       </c>
       <c r="F333" s="3" t="n">
-        <v>346031.9845714286</v>
+        <v>330011.9852857143</v>
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
@@ -14581,7 +14581,7 @@
         <v>320399.9857142857</v>
       </c>
       <c r="F334" s="3" t="n">
-        <v>346031.9845714286</v>
+        <v>330011.9852857143</v>
       </c>
       <c r="G334" s="2" t="inlineStr">
         <is>
@@ -14620,7 +14620,7 @@
         <v>415738.2632653061</v>
       </c>
       <c r="F335" s="3" t="n">
-        <v>448997.3243265306</v>
+        <v>428210.4111632654</v>
       </c>
       <c r="G335" s="2" t="inlineStr">
         <is>
@@ -14659,7 +14659,7 @@
         <v>387263.8744897959</v>
       </c>
       <c r="F336" s="3" t="n">
-        <v>418244.9844489797</v>
+        <v>398881.7907244898</v>
       </c>
       <c r="G336" s="2" t="inlineStr">
         <is>
@@ -14698,7 +14698,7 @@
         <v>438519.5153061225</v>
       </c>
       <c r="F337" s="3" t="n">
-        <v>473601.0765306123</v>
+        <v>451675.1007653062</v>
       </c>
       <c r="G337" s="2" t="inlineStr">
         <is>
@@ -14737,7 +14737,7 @@
         <v>438519.5153061225</v>
       </c>
       <c r="F338" s="3" t="n">
-        <v>473601.0765306123</v>
+        <v>451675.1007653062</v>
       </c>
       <c r="G338" s="2" t="inlineStr">
         <is>
@@ -14776,7 +14776,7 @@
         <v>569505.1857142857</v>
       </c>
       <c r="F339" s="3" t="n">
-        <v>615065.6005714287</v>
+        <v>586590.3412857143</v>
       </c>
       <c r="G339" s="2" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>518249.5448979592</v>
       </c>
       <c r="F340" s="3" t="n">
-        <v>559709.508489796</v>
+        <v>533797.031244898</v>
       </c>
       <c r="G340" s="2" t="inlineStr">
         <is>
@@ -14854,7 +14854,7 @@
         <v>609374.5530612245</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>658124.5173061226</v>
+        <v>627655.7896530613</v>
       </c>
       <c r="G341" s="2" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>609374.5530612245</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>658124.5173061226</v>
+        <v>627655.7896530613</v>
       </c>
       <c r="G342" s="2" t="inlineStr">
         <is>
@@ -14932,7 +14932,7 @@
         <v>273357.6142857143</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>295226.2234285714</v>
+        <v>281558.3427142857</v>
       </c>
       <c r="G343" s="2" t="inlineStr">
         <is>
@@ -14971,7 +14971,7 @@
         <v>256269.4989795919</v>
       </c>
       <c r="F344" s="3" t="n">
-        <v>276771.0588979592</v>
+        <v>263957.5839489796</v>
       </c>
       <c r="G344" s="2" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>290445.7295918367</v>
       </c>
       <c r="F345" s="3" t="n">
-        <v>313681.3879591837</v>
+        <v>299159.1014795919</v>
       </c>
       <c r="G345" s="2" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>290445.7295918367</v>
       </c>
       <c r="F346" s="3" t="n">
-        <v>313681.3879591837</v>
+        <v>299159.1014795919</v>
       </c>
       <c r="G346" s="2" t="inlineStr">
         <is>
@@ -15088,7 +15088,7 @@
         <v>364482.6224489796</v>
       </c>
       <c r="F347" s="3" t="n">
-        <v>393641.232244898</v>
+        <v>375417.101122449</v>
       </c>
       <c r="G347" s="2" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>335999.5285714286</v>
       </c>
       <c r="F348" s="3" t="n">
-        <v>362879.4908571428</v>
+        <v>346079.5144285714</v>
       </c>
       <c r="G348" s="2" t="inlineStr">
         <is>
@@ -15166,7 +15166,7 @@
         <v>387263.8744897959</v>
       </c>
       <c r="F349" s="3" t="n">
-        <v>418244.9844489797</v>
+        <v>398881.7907244898</v>
       </c>
       <c r="G349" s="2" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>387263.8744897959</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>418244.9844489797</v>
+        <v>398881.7907244898</v>
       </c>
       <c r="G350" s="2" t="inlineStr">
         <is>
@@ -15244,7 +15244,7 @@
         <v>158807.1765306123</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>171511.7506530613</v>
+        <v>163571.3918265306</v>
       </c>
       <c r="G351" s="2" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>469117.9489795919</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>506647.3848979593</v>
+        <v>483191.4874489796</v>
       </c>
       <c r="G352" s="2" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>756374.2907216495</v>
       </c>
       <c r="F353" s="3" t="n">
-        <v>816884.2339793815</v>
+        <v>779065.519443299</v>
       </c>
       <c r="G353" s="2" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>221456.9387755102</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>239173.4938775511</v>
+        <v>228100.6469387755</v>
       </c>
       <c r="G354" s="2" t="inlineStr">
         <is>
@@ -15400,7 +15400,7 @@
         <v>221457.1428571429</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>239173.7142857143</v>
+        <v>228100.8571428572</v>
       </c>
       <c r="G355" s="2" t="inlineStr">
         <is>
@@ -15439,7 +15439,7 @@
         <v>221457.1428571429</v>
       </c>
       <c r="F356" s="3" t="n">
-        <v>239173.7142857143</v>
+        <v>228100.8571428572</v>
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
@@ -15478,7 +15478,7 @@
         <v>221457.1428571429</v>
       </c>
       <c r="F357" s="3" t="n">
-        <v>239173.7142857143</v>
+        <v>228100.8571428572</v>
       </c>
       <c r="G357" s="2" t="inlineStr">
         <is>
@@ -15517,7 +15517,7 @@
         <v>495468.2928571429</v>
       </c>
       <c r="F358" s="3" t="n">
-        <v>535105.7562857143</v>
+        <v>510332.3416428572</v>
       </c>
       <c r="G358" s="2" t="inlineStr">
         <is>
@@ -15556,7 +15556,7 @@
         <v>39860.66224489796</v>
       </c>
       <c r="F359" s="3" t="n">
-        <v>43049.5152244898</v>
+        <v>41056.4821122449</v>
       </c>
       <c r="G359" s="2" t="inlineStr">
         <is>
@@ -15595,7 +15595,7 @@
         <v>45553.79897959183</v>
       </c>
       <c r="F360" s="3" t="n">
-        <v>49198.10289795918</v>
+        <v>46920.41294897959</v>
       </c>
       <c r="G360" s="2" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45553.79897959183</v>
       </c>
       <c r="F361" s="3" t="n">
-        <v>49198.10289795918</v>
+        <v>46920.41294897959</v>
       </c>
       <c r="G361" s="2" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>182071.1340206186</v>
       </c>
       <c r="F362" s="3" t="n">
-        <v>196636.8247422681</v>
+        <v>187533.2680412371</v>
       </c>
       <c r="G362" s="2" t="inlineStr">
         <is>
@@ -15712,7 +15712,7 @@
         <v>182071.1340206186</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>196636.8247422681</v>
+        <v>187533.2680412371</v>
       </c>
       <c r="G363" s="2" t="inlineStr">
         <is>
@@ -15751,7 +15751,7 @@
         <v>182070.8886597938</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>196636.5597525773</v>
+        <v>187533.0153195876</v>
       </c>
       <c r="G364" s="2" t="inlineStr">
         <is>
@@ -15790,7 +15790,7 @@
         <v>288356.1224489796</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>311424.612244898</v>
+        <v>297006.806122449</v>
       </c>
       <c r="G365" s="2" t="inlineStr">
         <is>
@@ -15829,7 +15829,7 @@
         <v>288356.1224489796</v>
       </c>
       <c r="F366" s="3" t="n">
-        <v>311424.612244898</v>
+        <v>297006.806122449</v>
       </c>
       <c r="G366" s="2" t="inlineStr">
         <is>
@@ -15868,7 +15868,7 @@
         <v>288356.5051020408</v>
       </c>
       <c r="F367" s="3" t="n">
-        <v>311425.0255102041</v>
+        <v>297007.2002551021</v>
       </c>
       <c r="G367" s="2" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>209053.0612244898</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>225777.306122449</v>
+        <v>215324.6530612245</v>
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
@@ -15946,7 +15946,7 @@
         <v>209053.0612244898</v>
       </c>
       <c r="F369" s="3" t="n">
-        <v>225777.306122449</v>
+        <v>215324.6530612245</v>
       </c>
       <c r="G369" s="2" t="inlineStr">
         <is>
@@ -15985,7 +15985,7 @@
         <v>209053.0255102041</v>
       </c>
       <c r="F370" s="3" t="n">
-        <v>225777.2675510204</v>
+        <v>215324.6162755102</v>
       </c>
       <c r="G370" s="2" t="inlineStr">
         <is>
@@ -16024,7 +16024,7 @@
         <v>2897959.183673469</v>
       </c>
       <c r="F371" s="3" t="n">
-        <v>3129795.918367347</v>
+        <v>2984897.959183673</v>
       </c>
       <c r="G371" s="2" t="inlineStr">
         <is>
@@ -16063,7 +16063,7 @@
         <v>7680784.693877551</v>
       </c>
       <c r="F372" s="3" t="n">
-        <v>8295247.469387756</v>
+        <v>7911208.234693877</v>
       </c>
       <c r="G372" s="2" t="inlineStr">
         <is>
@@ -16102,7 +16102,7 @@
         <v>3205351.020408163</v>
       </c>
       <c r="F373" s="3" t="n">
-        <v>3461779.102040817</v>
+        <v>3301511.551020409</v>
       </c>
       <c r="G373" s="2" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>5059328.571428572</v>
       </c>
       <c r="F374" s="3" t="n">
-        <v>5464074.857142858</v>
+        <v>5211108.428571429</v>
       </c>
       <c r="G374" s="2" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>2051108.163265306</v>
       </c>
       <c r="F375" s="3" t="n">
-        <v>2215196.816326531</v>
+        <v>2112641.408163265</v>
       </c>
       <c r="G375" s="2" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>2113265.306122449</v>
       </c>
       <c r="F376" s="3" t="n">
-        <v>2282326.530612245</v>
+        <v>2176663.265306123</v>
       </c>
       <c r="G376" s="2" t="inlineStr">
         <is>
@@ -16258,7 +16258,7 @@
         <v>302040.8163265306</v>
       </c>
       <c r="F377" s="3" t="n">
-        <v>326204.0816326531</v>
+        <v>311102.0408163265</v>
       </c>
       <c r="G377" s="2" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>206214.2857142857</v>
       </c>
       <c r="F378" s="3" t="n">
-        <v>222711.4285714286</v>
+        <v>212400.7142857143</v>
       </c>
       <c r="G378" s="2" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>11895815.87628866</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>12847481.14639175</v>
+        <v>12252690.35257732</v>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
@@ -16375,7 +16375,7 @@
         <v>13947137.73195876</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>15062908.75051547</v>
+        <v>14365551.86391753</v>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
@@ -16414,7 +16414,7 @@
         <v>17815622.06185567</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>19240871.82680412</v>
+        <v>18350090.72371134</v>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
@@ -16453,7 +16453,7 @@
         <v>7261123.092783506</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>7842012.940206187</v>
+        <v>7478956.785567012</v>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>8828193.608247424</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>9534449.096907219</v>
+        <v>9093039.416494846</v>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
@@ -16531,7 +16531,7 @@
         <v>8720545.154639177</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>9418188.767010313</v>
+        <v>8982161.509278353</v>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>8720545.154639177</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>9418188.767010313</v>
+        <v>8982161.509278353</v>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
@@ -16609,7 +16609,7 @@
         <v>11039669.69072165</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>11922843.26597938</v>
+        <v>11370859.7814433</v>
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
@@ -16648,7 +16648,7 @@
         <v>11039669.69072165</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>11922843.26597938</v>
+        <v>11370859.7814433</v>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
@@ -16687,7 +16687,7 @@
         <v>14309141.64948454</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>15453872.9814433</v>
+        <v>14738415.89896907</v>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
@@ -16726,7 +16726,7 @@
         <v>14309141.64948454</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>15453872.9814433</v>
+        <v>14738415.89896907</v>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
@@ -16765,7 +16765,7 @@
         <v>3530798.556701031</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>3813262.441237114</v>
+        <v>3636722.513402062</v>
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>3530798.556701031</v>
       </c>
       <c r="F391" s="3" t="n">
-        <v>3813262.441237114</v>
+        <v>3636722.513402062</v>
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
@@ -16843,7 +16843,7 @@
         <v>4969903.298969072</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>5367495.562886599</v>
+        <v>5119000.397938144</v>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>4969903.298969072</v>
       </c>
       <c r="F393" s="3" t="n">
-        <v>5367495.562886599</v>
+        <v>5119000.397938144</v>
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
@@ -16921,7 +16921,7 @@
         <v>6609796.907216495</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>7138580.659793815</v>
+        <v>6808090.81443299</v>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
@@ -16960,7 +16960,7 @@
         <v>6609796.907216495</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>7138580.659793815</v>
+        <v>6808090.81443299</v>
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
@@ -16999,7 +16999,7 @@
         <v>584312.5642857143</v>
       </c>
       <c r="F396" s="3" t="n">
-        <v>631057.5694285715</v>
+        <v>601841.9412142858</v>
       </c>
       <c r="G396" s="2" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>1083080.090816327</v>
       </c>
       <c r="F397" s="3" t="n">
-        <v>1169726.498081633</v>
+        <v>1115572.493540816</v>
       </c>
       <c r="G397" s="2" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>584312.5642857143</v>
       </c>
       <c r="F398" s="3" t="n">
-        <v>631057.5694285715</v>
+        <v>601841.9412142858</v>
       </c>
       <c r="G398" s="2" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>728710.0000000001</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>787006.8000000002</v>
+        <v>750571.3000000002</v>
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
@@ -17155,7 +17155,7 @@
         <v>903010.0000000001</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>975250.8000000002</v>
+        <v>930100.3000000002</v>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>2143500</v>
       </c>
       <c r="F401" s="3" t="n">
-        <v>2314980</v>
+        <v>2207805</v>
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>3675100</v>
       </c>
       <c r="F402" s="3" t="n">
-        <v>3969108</v>
+        <v>3785353</v>
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>5447760</v>
       </c>
       <c r="F403" s="3" t="n">
-        <v>5883580.800000001</v>
+        <v>5611192.8</v>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>1503562.634693878</v>
       </c>
       <c r="F404" s="3" t="n">
-        <v>1623847.645469388</v>
+        <v>1548669.513734694</v>
       </c>
       <c r="G404" s="2" t="inlineStr">
         <is>
@@ -17350,7 +17350,7 @@
         <v>760660.5214285714</v>
       </c>
       <c r="F405" s="3" t="n">
-        <v>821513.3631428572</v>
+        <v>783480.3370714285</v>
       </c>
       <c r="G405" s="2" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>158184.0886597938</v>
       </c>
       <c r="F406" s="3" t="n">
-        <v>170838.8157525773</v>
+        <v>162929.6113195876</v>
       </c>
       <c r="G406" s="2" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>626641.5268041237</v>
       </c>
       <c r="F407" s="3" t="n">
-        <v>676772.8489484536</v>
+        <v>645440.7726082474</v>
       </c>
       <c r="G407" s="2" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>626641.5268041237</v>
       </c>
       <c r="F408" s="3" t="n">
-        <v>676772.8489484536</v>
+        <v>645440.7726082474</v>
       </c>
       <c r="G408" s="2" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>626641.5268041237</v>
       </c>
       <c r="F409" s="3" t="n">
-        <v>676772.8489484536</v>
+        <v>645440.7726082474</v>
       </c>
       <c r="G409" s="2" t="inlineStr">
         <is>
@@ -17545,7 +17545,7 @@
         <v>626641.5268041237</v>
       </c>
       <c r="F410" s="3" t="n">
-        <v>676772.8489484536</v>
+        <v>645440.7726082474</v>
       </c>
       <c r="G410" s="2" t="inlineStr">
         <is>
@@ -17584,7 +17584,7 @@
         <v>713675.3164948454</v>
       </c>
       <c r="F411" s="3" t="n">
-        <v>770769.3418144331</v>
+        <v>735085.5759896908</v>
       </c>
       <c r="G411" s="2" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>713675.3164948454</v>
       </c>
       <c r="F412" s="3" t="n">
-        <v>770769.3418144331</v>
+        <v>735085.5759896908</v>
       </c>
       <c r="G412" s="2" t="inlineStr">
         <is>
@@ -17662,7 +17662,7 @@
         <v>713675.3164948454</v>
       </c>
       <c r="F413" s="3" t="n">
-        <v>770769.3418144331</v>
+        <v>735085.5759896908</v>
       </c>
       <c r="G413" s="2" t="inlineStr">
         <is>
@@ -17701,7 +17701,7 @@
         <v>713675.3164948454</v>
       </c>
       <c r="F414" s="3" t="n">
-        <v>770769.3418144331</v>
+        <v>735085.5759896908</v>
       </c>
       <c r="G414" s="2" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
         <v>733692.3845360825</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>792387.7752989691</v>
+        <v>755703.156072165</v>
       </c>
       <c r="G415" s="2" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>622832.6408163266</v>
       </c>
       <c r="F416" s="3" t="n">
-        <v>672659.2520816327</v>
+        <v>641517.6200408164</v>
       </c>
       <c r="G416" s="2" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>622832.6408163266</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>672659.2520816327</v>
+        <v>641517.6200408164</v>
       </c>
       <c r="G417" s="2" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>622832.6408163266</v>
       </c>
       <c r="F418" s="3" t="n">
-        <v>672659.2520816327</v>
+        <v>641517.6200408164</v>
       </c>
       <c r="G418" s="2" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>622832.6408163266</v>
       </c>
       <c r="F419" s="3" t="n">
-        <v>672659.2520816327</v>
+        <v>641517.6200408164</v>
       </c>
       <c r="G419" s="2" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>745873.2453608247</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>805543.1049896908</v>
+        <v>768249.4427216495</v>
       </c>
       <c r="G420" s="2" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>789064.7309278351</v>
       </c>
       <c r="F421" s="3" t="n">
-        <v>852189.909402062</v>
+        <v>812736.6728556702</v>
       </c>
       <c r="G421" s="2" t="inlineStr">
         <is>
@@ -18013,7 +18013,7 @@
         <v>36551.37731958763</v>
       </c>
       <c r="F422" s="3" t="n">
-        <v>39475.48750515465</v>
+        <v>37647.91863917527</v>
       </c>
       <c r="G422" s="2" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>28715.17010309278</v>
       </c>
       <c r="F423" s="3" t="n">
-        <v>31012.38371134021</v>
+        <v>29576.62520618557</v>
       </c>
       <c r="G423" s="2" t="inlineStr">
         <is>
@@ -18091,7 +18091,7 @@
         <v>86163.09999999999</v>
       </c>
       <c r="F424" s="3" t="n">
-        <v>93056.148</v>
+        <v>88747.99299999999</v>
       </c>
       <c r="G424" s="2" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>73102.75463917527</v>
       </c>
       <c r="F425" s="3" t="n">
-        <v>78950.9750103093</v>
+        <v>75295.83727835053</v>
       </c>
       <c r="G425" s="2" t="inlineStr">
         <is>
@@ -18169,7 +18169,7 @@
         <v>281989.1268041237</v>
       </c>
       <c r="F426" s="3" t="n">
-        <v>304548.2569484536</v>
+        <v>290448.8006082474</v>
       </c>
       <c r="G426" s="2" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>253265.1618556701</v>
       </c>
       <c r="F427" s="3" t="n">
-        <v>273526.3748041237</v>
+        <v>260863.1167113402</v>
       </c>
       <c r="G427" s="2" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         <v>555254.9336734693</v>
       </c>
       <c r="F428" s="3" t="n">
-        <v>599675.3283673469</v>
+        <v>571912.5816836734</v>
       </c>
       <c r="G428" s="2" t="inlineStr">
         <is>
@@ -18286,7 +18286,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F429" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G429" s="2" t="inlineStr">
         <is>
@@ -18325,7 +18325,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F430" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G430" s="2" t="inlineStr">
         <is>
@@ -18364,7 +18364,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F431" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G431" s="2" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>11243797.06428571</v>
       </c>
       <c r="F432" s="3" t="n">
-        <v>12143300.82942857</v>
+        <v>11581110.97621429</v>
       </c>
       <c r="G432" s="2" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>13363428.4755102</v>
       </c>
       <c r="F433" s="3" t="n">
-        <v>14432502.75355102</v>
+        <v>13764331.32977551</v>
       </c>
       <c r="G433" s="2" t="inlineStr">
         <is>
@@ -18481,7 +18481,7 @@
         <v>571136.9800000001</v>
       </c>
       <c r="F434" s="3" t="n">
-        <v>616827.9384000001</v>
+        <v>588271.0894000002</v>
       </c>
       <c r="G434" s="2" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>427037.4857142857</v>
       </c>
       <c r="F435" s="3" t="n">
-        <v>461200.4845714286</v>
+        <v>439848.6102857143</v>
       </c>
       <c r="G435" s="2" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>1411123.156122449</v>
       </c>
       <c r="F436" s="3" t="n">
-        <v>1524013.008612245</v>
+        <v>1453456.850806123</v>
       </c>
       <c r="G436" s="2" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>1411123.156122449</v>
       </c>
       <c r="F437" s="3" t="n">
-        <v>1524013.008612245</v>
+        <v>1453456.850806123</v>
       </c>
       <c r="G437" s="2" t="inlineStr">
         <is>
@@ -18637,7 +18637,7 @@
         <v>1198640.320408163</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>1294531.546040816</v>
+        <v>1234599.530020408</v>
       </c>
       <c r="G438" s="2" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>1198640.320408163</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>1294531.546040816</v>
+        <v>1234599.530020408</v>
       </c>
       <c r="G439" s="2" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>1198640.320408163</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>1294531.546040816</v>
+        <v>1234599.530020408</v>
       </c>
       <c r="G440" s="2" t="inlineStr">
         <is>
@@ -18754,7 +18754,7 @@
         <v>1198640.320408163</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>1294531.546040816</v>
+        <v>1234599.530020408</v>
       </c>
       <c r="G441" s="2" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
         <v>398502.1612244898</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>430382.334122449</v>
+        <v>410457.2260612245</v>
       </c>
       <c r="G442" s="2" t="inlineStr">
         <is>
@@ -18832,7 +18832,7 @@
         <v>1331967.663265306</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>1438525.076326531</v>
+        <v>1371926.693163265</v>
       </c>
       <c r="G443" s="2" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
         <v>1331967.663265306</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>1438525.076326531</v>
+        <v>1371926.693163265</v>
       </c>
       <c r="G444" s="2" t="inlineStr">
         <is>
@@ -18910,7 +18910,7 @@
         <v>346463.0612244898</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>374180.106122449</v>
+        <v>356856.9530612245</v>
       </c>
       <c r="G445" s="2" t="inlineStr">
         <is>
@@ -18949,7 +18949,7 @@
         <v>346463.0612244898</v>
       </c>
       <c r="F446" s="3" t="n">
-        <v>374180.106122449</v>
+        <v>356856.9530612245</v>
       </c>
       <c r="G446" s="2" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>6243769.259183673</v>
       </c>
       <c r="F447" s="3" t="n">
-        <v>6743270.799918368</v>
+        <v>6431082.336959183</v>
       </c>
       <c r="G447" s="2" t="inlineStr">
         <is>
@@ -19027,7 +19027,7 @@
         <v>6243769.259183673</v>
       </c>
       <c r="F448" s="3" t="n">
-        <v>6743270.799918368</v>
+        <v>6431082.336959183</v>
       </c>
       <c r="G448" s="2" t="inlineStr">
         <is>
@@ -19066,7 +19066,7 @@
         <v>6342406.770408163</v>
       </c>
       <c r="F449" s="3" t="n">
-        <v>6849799.312040816</v>
+        <v>6532678.973520407</v>
       </c>
       <c r="G449" s="2" t="inlineStr">
         <is>
@@ -19105,7 +19105,7 @@
         <v>6342406.770408163</v>
       </c>
       <c r="F450" s="3" t="n">
-        <v>6849799.312040816</v>
+        <v>6532678.973520407</v>
       </c>
       <c r="G450" s="2" t="inlineStr">
         <is>
@@ -19144,7 +19144,7 @@
         <v>421283.4132653062</v>
       </c>
       <c r="F451" s="3" t="n">
-        <v>454986.0863265307</v>
+        <v>433921.9156632653</v>
       </c>
       <c r="G451" s="2" t="inlineStr">
         <is>
@@ -19183,7 +19183,7 @@
         <v>540734.8234693877</v>
       </c>
       <c r="F452" s="3" t="n">
-        <v>583993.6093469388</v>
+        <v>556956.8681734693</v>
       </c>
       <c r="G452" s="2" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>421283.4132653062</v>
       </c>
       <c r="F453" s="3" t="n">
-        <v>454986.0863265307</v>
+        <v>433921.9156632653</v>
       </c>
       <c r="G453" s="2" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>931350.1622448979</v>
       </c>
       <c r="F454" s="3" t="n">
-        <v>1005858.17522449</v>
+        <v>959290.6671122449</v>
       </c>
       <c r="G454" s="2" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>425626.5412371134</v>
       </c>
       <c r="F455" s="3" t="n">
-        <v>459676.6645360825</v>
+        <v>438395.3374742268</v>
       </c>
       <c r="G455" s="2" t="inlineStr">
         <is>
@@ -19339,7 +19339,7 @@
         <v>546309.4092783505</v>
       </c>
       <c r="F456" s="3" t="n">
-        <v>590014.1620206186</v>
+        <v>562698.6915567011</v>
       </c>
       <c r="G456" s="2" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>425626.5412371134</v>
       </c>
       <c r="F457" s="3" t="n">
-        <v>459676.6645360825</v>
+        <v>438395.3374742268</v>
       </c>
       <c r="G457" s="2" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>931350.1622448979</v>
       </c>
       <c r="F458" s="3" t="n">
-        <v>1005858.17522449</v>
+        <v>959290.6671122449</v>
       </c>
       <c r="G458" s="2" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>61968.48041237114</v>
       </c>
       <c r="F459" s="3" t="n">
-        <v>66925.95884536083</v>
+        <v>63827.53482474227</v>
       </c>
       <c r="G459" s="2" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>12887259.39387755</v>
       </c>
       <c r="F460" s="3" t="n">
-        <v>13918240.14538776</v>
+        <v>13273877.17569388</v>
       </c>
       <c r="G460" s="2" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>6359695.103061224</v>
       </c>
       <c r="F461" s="3" t="n">
-        <v>6868470.711306123</v>
+        <v>6550485.956153061</v>
       </c>
       <c r="G461" s="2" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>7271258.163265307</v>
       </c>
       <c r="F462" s="3" t="n">
-        <v>7852958.816326532</v>
+        <v>7489395.908163266</v>
       </c>
       <c r="G462" s="2" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>49227.35204081633</v>
       </c>
       <c r="F463" s="3" t="n">
-        <v>53165.54020408164</v>
+        <v>50704.17260204082</v>
       </c>
       <c r="G463" s="2" t="inlineStr">
         <is>
@@ -19651,7 +19651,7 @@
         <v>49227.35204081633</v>
       </c>
       <c r="F464" s="3" t="n">
-        <v>53165.54020408164</v>
+        <v>50704.17260204082</v>
       </c>
       <c r="G464" s="2" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>65532.00816326531</v>
       </c>
       <c r="F465" s="3" t="n">
-        <v>70774.56881632654</v>
+        <v>67497.96840816327</v>
       </c>
       <c r="G465" s="2" t="inlineStr">
         <is>
@@ -19729,7 +19729,7 @@
         <v>1204141.944897959</v>
       </c>
       <c r="F466" s="3" t="n">
-        <v>1300473.300489796</v>
+        <v>1240266.203244898</v>
       </c>
       <c r="G466" s="2" t="inlineStr">
         <is>
@@ -19768,7 +19768,7 @@
         <v>2028680.594845361</v>
       </c>
       <c r="F467" s="3" t="n">
-        <v>2190975.04243299</v>
+        <v>2089541.012690722</v>
       </c>
       <c r="G467" s="2" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>52179.8175257732</v>
       </c>
       <c r="F468" s="3" t="n">
-        <v>56354.20292783506</v>
+        <v>53745.2120515464</v>
       </c>
       <c r="G468" s="2" t="inlineStr">
         <is>
@@ -19846,7 +19846,7 @@
         <v>1170244.27755102</v>
       </c>
       <c r="F469" s="3" t="n">
-        <v>1263863.819755102</v>
+        <v>1205351.605877551</v>
       </c>
       <c r="G469" s="2" t="inlineStr">
         <is>
@@ -19885,7 +19885,7 @@
         <v>368547.9948453608</v>
       </c>
       <c r="F470" s="3" t="n">
-        <v>398031.8344329897</v>
+        <v>379604.4346907216</v>
       </c>
       <c r="G470" s="2" t="inlineStr">
         <is>
@@ -19924,7 +19924,7 @@
         <v>71097.52989690722</v>
       </c>
       <c r="F471" s="3" t="n">
-        <v>76785.3322886598</v>
+        <v>73230.45579381444</v>
       </c>
       <c r="G471" s="2" t="inlineStr">
         <is>
@@ -19963,7 +19963,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F472" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G472" s="2" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F473" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G473" s="2" t="inlineStr">
         <is>
@@ -20041,7 +20041,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F474" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G474" s="2" t="inlineStr">
         <is>
@@ -20080,7 +20080,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F475" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G475" s="2" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F476" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G476" s="2" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F477" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G477" s="2" t="inlineStr">
         <is>
@@ -20197,7 +20197,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F478" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G478" s="2" t="inlineStr">
         <is>
@@ -20236,7 +20236,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F479" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G479" s="2" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F480" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G480" s="2" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>1695571.070408163</v>
       </c>
       <c r="F481" s="3" t="n">
-        <v>1831216.756040817</v>
+        <v>1746438.202520408</v>
       </c>
       <c r="G481" s="2" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>47738.77959183673</v>
       </c>
       <c r="F482" s="3" t="n">
-        <v>51557.88195918367</v>
+        <v>49170.94297959184</v>
       </c>
       <c r="G482" s="2" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>477518.3724489796</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>515719.842244898</v>
+        <v>491843.923622449</v>
       </c>
       <c r="G483" s="2" t="inlineStr">
         <is>
@@ -20431,7 +20431,7 @@
         <v>706481.1329896908</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>762999.623628866</v>
+        <v>727675.5669793815</v>
       </c>
       <c r="G484" s="2" t="inlineStr">
         <is>
@@ -20470,7 +20470,7 @@
         <v>706481.1329896908</v>
       </c>
       <c r="F485" s="3" t="n">
-        <v>762999.623628866</v>
+        <v>727675.5669793815</v>
       </c>
       <c r="G485" s="2" t="inlineStr">
         <is>
@@ -20509,7 +20509,7 @@
         <v>1369278.269072165</v>
       </c>
       <c r="F486" s="3" t="n">
-        <v>1478820.530597938</v>
+        <v>1410356.61714433</v>
       </c>
       <c r="G486" s="2" t="inlineStr">
         <is>
@@ -20548,7 +20548,7 @@
         <v>1369278.269072165</v>
       </c>
       <c r="F487" s="3" t="n">
-        <v>1478820.530597938</v>
+        <v>1410356.61714433</v>
       </c>
       <c r="G487" s="2" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>3055559.175257732</v>
       </c>
       <c r="F488" s="3" t="n">
-        <v>3300003.909278351</v>
+        <v>3147225.950515464</v>
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
@@ -20626,7 +20626,7 @@
         <v>2659895.441237114</v>
       </c>
       <c r="F489" s="3" t="n">
-        <v>2872687.076536083</v>
+        <v>2739692.304474228</v>
       </c>
       <c r="G489" s="2" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>5398274.432989691</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>5830136.387628867</v>
+        <v>5560222.665979383</v>
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>5398274.432989691</v>
       </c>
       <c r="F491" s="3" t="n">
-        <v>5830136.387628867</v>
+        <v>5560222.665979383</v>
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>657461.5367346939</v>
       </c>
       <c r="F492" s="3" t="n">
-        <v>710058.4596734694</v>
+        <v>677185.3828367348</v>
       </c>
       <c r="G492" s="2" t="inlineStr">
         <is>
@@ -20782,7 +20782,7 @@
         <v>647365.306122449</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>699154.530612245</v>
+        <v>666786.2653061225</v>
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
@@ -20821,7 +20821,7 @@
         <v>477518.3724489796</v>
       </c>
       <c r="F494" s="3" t="n">
-        <v>515719.842244898</v>
+        <v>491843.923622449</v>
       </c>
       <c r="G494" s="2" t="inlineStr">
         <is>
@@ -21704,7 +21704,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -21729,7 +21729,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>890022.1680000001</v>
@@ -21767,7 +21767,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
     </row>
     <row r="3">
@@ -21789,7 +21789,7 @@
         <v>290687.0204081628</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>15697099.10204082</v>
+        <v>14970381.55102041</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>14352693.2</v>
@@ -21804,7 +21804,7 @@
         <v>292912.106122449</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>15817253.73061225</v>
+        <v>15084973.46530612</v>
       </c>
     </row>
     <row r="4">
@@ -21833,7 +21833,7 @@
         <v>68839.65861224476</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>3717341.565061225</v>
+        <v>3545242.418530612</v>
       </c>
     </row>
     <row r="5">
@@ -21855,7 +21855,7 @@
         <v>56886.30612244923</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3071860.530612245</v>
+        <v>2929644.765306123</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2787429</v>
@@ -21870,7 +21870,7 @@
         <v>56886.30612244923</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3071860.530612245</v>
+        <v>2929644.765306123</v>
       </c>
     </row>
     <row r="6">
@@ -21892,7 +21892,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -21907,7 +21907,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -21929,7 +21929,7 @@
         <v>178186.8062448986</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9622087.537224492</v>
+        <v>9176620.521612247</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>14757959.936</v>
@@ -21944,7 +21944,7 @@
         <v>301182.8558367342</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>16263874.21518368</v>
+        <v>15510917.07559184</v>
       </c>
     </row>
     <row r="8">
@@ -21966,7 +21966,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>113615.858</v>
@@ -21981,7 +21981,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
     </row>
     <row r="9">
@@ -22003,7 +22003,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>503994.418</v>
@@ -22018,7 +22018,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
     </row>
     <row r="10">
@@ -22040,7 +22040,7 @@
         <v>13884.98595918366</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>749789.2417959184</v>
+        <v>715076.7768979592</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1019795.74</v>
@@ -22055,7 +22055,7 @@
         <v>20812.15795918368</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1123856.529795918</v>
+        <v>1071826.134897959</v>
       </c>
     </row>
     <row r="11">
@@ -22077,7 +22077,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -22092,7 +22092,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -22114,7 +22114,7 @@
         <v>20687.87368421053</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>446858.0715789474</v>
+        <v>426170.1978947368</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>749034</v>
@@ -22129,7 +22129,7 @@
         <v>39422.84210526315</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>851533.3894736842</v>
+        <v>812110.5473684211</v>
       </c>
     </row>
     <row r="13">
@@ -22151,7 +22151,7 @@
         <v>7777.105855670117</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>279975.8108041238</v>
+        <v>267013.9677113402</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>278093.538</v>
@@ -22166,7 +22166,7 @@
         <v>8600.831072164932</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>309629.9185979381</v>
+        <v>295295.2001443299</v>
       </c>
     </row>
     <row r="14">
@@ -22186,7 +22186,7 @@
         <v>742005.3058664128</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>39258011.50401574</v>
+        <v>37440510.9714224</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>47710885.87800001</v>
@@ -22199,7 +22199,7 @@
         <v>1000753.435218245</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>52608570.45827571</v>
+        <v>50172988.4926148</v>
       </c>
     </row>
   </sheetData>
@@ -22258,7 +22258,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -22283,7 +22283,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -22306,7 +22306,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>890022.1680000001</v>
@@ -22321,7 +22321,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
     </row>
     <row r="3">
@@ -22343,7 +22343,7 @@
         <v>581374.0408163257</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>31394198.20408163</v>
+        <v>29940763.10204082</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>28705386.4</v>
@@ -22358,7 +22358,7 @@
         <v>585824.2122448981</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>31634507.46122449</v>
+        <v>30169946.93061225</v>
       </c>
     </row>
     <row r="4">
@@ -22380,7 +22380,7 @@
         <v>132286.9090612242</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7143493.089306123</v>
+        <v>6812775.816653061</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>6746286.544</v>
@@ -22395,7 +22395,7 @@
         <v>137679.3172244895</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>7434683.130122449</v>
+        <v>7090484.837061225</v>
       </c>
     </row>
     <row r="5">
@@ -22417,7 +22417,7 @@
         <v>56886.30612244923</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3071860.530612245</v>
+        <v>2929644.765306123</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5574858</v>
@@ -22432,7 +22432,7 @@
         <v>113772.6122448985</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>6143721.06122449</v>
+        <v>5859289.530612245</v>
       </c>
     </row>
     <row r="6">
@@ -22454,7 +22454,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -22469,7 +22469,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -22491,7 +22491,7 @@
         <v>148133.0757551026</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7999186.090775511</v>
+        <v>7628853.401387756</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10260287.378</v>
@@ -22506,7 +22506,7 @@
         <v>209393.619959183</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>11307255.47779592</v>
+        <v>10783771.42789796</v>
       </c>
     </row>
     <row r="8">
@@ -22528,7 +22528,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>113615.858</v>
@@ -22543,7 +22543,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
     </row>
     <row r="9">
@@ -22565,7 +22565,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>503994.418</v>
@@ -22580,7 +22580,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
     </row>
     <row r="10">
@@ -22602,7 +22602,7 @@
         <v>26769.35330612259</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1445545.078530613</v>
+        <v>1378621.695265306</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2623396.624</v>
@@ -22617,7 +22617,7 @@
         <v>53538.70661224518</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>2891090.157061225</v>
+        <v>2757243.390530613</v>
       </c>
     </row>
     <row r="11">
@@ -22639,7 +22639,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -22654,7 +22654,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -22676,7 +22676,7 @@
         <v>30446.14736842108</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>657636.7831578949</v>
+        <v>627190.6357894738</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1290405.6</v>
@@ -22691,7 +22691,7 @@
         <v>67916.08421052643</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1466987.418947369</v>
+        <v>1399071.334736842</v>
       </c>
     </row>
     <row r="13">
@@ -22713,7 +22713,7 @@
         <v>8600.831072164932</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>309629.9185979381</v>
+        <v>295295.2001443299</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>331361.102</v>
@@ -22728,7 +22728,7 @@
         <v>10248.28150515462</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>368938.134185567</v>
+        <v>351857.6650103093</v>
       </c>
     </row>
     <row r="14">
@@ -22748,7 +22748,7 @@
         <v>1158391.871093653</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>61411890.90502114</v>
+        <v>58568747.80756646</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>65924718.84</v>
@@ -22761,7 +22761,7 @@
         <v>1390469.511389159</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>72700403.41950029</v>
+        <v>69334644.00193083</v>
       </c>
     </row>
   </sheetData>
@@ -22820,7 +22820,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -22845,7 +22845,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -22868,7 +22868,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1366359.084</v>
@@ -22883,7 +22883,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
     </row>
     <row r="3">
@@ -22905,7 +22905,7 @@
         <v>872061.0612244904</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>47091297.30612245</v>
+        <v>44911144.65306123</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>43058079.6</v>
@@ -22920,7 +22920,7 @@
         <v>878736.3183673471</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>47451761.19183674</v>
+        <v>45254920.39591837</v>
       </c>
     </row>
     <row r="4">
@@ -22942,7 +22942,7 @@
         <v>198430.3635918368</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>10715239.63395918</v>
+        <v>10219163.72497959</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>10119429.816</v>
@@ -22957,7 +22957,7 @@
         <v>206518.9758367352</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>11152024.69518367</v>
+        <v>10635727.25559184</v>
       </c>
     </row>
     <row r="5">
@@ -22979,7 +22979,7 @@
         <v>113772.6122448985</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6143721.06122449</v>
+        <v>5859289.530612245</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8362287</v>
@@ -22994,7 +22994,7 @@
         <v>170658.9183673467</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>9215581.591836736</v>
+        <v>8788934.295918368</v>
       </c>
     </row>
     <row r="6">
@@ -23016,7 +23016,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -23031,7 +23031,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -23053,7 +23053,7 @@
         <v>105380.0485714283</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5690522.622857143</v>
+        <v>5427072.501428572</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4985991.14</v>
@@ -23068,7 +23068,7 @@
         <v>101754.9212244898</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5494765.746122449</v>
+        <v>5240378.443061224</v>
       </c>
     </row>
     <row r="8">
@@ -23090,7 +23090,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>141290.422</v>
@@ -23105,7 +23105,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
     </row>
     <row r="9">
@@ -23127,7 +23127,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>786592.324</v>
@@ -23142,7 +23142,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
     </row>
     <row r="10">
@@ -23164,7 +23164,7 @@
         <v>39003.63902040827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2106196.507102041</v>
+        <v>2008687.409551021</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>3822356.624</v>
@@ -23179,7 +23179,7 @@
         <v>78007.27804081654</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>4212393.014204082</v>
+        <v>4017374.819102041</v>
       </c>
     </row>
     <row r="11">
@@ -23201,7 +23201,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -23216,7 +23216,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -23238,7 +23238,7 @@
         <v>40204.42105263157</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>868415.4947368422</v>
+        <v>828211.0736842107</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1831777.2</v>
@@ -23253,7 +23253,7 @@
         <v>96409.32631578948</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2082441.448421052</v>
+        <v>1986032.122105263</v>
       </c>
     </row>
     <row r="13">
@@ -23275,7 +23275,7 @@
         <v>13973.77799999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>503056.008</v>
+        <v>479766.378</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>531720.1680000001</v>
@@ -23290,7 +23290,7 @@
         <v>16444.95364948455</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>592018.3313814434</v>
+        <v>564610.0752989692</v>
       </c>
     </row>
     <row r="14">
@@ -23310,7 +23310,7 @@
         <v>1572774.384073049</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>83375665.49383889</v>
+        <v>79515680.98023523</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>83890988.12600002</v>
@@ -23323,7 +23323,7 @@
         <v>1776680.621965274</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>92521082.24780251</v>
+        <v>88237698.81040421</v>
       </c>
     </row>
   </sheetData>
@@ -23382,7 +23382,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -23407,7 +23407,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -23430,7 +23430,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1366359.084</v>
@@ -23445,7 +23445,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
     </row>
     <row r="3">
@@ -23467,7 +23467,7 @@
         <v>1162748.081632651</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>62788396.40816326</v>
+        <v>59881526.20408163</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>57410772.8</v>
@@ -23482,7 +23482,7 @@
         <v>1171648.424489796</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>63269014.92244898</v>
+        <v>60339893.86122449</v>
       </c>
     </row>
     <row r="4">
@@ -23504,7 +23504,7 @@
         <v>264573.8181224484</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>14286986.17861225</v>
+        <v>13625551.63330612</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>13492573.088</v>
@@ -23519,7 +23519,7 @@
         <v>275358.634448979</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>14869366.2602449</v>
+        <v>14180969.67412245</v>
       </c>
     </row>
     <row r="5">
@@ -23541,7 +23541,7 @@
         <v>113772.6122448985</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6143721.06122449</v>
+        <v>5859289.530612245</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>11149716</v>
@@ -23556,7 +23556,7 @@
         <v>227545.2244897969</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>12287442.12244898</v>
+        <v>11718579.06122449</v>
       </c>
     </row>
     <row r="6">
@@ -23578,7 +23578,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -23593,7 +23593,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -23615,7 +23615,7 @@
         <v>55557.48489795905</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3000104.184489796</v>
+        <v>2861210.472244898</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>2634757.52</v>
@@ -23630,7 +23630,7 @@
         <v>53770.56163265323</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>2903610.328163266</v>
+        <v>2769183.924081633</v>
       </c>
     </row>
     <row r="8">
@@ -23652,7 +23652,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>141290.422</v>
@@ -23667,7 +23667,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
     </row>
     <row r="9">
@@ -23689,7 +23689,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>786592.324</v>
@@ -23704,7 +23704,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
     </row>
     <row r="10">
@@ -23726,7 +23726,7 @@
         <v>51888.0063673472</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2801952.343836735</v>
+        <v>2672232.327918368</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>5085024.624000001</v>
@@ -23741,7 +23741,7 @@
         <v>103776.0127346944</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>5603904.687673471</v>
+        <v>5344464.655836736</v>
       </c>
     </row>
     <row r="11">
@@ -23763,7 +23763,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -23778,7 +23778,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -23800,7 +23800,7 @@
         <v>49962.69473684218</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1079194.20631579</v>
+        <v>1029231.511578948</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>2373148.8</v>
@@ -23815,7 +23815,7 @@
         <v>124902.5684210528</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2697895.477894737</v>
+        <v>2572992.909473685</v>
       </c>
     </row>
     <row r="13">
@@ -23837,7 +23837,7 @@
         <v>14797.50321649486</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>532710.1157938145</v>
+        <v>508047.6104329897</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>584987.7320000001</v>
@@ -23852,7 +23852,7 @@
         <v>18092.4040824743</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>651326.5469690723</v>
+        <v>621172.5401649487</v>
       </c>
     </row>
     <row r="14">
@@ -23872,7 +23872,7 @@
         <v>1903248.661585987</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>100890281.3582729</v>
+        <v>96219434.99909355</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>103910327.142</v>
@@ -23885,7 +23885,7 @@
         <v>2203243.760462701</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>114602656.5746597</v>
+        <v>109296978.0295366</v>
       </c>
     </row>
   </sheetData>
@@ -23944,7 +23944,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -23969,7 +23969,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -23992,7 +23992,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>890022.1680000001</v>
@@ -24007,7 +24007,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
     </row>
     <row r="3">
@@ -24029,7 +24029,7 @@
         <v>290687.0204081628</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>15697099.10204082</v>
+        <v>14970381.55102041</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>14352693.2</v>
@@ -24044,7 +24044,7 @@
         <v>292912.106122449</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>15817253.73061225</v>
+        <v>15084973.46530612</v>
       </c>
     </row>
     <row r="4">
@@ -24073,7 +24073,7 @@
         <v>68817.32726530638</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>3716135.672326531</v>
+        <v>3544092.354163265</v>
       </c>
     </row>
     <row r="5">
@@ -24095,7 +24095,7 @@
         <v>56886.30612244923</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3071860.530612245</v>
+        <v>2929644.765306123</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>2787429</v>
@@ -24110,7 +24110,7 @@
         <v>56886.30612244923</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>3071860.530612245</v>
+        <v>2929644.765306123</v>
       </c>
     </row>
     <row r="6">
@@ -24132,7 +24132,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -24147,7 +24147,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -24169,7 +24169,7 @@
         <v>178186.8062448986</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>9622087.537224492</v>
+        <v>9176620.521612247</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>14757959.936</v>
@@ -24184,7 +24184,7 @@
         <v>301182.8558367342</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>16263874.21518368</v>
+        <v>15510917.07559184</v>
       </c>
     </row>
     <row r="8">
@@ -24206,7 +24206,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>113615.858</v>
@@ -24221,7 +24221,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
     </row>
     <row r="9">
@@ -24243,7 +24243,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>503994.418</v>
@@ -24258,7 +24258,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
     </row>
     <row r="10">
@@ -24280,7 +24280,7 @@
         <v>13884.98595918366</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>749789.2417959184</v>
+        <v>715076.7768979592</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>1019795.74</v>
@@ -24295,7 +24295,7 @@
         <v>20812.15795918368</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>1123856.529795918</v>
+        <v>1071826.134897959</v>
       </c>
     </row>
     <row r="11">
@@ -24317,7 +24317,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -24332,7 +24332,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -24354,7 +24354,7 @@
         <v>20687.87368421053</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>446858.0715789474</v>
+        <v>426170.1978947368</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>749034</v>
@@ -24369,7 +24369,7 @@
         <v>39422.84210526315</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>851533.3894736842</v>
+        <v>812110.5473684211</v>
       </c>
     </row>
     <row r="13">
@@ -24391,7 +24391,7 @@
         <v>7777.105855670117</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>279975.8108041238</v>
+        <v>267013.9677113402</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>278093.538</v>
@@ -24406,7 +24406,7 @@
         <v>8600.831072164932</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>309629.9185979381</v>
+        <v>295295.2001443299</v>
       </c>
     </row>
     <row r="14">
@@ -24426,7 +24426,7 @@
         <v>742005.3058664128</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>39258011.50401574</v>
+        <v>37440510.9714224</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>47709791.642</v>
@@ -24439,7 +24439,7 @@
         <v>1000731.103871301</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>52607364.56554101</v>
+        <v>50171838.42824745</v>
       </c>
     </row>
   </sheetData>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -24523,7 +24523,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -24546,7 +24546,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>890022.1680000001</v>
@@ -24561,7 +24561,7 @@
         <v>18163.71771428571</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>980840.7565714287</v>
+        <v>935431.4622857143</v>
       </c>
     </row>
     <row r="3">
@@ -24583,7 +24583,7 @@
         <v>581374.0408163257</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>31394198.20408163</v>
+        <v>29940763.10204082</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>28705386.4</v>
@@ -24598,7 +24598,7 @@
         <v>585824.2122448981</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>31634507.46122449</v>
+        <v>30169946.93061225</v>
       </c>
     </row>
     <row r="4">
@@ -24620,7 +24620,7 @@
         <v>132242.2463673474</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>7141081.303836735</v>
+        <v>6810475.687918368</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>6744098.072</v>
@@ -24635,7 +24635,7 @@
         <v>137634.6545306128</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>7432271.344653062</v>
+        <v>7088184.708326531</v>
       </c>
     </row>
     <row r="5">
@@ -24657,7 +24657,7 @@
         <v>56886.30612244923</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>3071860.530612245</v>
+        <v>2929644.765306123</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>5574858</v>
@@ -24672,7 +24672,7 @@
         <v>113772.6122448985</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>6143721.06122449</v>
+        <v>5859289.530612245</v>
       </c>
     </row>
     <row r="6">
@@ -24694,7 +24694,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -24709,7 +24709,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -24731,7 +24731,7 @@
         <v>148133.0757551026</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7999186.090775511</v>
+        <v>7628853.401387756</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10260287.378</v>
@@ -24746,7 +24746,7 @@
         <v>209393.619959183</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>11307255.47779592</v>
+        <v>10783771.42789796</v>
       </c>
     </row>
     <row r="8">
@@ -24768,7 +24768,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>113615.858</v>
@@ -24783,7 +24783,7 @@
         <v>2318.690979591833</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>125209.3128979592</v>
+        <v>119412.5854489796</v>
       </c>
     </row>
     <row r="9">
@@ -24805,7 +24805,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>503994.418</v>
@@ -24820,7 +24820,7 @@
         <v>10285.60036734695</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>555422.4198367348</v>
+        <v>529708.4189183674</v>
       </c>
     </row>
     <row r="10">
@@ -24842,7 +24842,7 @@
         <v>26769.35330612259</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1445545.078530613</v>
+        <v>1378621.695265306</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>2623396.624</v>
@@ -24857,7 +24857,7 @@
         <v>53538.70661224518</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>2891090.157061225</v>
+        <v>2757243.390530613</v>
       </c>
     </row>
     <row r="11">
@@ -24879,7 +24879,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -24894,7 +24894,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -24916,7 +24916,7 @@
         <v>30446.14736842108</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>657636.7831578949</v>
+        <v>627190.6357894738</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1290405.6</v>
@@ -24931,7 +24931,7 @@
         <v>67916.08421052643</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1466987.418947369</v>
+        <v>1399071.334736842</v>
       </c>
     </row>
     <row r="13">
@@ -24953,7 +24953,7 @@
         <v>8600.831072164932</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>309629.9185979381</v>
+        <v>295295.2001443299</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>331361.102</v>
@@ -24968,7 +24968,7 @@
         <v>10248.28150515462</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>368938.134185567</v>
+        <v>351857.6650103093</v>
       </c>
     </row>
     <row r="14">
@@ -24988,7 +24988,7 @@
         <v>1158347.208399773</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>61409479.11955174</v>
+        <v>58566447.67883177</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>65922530.36799999</v>
@@ -25001,7 +25001,7 @@
         <v>1390424.848695286</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>72697991.63403089</v>
+        <v>69332343.87319614</v>
       </c>
     </row>
   </sheetData>
@@ -25060,7 +25060,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Non_SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>Non_SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -25085,7 +25085,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>SD 고객 제시가(최초견적, 버퍼 8%p)</t>
+          <t>SD 고객 제시가(최초견적, 버퍼 3%p)</t>
         </is>
       </c>
     </row>
@@ -25108,7 +25108,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1366359.084</v>
@@ -25123,7 +25123,7 @@
         <v>27884.87926530605</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>1505783.480326531</v>
+        <v>1436071.282163265</v>
       </c>
     </row>
     <row r="3">
@@ -25145,7 +25145,7 @@
         <v>872061.0612244904</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>47091297.30612245</v>
+        <v>44911144.65306123</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>43058079.6</v>
@@ -25160,7 +25160,7 @@
         <v>878736.3183673471</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>47451761.19183674</v>
+        <v>45254920.39591837</v>
       </c>
     </row>
     <row r="4">
@@ -25182,7 +25182,7 @@
         <v>198363.3695510197</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>10711621.9557551</v>
+        <v>10215713.53187755</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>10116147.108</v>
@@ -25197,7 +25197,7 @@
         <v>206451.9817959182</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>11148407.01697959</v>
+        <v>10632277.06248979</v>
       </c>
     </row>
     <row r="5">
@@ -25219,7 +25219,7 @@
         <v>113772.6122448985</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6143721.06122449</v>
+        <v>5859289.530612245</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>8362287</v>
@@ -25234,7 +25234,7 @@
         <v>170658.9183673467</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>9215581.591836736</v>
+        <v>8788934.295918368</v>
       </c>
     </row>
     <row r="6">
@@ -25256,7 +25256,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>5141360.708</v>
@@ -25271,7 +25271,7 @@
         <v>104925.7287346944</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>5665989.35167347</v>
+        <v>5403675.029836735</v>
       </c>
     </row>
     <row r="7">
@@ -25293,7 +25293,7 @@
         <v>105380.0485714283</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>5690522.622857143</v>
+        <v>5427072.501428572</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>4985991.14</v>
@@ -25308,7 +25308,7 @@
         <v>101754.9212244898</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>5494765.746122449</v>
+        <v>5240378.443061224</v>
       </c>
     </row>
     <row r="8">
@@ -25330,7 +25330,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>141290.422</v>
@@ -25345,7 +25345,7 @@
         <v>2883.478000000003</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>155707.812</v>
+        <v>148499.117</v>
       </c>
     </row>
     <row r="9">
@@ -25367,7 +25367,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>786592.324</v>
@@ -25382,7 +25382,7 @@
         <v>16052.90457142855</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>866856.8468571429</v>
+        <v>826724.5854285714</v>
       </c>
     </row>
     <row r="10">
@@ -25404,7 +25404,7 @@
         <v>39003.63902040827</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>2106196.507102041</v>
+        <v>2008687.409551021</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>3822356.624</v>
@@ -25419,7 +25419,7 @@
         <v>78007.27804081654</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>4212393.014204082</v>
+        <v>4017374.819102041</v>
       </c>
     </row>
     <row r="11">
@@ -25441,7 +25441,7 @@
         <v>38201.46979591832</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2062879.368979592</v>
+        <v>1967375.694489796</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>3743744.04</v>
@@ -25456,7 +25456,7 @@
         <v>76402.93959183665</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>4125758.737959184</v>
+        <v>3934751.388979592</v>
       </c>
     </row>
     <row r="12">
@@ -25478,7 +25478,7 @@
         <v>40204.42105263157</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>868415.4947368422</v>
+        <v>828211.0736842107</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1831777.2</v>
@@ -25493,7 +25493,7 @@
         <v>96409.32631578948</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2082441.448421052</v>
+        <v>1986032.122105263</v>
       </c>
     </row>
     <row r="13">
@@ -25515,7 +25515,7 @@
         <v>13973.77799999999</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>503056.008</v>
+        <v>479766.378</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>531720.1680000001</v>
@@ -25530,7 +25530,7 @@
         <v>16444.95364948455</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>592018.3313814434</v>
+        <v>564610.0752989692</v>
       </c>
     </row>
     <row r="14">
@@ -25550,7 +25550,7 @@
         <v>1572707.390032217</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>83372047.8156348</v>
+        <v>79512230.78713319</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>83887705.41800001</v>
@@ -25563,7 +25563,7 @@
         <v>1776613.627924457</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>92517464.56959842</v>
+        <v>88234248.61730218</v>
       </c>
     </row>
   </sheetData>

--- a/output/15_매입판매가_제시안.xlsx
+++ b/output/15_매입판매가_제시안.xlsx
@@ -1554,7 +1554,7 @@
   <dimension ref="A1:I494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
@@ -1732,7 +1732,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R493</t>
+          <t>K9213024</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R492</t>
+          <t>K9213023</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R495</t>
+          <t>K9213026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1849,7 +1849,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R494</t>
+          <t>K9213025</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R497</t>
+          <t>K9213028</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1927,7 +1927,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R496</t>
+          <t>K9213027</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R499</t>
+          <t>K9213030</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R498</t>
+          <t>K9213029</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -6451,7 +6451,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R502</t>
+          <t>K9213033</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6490,7 +6490,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R500</t>
+          <t>K9213031</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6529,7 +6529,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R501</t>
+          <t>K9213032</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R485</t>
+          <t>K9213016</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
@@ -16045,7 +16045,7 @@
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R484</t>
+          <t>K9212896</t>
         </is>
       </c>
       <c r="B372" s="2" t="inlineStr">
@@ -16084,7 +16084,7 @@
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R487</t>
+          <t>K9213018</t>
         </is>
       </c>
       <c r="B373" s="2" t="inlineStr">
@@ -16123,7 +16123,7 @@
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R486</t>
+          <t>K9213017</t>
         </is>
       </c>
       <c r="B374" s="2" t="inlineStr">
@@ -16162,7 +16162,7 @@
     <row r="375">
       <c r="A375" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R489</t>
+          <t>K9213020</t>
         </is>
       </c>
       <c r="B375" s="2" t="inlineStr">
@@ -16201,7 +16201,7 @@
     <row r="376">
       <c r="A376" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R488</t>
+          <t>K9213019</t>
         </is>
       </c>
       <c r="B376" s="2" t="inlineStr">
@@ -16240,7 +16240,7 @@
     <row r="377">
       <c r="A377" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R491</t>
+          <t>K9213022</t>
         </is>
       </c>
       <c r="B377" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
     <row r="378">
       <c r="A378" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R490</t>
+          <t>K9213021</t>
         </is>
       </c>
       <c r="B378" s="2" t="inlineStr">

--- a/output/15_매입판매가_제시안.xlsx
+++ b/output/15_매입판매가_제시안.xlsx
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -129,9 +129,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -695,7 +692,7 @@
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1136,38 +1133,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>949291.2000000001</v>
+        <v>910936</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>958880</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9588.79999999993</v>
+        <v>47944</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>987646.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2373148.8</v>
+        <v>2277256</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>2397120</v>
+      <c r="I12" s="3" t="n">
+        <v>2397111.578947369</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>23971.19999999972</v>
+        <v>119855.5789473685</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2469033.6</v>
+        <v>2469024.92631579</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -1204,36 +1201,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>91509301.57800002</v>
+        <v>91470946.37800002</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>93372087.01946141</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1862785.441461384</v>
+        <v>1901140.641461387</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>96173249.63004522</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>103905950.198</v>
+        <v>103810057.398</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>106008173.2646539</v>
+        <v>106008164.8436013</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2102223.066653907</v>
+        <v>2198107.44560127</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>109188418.4625935</v>
+        <v>109188409.7889093</v>
       </c>
     </row>
   </sheetData>
@@ -1316,28 +1313,28 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="C2" s="3" t="n">
         <v>36333293.1781822</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>725287.8321821988</v>
+        <v>741169.4321822003</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>37423291.97352767</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>47710885.87800001</v>
+        <v>47680619.87800001</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>48679782.47111298</v>
+        <v>48679780.36584982</v>
       </c>
       <c r="H2" s="3" t="n">
-        <v>968896.5931129754</v>
+        <v>999160.4878498167</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>50140175.94524637</v>
+        <v>50140173.77682532</v>
       </c>
     </row>
     <row r="3">
@@ -1347,28 +1344,28 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>55704470.07799999</v>
+        <v>55681097.278</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>56838259.00172523</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>1133788.923725232</v>
+        <v>1157161.72372523</v>
       </c>
       <c r="E3" s="3" t="n">
         <v>58543406.77177699</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>65924718.84</v>
+        <v>65872577.23999999</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>67260306.66717862</v>
+        <v>67260302.4566523</v>
       </c>
       <c r="H3" s="3" t="n">
-        <v>1335587.82717862</v>
+        <v>1387725.216652304</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>69278115.86719398</v>
+        <v>69278111.53035188</v>
       </c>
     </row>
     <row r="4">
@@ -1378,28 +1375,28 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>75626915.888</v>
+        <v>75596051.888</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>77167201.85102041</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>1540285.963020414</v>
+        <v>1571149.963020414</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>79482217.90655102</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>83890988.12600002</v>
+        <v>83816970.92600001</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>85589762.22164948</v>
+        <v>85589755.90586001</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>1698774.095649466</v>
+        <v>1772784.979859993</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>88157455.08829896</v>
+        <v>88157448.5830358</v>
       </c>
     </row>
     <row r="5">
@@ -1409,28 +1406,28 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>91513678.52200001</v>
+        <v>91475323.32200001</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>93376553.28884916</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>1862874.766849145</v>
+        <v>1901229.966849148</v>
       </c>
       <c r="E5" s="3" t="n">
         <v>96177849.88751461</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>103910327.142</v>
+        <v>103814434.342</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>106012639.5340417</v>
+        <v>106012631.112989</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>2102312.392041653</v>
+        <v>2198196.770989016</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>109193018.7200629</v>
+        <v>109193010.0463787</v>
       </c>
     </row>
     <row r="6">
@@ -1440,28 +1437,28 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>36333293.1781822</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>725287.8321821988</v>
+        <v>741169.4321822003</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>37423291.97352767</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>47709791.642</v>
+        <v>47679525.642</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>48678665.90376604</v>
+        <v>48678663.79850288</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>968874.2617660388</v>
+        <v>999138.1565028802</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>50139025.88087902</v>
+        <v>50139023.71245797</v>
       </c>
     </row>
     <row r="7">
@@ -1471,28 +1468,28 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>55702281.606</v>
+        <v>55678908.806</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>56836025.86703135</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1133744.261031352</v>
+        <v>1157117.061031349</v>
       </c>
       <c r="E7" s="3" t="n">
         <v>58541106.6430423</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>65922530.36799999</v>
+        <v>65870388.76799999</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>67258073.53248474</v>
+        <v>67258069.32195842</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1335543.164484747</v>
+        <v>1387680.553958431</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>69275815.73845929</v>
+        <v>69275811.40161718</v>
       </c>
     </row>
     <row r="8">
@@ -1502,28 +1499,28 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>75623633.18000001</v>
+        <v>75592769.18000001</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>77163852.14897959</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>1540218.968979582</v>
+        <v>1571082.968979582</v>
       </c>
       <c r="E8" s="3" t="n">
         <v>79478767.71344897</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>83887705.41800001</v>
+        <v>83813688.21800001</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>85586412.51960868</v>
+        <v>85586406.2038192</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1698707.101608664</v>
+        <v>1772717.985819191</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>88154004.89519693</v>
+        <v>88153998.38993376</v>
       </c>
     </row>
     <row r="9">
@@ -1533,28 +1530,28 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>91509301.57800002</v>
+        <v>91470946.37800002</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>93372087.01946141</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>1862785.441461384</v>
+        <v>1901140.641461387</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>96173249.63004522</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>103905950.198</v>
+        <v>103810057.398</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>106008173.2646539</v>
+        <v>106008164.8436013</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>2102223.066653907</v>
+        <v>2198107.44560127</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>109188418.4625935</v>
+        <v>109188409.7889093</v>
       </c>
     </row>
   </sheetData>
@@ -1581,7 +1578,7 @@
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="39" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1648,16 +1645,16 @@
         </is>
       </c>
       <c r="C2" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="D2" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="E2" s="10" t="n">
-        <v>43070</v>
+      <c r="E2" s="3" t="n">
+        <v>43069.47368421053</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>44362.1</v>
+        <v>44361.55789473684</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1669,16 +1666,12 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1692,12 +1685,12 @@
         </is>
       </c>
       <c r="C3" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="D3" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="E3" s="10" t="n">
+      <c r="E3" s="3" t="n">
         <v>26220</v>
       </c>
       <c r="F3" s="3" t="n">
@@ -1713,16 +1706,12 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1736,12 +1725,12 @@
         </is>
       </c>
       <c r="C4" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="E4" s="10" t="n">
+      <c r="E4" s="3" t="n">
         <v>46820</v>
       </c>
       <c r="F4" s="3" t="n">
@@ -1757,16 +1746,12 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1801,7 +1786,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1841,7 +1826,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1881,7 +1866,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1921,7 +1906,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1961,7 +1946,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2001,7 +1986,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="I10" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2041,7 +2026,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2081,7 +2066,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I12" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2121,7 +2106,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2161,7 +2146,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2201,7 +2186,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2241,7 +2226,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2281,7 +2266,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2321,7 +2306,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="I18" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2361,7 +2346,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2401,7 +2386,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2441,7 +2426,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2481,7 +2466,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I22" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2521,7 +2506,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2561,7 +2546,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2601,7 +2586,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2641,7 +2626,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2681,7 +2666,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2721,7 +2706,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="I28" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2761,7 +2746,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2801,7 +2786,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2841,7 +2826,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2881,7 +2866,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2921,7 +2906,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2961,7 +2946,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
+      <c r="I34" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3001,7 +2986,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3041,7 +3026,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="I36" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3081,7 +3066,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3121,7 +3106,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3161,7 +3146,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3201,7 +3186,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I40" s="9" t="inlineStr">
+      <c r="I40" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3241,7 +3226,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3281,7 +3266,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="I42" s="8" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3321,7 +3306,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3361,7 +3346,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3401,7 +3386,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3441,7 +3426,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3481,7 +3466,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3521,7 +3506,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="I48" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3561,7 +3546,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="I49" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3601,7 +3586,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="I50" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3641,7 +3626,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="I51" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3681,7 +3666,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="I52" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3721,7 +3706,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="I53" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3761,7 +3746,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="I54" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3801,7 +3786,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="I55" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3841,7 +3826,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="I56" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3881,7 +3866,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="I57" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3921,7 +3906,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="I58" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3961,7 +3946,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="I59" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4001,7 +3986,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="I60" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4041,7 +4026,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="I61" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4081,7 +4066,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="I62" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4121,7 +4106,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="I63" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4161,7 +4146,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="I64" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4201,7 +4186,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="I65" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4241,7 +4226,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="I66" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4281,7 +4266,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="I67" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4321,7 +4306,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="I68" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4361,7 +4346,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4401,7 +4386,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4441,7 +4426,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4481,7 +4466,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4521,7 +4506,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="I73" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4561,7 +4546,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="I74" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4601,7 +4586,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="I75" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4641,7 +4626,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="I76" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4681,7 +4666,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="I77" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4721,7 +4706,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="I78" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4761,7 +4746,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="I79" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4780,16 +4765,16 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="D80" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E80" s="10" t="n">
-        <v>8631560</v>
+      <c r="E80" s="3" t="n">
+        <v>8631559.793814434</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>8890506.800000001</v>
+        <v>8890506.587628867</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -4801,16 +4786,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J80" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I80" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4824,16 +4805,16 @@
         </is>
       </c>
       <c r="C81" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="D81" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E81" s="10" t="n">
-        <v>8631560</v>
+      <c r="E81" s="3" t="n">
+        <v>8631559.793814434</v>
       </c>
       <c r="F81" s="3" t="n">
-        <v>8890506.800000001</v>
+        <v>8890506.587628867</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4826,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I81" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J81" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I81" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4868,16 +4845,16 @@
         </is>
       </c>
       <c r="C82" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="D82" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E82" s="10" t="n">
-        <v>10927020</v>
+      <c r="E82" s="3" t="n">
+        <v>10927019.58762887</v>
       </c>
       <c r="F82" s="3" t="n">
-        <v>11254830.6</v>
+        <v>11254830.17525773</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -4889,16 +4866,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J82" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I82" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4912,16 +4885,16 @@
         </is>
       </c>
       <c r="C83" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="D83" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E83" s="10" t="n">
-        <v>10927020</v>
+      <c r="E83" s="3" t="n">
+        <v>10927019.58762887</v>
       </c>
       <c r="F83" s="3" t="n">
-        <v>11254830.6</v>
+        <v>11254830.17525773</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -4933,16 +4906,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I83" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J83" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I83" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4956,16 +4925,16 @@
         </is>
       </c>
       <c r="C84" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="D84" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E84" s="10" t="n">
-        <v>14163130</v>
+      <c r="E84" s="3" t="n">
+        <v>14163129.89690722</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>14588023.9</v>
+        <v>14588023.79381444</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -4977,16 +4946,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I84" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -5000,16 +4965,16 @@
         </is>
       </c>
       <c r="C85" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="D85" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E85" s="10" t="n">
-        <v>14163130</v>
+      <c r="E85" s="3" t="n">
+        <v>14163129.89690722</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>14588023.9</v>
+        <v>14588023.79381444</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -5021,16 +4986,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I85" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J85" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I85" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5044,12 +5005,12 @@
         </is>
       </c>
       <c r="C86" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="D86" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E86" s="10" t="n">
+      <c r="E86" s="9" t="n">
         <v>3494770</v>
       </c>
       <c r="F86" s="3" t="n">
@@ -5065,12 +5026,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J86" s="8" t="inlineStr">
+      <c r="I86" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J86" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5088,12 +5049,12 @@
         </is>
       </c>
       <c r="C87" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="D87" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E87" s="10" t="n">
+      <c r="E87" s="9" t="n">
         <v>3494770</v>
       </c>
       <c r="F87" s="3" t="n">
@@ -5109,12 +5070,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I87" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J87" s="8" t="inlineStr">
+      <c r="I87" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J87" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5132,16 +5093,16 @@
         </is>
       </c>
       <c r="C88" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="D88" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E88" s="10" t="n">
-        <v>4919190</v>
+      <c r="E88" s="3" t="n">
+        <v>4919189.69072165</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>5066765.7</v>
+        <v>5066765.381443299</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5153,16 +5114,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I88" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J88" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I88" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5176,16 +5133,16 @@
         </is>
       </c>
       <c r="C89" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="D89" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E89" s="10" t="n">
-        <v>4919190</v>
+      <c r="E89" s="3" t="n">
+        <v>4919189.69072165</v>
       </c>
       <c r="F89" s="3" t="n">
-        <v>5066765.7</v>
+        <v>5066765.381443299</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5197,16 +5154,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5220,12 +5173,12 @@
         </is>
       </c>
       <c r="C90" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="D90" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E90" s="10" t="n">
+      <c r="E90" s="9" t="n">
         <v>6542350</v>
       </c>
       <c r="F90" s="3" t="n">
@@ -5241,12 +5194,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J90" s="8" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J90" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5264,12 +5217,12 @@
         </is>
       </c>
       <c r="C91" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="D91" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E91" s="10" t="n">
+      <c r="E91" s="9" t="n">
         <v>6542350</v>
       </c>
       <c r="F91" s="3" t="n">
@@ -5285,12 +5238,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J91" s="8" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J91" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5329,7 +5282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5369,7 +5322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5409,7 +5362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5449,7 +5402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5489,7 +5442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5529,7 +5482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="I97" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5569,7 +5522,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="I98" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5609,7 +5562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="I99" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5649,7 +5602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="I100" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5689,7 +5642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="I101" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5729,7 +5682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="I102" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5769,7 +5722,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="I103" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5809,7 +5762,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="I104" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5849,7 +5802,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="I105" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5889,7 +5842,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="I106" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5929,7 +5882,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="I107" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5969,7 +5922,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="I108" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6009,7 +5962,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="I109" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6049,7 +6002,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="I110" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6089,7 +6042,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I111" s="8" t="inlineStr">
+      <c r="I111" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6129,7 +6082,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="I112" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6169,7 +6122,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="I113" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6209,7 +6162,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="I114" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6249,7 +6202,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="I115" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6289,7 +6242,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="I116" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6329,7 +6282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I117" s="8" t="inlineStr">
+      <c r="I117" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6369,7 +6322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I118" s="8" t="inlineStr">
+      <c r="I118" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6409,7 +6362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="I119" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6449,7 +6402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="I120" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6489,7 +6442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="I121" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6529,7 +6482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="I122" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6569,7 +6522,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="I123" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6609,7 +6562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="I124" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6649,7 +6602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="I125" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6689,7 +6642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="I126" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6729,7 +6682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="I127" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6769,7 +6722,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="I128" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6809,7 +6762,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="I129" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6849,7 +6802,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="I130" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6889,7 +6842,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="I131" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6929,7 +6882,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="I132" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6969,7 +6922,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="I133" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7009,7 +6962,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="I134" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7049,7 +7002,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="I135" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7089,7 +7042,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="I136" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7129,7 +7082,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="I137" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7169,7 +7122,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="I138" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7209,7 +7162,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I139" s="8" t="inlineStr">
+      <c r="I139" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7249,7 +7202,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="I140" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7289,7 +7242,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="I141" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7329,7 +7282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="I142" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7369,7 +7322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="I143" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7409,7 +7362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="I144" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7449,7 +7402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="I145" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7489,7 +7442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="I146" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7529,7 +7482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I147" s="8" t="inlineStr">
+      <c r="I147" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7569,7 +7522,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I148" s="8" t="inlineStr">
+      <c r="I148" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7609,7 +7562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="I149" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7649,7 +7602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="I150" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7689,7 +7642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I151" s="8" t="inlineStr">
+      <c r="I151" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7729,7 +7682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I152" s="8" t="inlineStr">
+      <c r="I152" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7769,7 +7722,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="I153" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7809,7 +7762,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I154" s="8" t="inlineStr">
+      <c r="I154" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7849,7 +7802,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I155" s="8" t="inlineStr">
+      <c r="I155" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7889,7 +7842,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I156" s="8" t="inlineStr">
+      <c r="I156" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7929,7 +7882,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I157" s="8" t="inlineStr">
+      <c r="I157" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7969,7 +7922,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I158" s="8" t="inlineStr">
+      <c r="I158" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8009,7 +7962,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I159" s="8" t="inlineStr">
+      <c r="I159" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8049,7 +8002,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I160" s="8" t="inlineStr">
+      <c r="I160" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8089,7 +8042,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I161" s="8" t="inlineStr">
+      <c r="I161" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8129,7 +8082,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I162" s="8" t="inlineStr">
+      <c r="I162" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8169,7 +8122,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I163" s="8" t="inlineStr">
+      <c r="I163" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8209,7 +8162,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I164" s="8" t="inlineStr">
+      <c r="I164" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8249,7 +8202,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I165" s="8" t="inlineStr">
+      <c r="I165" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8289,7 +8242,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I166" s="8" t="inlineStr">
+      <c r="I166" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8329,7 +8282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="I167" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8369,7 +8322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I168" s="8" t="inlineStr">
+      <c r="I168" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8409,7 +8362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I169" s="8" t="inlineStr">
+      <c r="I169" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8449,7 +8402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I170" s="8" t="inlineStr">
+      <c r="I170" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8489,7 +8442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I171" s="8" t="inlineStr">
+      <c r="I171" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8529,7 +8482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="I172" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8569,7 +8522,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I173" s="8" t="inlineStr">
+      <c r="I173" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8609,7 +8562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="I174" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8649,7 +8602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I175" s="8" t="inlineStr">
+      <c r="I175" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8689,7 +8642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I176" s="8" t="inlineStr">
+      <c r="I176" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8729,7 +8682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I177" s="8" t="inlineStr">
+      <c r="I177" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8769,7 +8722,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I178" s="8" t="inlineStr">
+      <c r="I178" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8809,7 +8762,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="I179" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8849,7 +8802,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I180" s="8" t="inlineStr">
+      <c r="I180" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8889,7 +8842,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I181" s="8" t="inlineStr">
+      <c r="I181" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8929,7 +8882,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="I182" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8969,7 +8922,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I183" s="8" t="inlineStr">
+      <c r="I183" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9009,7 +8962,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I184" s="8" t="inlineStr">
+      <c r="I184" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9049,7 +9002,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I185" s="8" t="inlineStr">
+      <c r="I185" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9089,7 +9042,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I186" s="8" t="inlineStr">
+      <c r="I186" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9129,7 +9082,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I187" s="8" t="inlineStr">
+      <c r="I187" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9169,7 +9122,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="I188" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9209,7 +9162,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I189" s="8" t="inlineStr">
+      <c r="I189" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9249,7 +9202,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I190" s="8" t="inlineStr">
+      <c r="I190" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9289,7 +9242,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I191" s="8" t="inlineStr">
+      <c r="I191" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9329,7 +9282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I192" s="8" t="inlineStr">
+      <c r="I192" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9369,7 +9322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I193" s="8" t="inlineStr">
+      <c r="I193" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9409,7 +9362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I194" s="8" t="inlineStr">
+      <c r="I194" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9449,7 +9402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I195" s="8" t="inlineStr">
+      <c r="I195" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9489,7 +9442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I196" s="8" t="inlineStr">
+      <c r="I196" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9529,7 +9482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I197" s="8" t="inlineStr">
+      <c r="I197" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9569,7 +9522,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I198" s="8" t="inlineStr">
+      <c r="I198" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9609,7 +9562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I199" s="8" t="inlineStr">
+      <c r="I199" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9649,7 +9602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I200" s="8" t="inlineStr">
+      <c r="I200" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9689,7 +9642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I201" s="8" t="inlineStr">
+      <c r="I201" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9729,7 +9682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I202" s="8" t="inlineStr">
+      <c r="I202" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9769,7 +9722,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I203" s="8" t="inlineStr">
+      <c r="I203" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9809,7 +9762,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I204" s="8" t="inlineStr">
+      <c r="I204" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9849,7 +9802,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I205" s="8" t="inlineStr">
+      <c r="I205" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9889,7 +9842,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I206" s="8" t="inlineStr">
+      <c r="I206" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9929,7 +9882,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I207" s="8" t="inlineStr">
+      <c r="I207" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9969,7 +9922,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I208" s="8" t="inlineStr">
+      <c r="I208" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10009,7 +9962,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I209" s="8" t="inlineStr">
+      <c r="I209" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10049,7 +10002,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I210" s="8" t="inlineStr">
+      <c r="I210" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10089,7 +10042,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I211" s="8" t="inlineStr">
+      <c r="I211" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10129,7 +10082,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I212" s="8" t="inlineStr">
+      <c r="I212" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10169,7 +10122,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I213" s="8" t="inlineStr">
+      <c r="I213" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10209,7 +10162,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I214" s="8" t="inlineStr">
+      <c r="I214" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10249,7 +10202,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I215" s="8" t="inlineStr">
+      <c r="I215" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10289,7 +10242,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I216" s="8" t="inlineStr">
+      <c r="I216" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10329,7 +10282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I217" s="8" t="inlineStr">
+      <c r="I217" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10369,7 +10322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I218" s="8" t="inlineStr">
+      <c r="I218" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10409,7 +10362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I219" s="8" t="inlineStr">
+      <c r="I219" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10449,7 +10402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I220" s="8" t="inlineStr">
+      <c r="I220" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10489,7 +10442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I221" s="8" t="inlineStr">
+      <c r="I221" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10529,7 +10482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I222" s="8" t="inlineStr">
+      <c r="I222" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10569,7 +10522,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I223" s="8" t="inlineStr">
+      <c r="I223" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10609,7 +10562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I224" s="8" t="inlineStr">
+      <c r="I224" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10649,7 +10602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I225" s="8" t="inlineStr">
+      <c r="I225" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10689,7 +10642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I226" s="8" t="inlineStr">
+      <c r="I226" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10729,7 +10682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I227" s="8" t="inlineStr">
+      <c r="I227" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10769,7 +10722,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I228" s="8" t="inlineStr">
+      <c r="I228" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10809,7 +10762,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I229" s="8" t="inlineStr">
+      <c r="I229" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10849,7 +10802,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I230" s="8" t="inlineStr">
+      <c r="I230" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10889,7 +10842,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I231" s="8" t="inlineStr">
+      <c r="I231" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10929,7 +10882,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I232" s="8" t="inlineStr">
+      <c r="I232" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10969,7 +10922,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I233" s="8" t="inlineStr">
+      <c r="I233" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11009,7 +10962,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I234" s="8" t="inlineStr">
+      <c r="I234" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11049,7 +11002,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I235" s="8" t="inlineStr">
+      <c r="I235" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11089,7 +11042,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I236" s="8" t="inlineStr">
+      <c r="I236" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11129,7 +11082,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I237" s="8" t="inlineStr">
+      <c r="I237" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11169,7 +11122,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I238" s="8" t="inlineStr">
+      <c r="I238" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11209,7 +11162,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I239" s="8" t="inlineStr">
+      <c r="I239" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11249,7 +11202,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I240" s="8" t="inlineStr">
+      <c r="I240" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11289,7 +11242,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I241" s="8" t="inlineStr">
+      <c r="I241" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11329,7 +11282,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I242" s="8" t="inlineStr">
+      <c r="I242" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11369,7 +11322,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I243" s="8" t="inlineStr">
+      <c r="I243" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11409,7 +11362,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I244" s="8" t="inlineStr">
+      <c r="I244" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11449,7 +11402,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I245" s="8" t="inlineStr">
+      <c r="I245" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11489,7 +11442,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I246" s="8" t="inlineStr">
+      <c r="I246" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11529,7 +11482,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I247" s="8" t="inlineStr">
+      <c r="I247" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11548,16 +11501,16 @@
         </is>
       </c>
       <c r="C248" s="3" t="n">
-        <v>634418</v>
+        <v>467968</v>
       </c>
       <c r="D248" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="E248" s="3" t="n">
-        <v>548550</v>
+        <v>477518.3673469388</v>
       </c>
       <c r="F248" s="3" t="n">
-        <v>565006.5</v>
+        <v>491843.9183673469</v>
       </c>
       <c r="G248" s="2" t="inlineStr">
         <is>
@@ -11569,16 +11522,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I248" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J248" s="11" t="inlineStr">
-        <is>
-          <t>데이터 이상치(할인 후 가격이 정가보다 높음 - 공급사 확인 필요)</t>
-        </is>
-      </c>
+      <c r="I248" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="2" t="inlineStr">
@@ -11613,7 +11562,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I249" s="8" t="inlineStr">
+      <c r="I249" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11653,7 +11602,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I250" s="8" t="inlineStr">
+      <c r="I250" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11693,7 +11642,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I251" s="8" t="inlineStr">
+      <c r="I251" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11733,7 +11682,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I252" s="8" t="inlineStr">
+      <c r="I252" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11752,12 +11701,12 @@
         </is>
       </c>
       <c r="C253" s="3" t="n">
-        <v>2963892.4</v>
+        <v>2933649</v>
       </c>
       <c r="D253" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E253" s="10" t="n">
+      <c r="E253" s="9" t="n">
         <v>3024380</v>
       </c>
       <c r="F253" s="3" t="n">
@@ -11773,12 +11722,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I253" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J253" s="8" t="inlineStr">
+      <c r="I253" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J253" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -11796,12 +11745,12 @@
         </is>
       </c>
       <c r="C254" s="3" t="n">
-        <v>2963892.4</v>
+        <v>2933649</v>
       </c>
       <c r="D254" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E254" s="10" t="n">
+      <c r="E254" s="9" t="n">
         <v>3024380</v>
       </c>
       <c r="F254" s="3" t="n">
@@ -11817,12 +11766,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I254" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J254" s="8" t="inlineStr">
+      <c r="I254" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J254" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -11840,16 +11789,16 @@
         </is>
       </c>
       <c r="C255" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="D255" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E255" s="10" t="n">
-        <v>5343190</v>
+      <c r="E255" s="3" t="n">
+        <v>5343189.69072165</v>
       </c>
       <c r="F255" s="3" t="n">
-        <v>5503485.7</v>
+        <v>5503485.381443299</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -11861,16 +11810,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I255" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J255" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I255" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -11884,16 +11829,16 @@
         </is>
       </c>
       <c r="C256" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="D256" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E256" s="10" t="n">
-        <v>5343190</v>
+      <c r="E256" s="3" t="n">
+        <v>5343189.69072165</v>
       </c>
       <c r="F256" s="3" t="n">
-        <v>5503485.7</v>
+        <v>5503485.381443299</v>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
@@ -11905,16 +11850,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I256" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J256" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I256" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -11949,7 +11890,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I257" s="8" t="inlineStr">
+      <c r="I257" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11989,7 +11930,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I258" s="8" t="inlineStr">
+      <c r="I258" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12029,7 +11970,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I259" s="8" t="inlineStr">
+      <c r="I259" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12069,7 +12010,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I260" s="8" t="inlineStr">
+      <c r="I260" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12109,7 +12050,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I261" s="8" t="inlineStr">
+      <c r="I261" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12149,7 +12090,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I262" s="8" t="inlineStr">
+      <c r="I262" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12189,7 +12130,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I263" s="8" t="inlineStr">
+      <c r="I263" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12229,7 +12170,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I264" s="8" t="inlineStr">
+      <c r="I264" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12269,7 +12210,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I265" s="8" t="inlineStr">
+      <c r="I265" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12309,7 +12250,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I266" s="8" t="inlineStr">
+      <c r="I266" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12349,7 +12290,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I267" s="8" t="inlineStr">
+      <c r="I267" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12389,7 +12330,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I268" s="8" t="inlineStr">
+      <c r="I268" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12429,7 +12370,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I269" s="8" t="inlineStr">
+      <c r="I269" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12469,7 +12410,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I270" s="8" t="inlineStr">
+      <c r="I270" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12509,7 +12450,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I271" s="8" t="inlineStr">
+      <c r="I271" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12549,7 +12490,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I272" s="8" t="inlineStr">
+      <c r="I272" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12589,7 +12530,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I273" s="8" t="inlineStr">
+      <c r="I273" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12624,12 +12565,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H274" s="11" t="inlineStr">
+      <c r="H274" s="10" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I274" s="8" t="inlineStr">
+      <c r="I274" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12664,12 +12605,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H275" s="11" t="inlineStr">
+      <c r="H275" s="10" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I275" s="8" t="inlineStr">
+      <c r="I275" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12704,12 +12645,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H276" s="11" t="inlineStr">
+      <c r="H276" s="10" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I276" s="8" t="inlineStr">
+      <c r="I276" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12744,12 +12685,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H277" s="11" t="inlineStr">
+      <c r="H277" s="10" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I277" s="8" t="inlineStr">
+      <c r="I277" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12784,12 +12725,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H278" s="11" t="inlineStr">
+      <c r="H278" s="10" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I278" s="8" t="inlineStr">
+      <c r="I278" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12824,12 +12765,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H279" s="11" t="inlineStr">
+      <c r="H279" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I279" s="8" t="inlineStr">
+      <c r="I279" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12864,12 +12805,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H280" s="11" t="inlineStr">
+      <c r="H280" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I280" s="8" t="inlineStr">
+      <c r="I280" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12904,12 +12845,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H281" s="11" t="inlineStr">
+      <c r="H281" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I281" s="8" t="inlineStr">
+      <c r="I281" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12944,12 +12885,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H282" s="11" t="inlineStr">
+      <c r="H282" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I282" s="8" t="inlineStr">
+      <c r="I282" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12984,12 +12925,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H283" s="11" t="inlineStr">
+      <c r="H283" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I283" s="8" t="inlineStr">
+      <c r="I283" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13024,12 +12965,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H284" s="11" t="inlineStr">
+      <c r="H284" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I284" s="8" t="inlineStr">
+      <c r="I284" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13064,12 +13005,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H285" s="11" t="inlineStr">
+      <c r="H285" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I285" s="8" t="inlineStr">
+      <c r="I285" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13104,12 +13045,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H286" s="11" t="inlineStr">
+      <c r="H286" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I286" s="8" t="inlineStr">
+      <c r="I286" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13144,12 +13085,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H287" s="11" t="inlineStr">
+      <c r="H287" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I287" s="8" t="inlineStr">
+      <c r="I287" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13184,12 +13125,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H288" s="11" t="inlineStr">
+      <c r="H288" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I288" s="8" t="inlineStr">
+      <c r="I288" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13224,12 +13165,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H289" s="11" t="inlineStr">
+      <c r="H289" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I289" s="8" t="inlineStr">
+      <c r="I289" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13264,12 +13205,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H290" s="11" t="inlineStr">
+      <c r="H290" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I290" s="8" t="inlineStr">
+      <c r="I290" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13304,12 +13245,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H291" s="11" t="inlineStr">
+      <c r="H291" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I291" s="8" t="inlineStr">
+      <c r="I291" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13344,12 +13285,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H292" s="11" t="inlineStr">
+      <c r="H292" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I292" s="8" t="inlineStr">
+      <c r="I292" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13384,12 +13325,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H293" s="11" t="inlineStr">
+      <c r="H293" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I293" s="8" t="inlineStr">
+      <c r="I293" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13424,12 +13365,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H294" s="11" t="inlineStr">
+      <c r="H294" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I294" s="8" t="inlineStr">
+      <c r="I294" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13464,12 +13405,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H295" s="11" t="inlineStr">
+      <c r="H295" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I295" s="8" t="inlineStr">
+      <c r="I295" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13504,12 +13445,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H296" s="11" t="inlineStr">
+      <c r="H296" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I296" s="8" t="inlineStr">
+      <c r="I296" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13544,12 +13485,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H297" s="11" t="inlineStr">
+      <c r="H297" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I297" s="8" t="inlineStr">
+      <c r="I297" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13584,12 +13525,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H298" s="11" t="inlineStr">
+      <c r="H298" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I298" s="8" t="inlineStr">
+      <c r="I298" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13624,12 +13565,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H299" s="11" t="inlineStr">
+      <c r="H299" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I299" s="8" t="inlineStr">
+      <c r="I299" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13664,12 +13605,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H300" s="11" t="inlineStr">
+      <c r="H300" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I300" s="8" t="inlineStr">
+      <c r="I300" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13704,12 +13645,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H301" s="11" t="inlineStr">
+      <c r="H301" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I301" s="8" t="inlineStr">
+      <c r="I301" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13744,12 +13685,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H302" s="11" t="inlineStr">
+      <c r="H302" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I302" s="8" t="inlineStr">
+      <c r="I302" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13784,12 +13725,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H303" s="11" t="inlineStr">
+      <c r="H303" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I303" s="8" t="inlineStr">
+      <c r="I303" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13824,12 +13765,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H304" s="11" t="inlineStr">
+      <c r="H304" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I304" s="8" t="inlineStr">
+      <c r="I304" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13864,12 +13805,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H305" s="11" t="inlineStr">
+      <c r="H305" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I305" s="8" t="inlineStr">
+      <c r="I305" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13904,12 +13845,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H306" s="11" t="inlineStr">
+      <c r="H306" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I306" s="8" t="inlineStr">
+      <c r="I306" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13944,12 +13885,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H307" s="11" t="inlineStr">
+      <c r="H307" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I307" s="8" t="inlineStr">
+      <c r="I307" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13984,12 +13925,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H308" s="11" t="inlineStr">
+      <c r="H308" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I308" s="8" t="inlineStr">
+      <c r="I308" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14024,12 +13965,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H309" s="11" t="inlineStr">
+      <c r="H309" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I309" s="8" t="inlineStr">
+      <c r="I309" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14064,12 +14005,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H310" s="11" t="inlineStr">
+      <c r="H310" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I310" s="8" t="inlineStr">
+      <c r="I310" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14104,12 +14045,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H311" s="11" t="inlineStr">
+      <c r="H311" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I311" s="8" t="inlineStr">
+      <c r="I311" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14144,12 +14085,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H312" s="11" t="inlineStr">
+      <c r="H312" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I312" s="8" t="inlineStr">
+      <c r="I312" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14184,12 +14125,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H313" s="11" t="inlineStr">
+      <c r="H313" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I313" s="8" t="inlineStr">
+      <c r="I313" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14224,12 +14165,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H314" s="11" t="inlineStr">
+      <c r="H314" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I314" s="8" t="inlineStr">
+      <c r="I314" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14264,12 +14205,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H315" s="11" t="inlineStr">
+      <c r="H315" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I315" s="8" t="inlineStr">
+      <c r="I315" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14304,12 +14245,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H316" s="11" t="inlineStr">
+      <c r="H316" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I316" s="8" t="inlineStr">
+      <c r="I316" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14344,12 +14285,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H317" s="11" t="inlineStr">
+      <c r="H317" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I317" s="8" t="inlineStr">
+      <c r="I317" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14384,12 +14325,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H318" s="11" t="inlineStr">
+      <c r="H318" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I318" s="8" t="inlineStr">
+      <c r="I318" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14424,12 +14365,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H319" s="11" t="inlineStr">
+      <c r="H319" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I319" s="8" t="inlineStr">
+      <c r="I319" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14464,12 +14405,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H320" s="11" t="inlineStr">
+      <c r="H320" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I320" s="8" t="inlineStr">
+      <c r="I320" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14504,12 +14445,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H321" s="11" t="inlineStr">
+      <c r="H321" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I321" s="8" t="inlineStr">
+      <c r="I321" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14544,12 +14485,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H322" s="11" t="inlineStr">
+      <c r="H322" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I322" s="8" t="inlineStr">
+      <c r="I322" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14584,12 +14525,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H323" s="11" t="inlineStr">
+      <c r="H323" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I323" s="8" t="inlineStr">
+      <c r="I323" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14624,12 +14565,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H324" s="11" t="inlineStr">
+      <c r="H324" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I324" s="8" t="inlineStr">
+      <c r="I324" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14664,12 +14605,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H325" s="11" t="inlineStr">
+      <c r="H325" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I325" s="8" t="inlineStr">
+      <c r="I325" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14704,12 +14645,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H326" s="11" t="inlineStr">
+      <c r="H326" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I326" s="8" t="inlineStr">
+      <c r="I326" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14744,12 +14685,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H327" s="11" t="inlineStr">
+      <c r="H327" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I327" s="8" t="inlineStr">
+      <c r="I327" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14784,12 +14725,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H328" s="11" t="inlineStr">
+      <c r="H328" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I328" s="8" t="inlineStr">
+      <c r="I328" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14824,12 +14765,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H329" s="11" t="inlineStr">
+      <c r="H329" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I329" s="8" t="inlineStr">
+      <c r="I329" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14864,12 +14805,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H330" s="11" t="inlineStr">
+      <c r="H330" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I330" s="8" t="inlineStr">
+      <c r="I330" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14904,12 +14845,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H331" s="11" t="inlineStr">
+      <c r="H331" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I331" s="8" t="inlineStr">
+      <c r="I331" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14944,12 +14885,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H332" s="11" t="inlineStr">
+      <c r="H332" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I332" s="8" t="inlineStr">
+      <c r="I332" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14984,12 +14925,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H333" s="11" t="inlineStr">
+      <c r="H333" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I333" s="8" t="inlineStr">
+      <c r="I333" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15024,12 +14965,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H334" s="11" t="inlineStr">
+      <c r="H334" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I334" s="8" t="inlineStr">
+      <c r="I334" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15064,12 +15005,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H335" s="11" t="inlineStr">
+      <c r="H335" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I335" s="8" t="inlineStr">
+      <c r="I335" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15104,12 +15045,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H336" s="11" t="inlineStr">
+      <c r="H336" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I336" s="8" t="inlineStr">
+      <c r="I336" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15144,12 +15085,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H337" s="11" t="inlineStr">
+      <c r="H337" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I337" s="8" t="inlineStr">
+      <c r="I337" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15184,12 +15125,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H338" s="11" t="inlineStr">
+      <c r="H338" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I338" s="8" t="inlineStr">
+      <c r="I338" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15224,12 +15165,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H339" s="11" t="inlineStr">
+      <c r="H339" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I339" s="8" t="inlineStr">
+      <c r="I339" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15264,12 +15205,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H340" s="11" t="inlineStr">
+      <c r="H340" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I340" s="8" t="inlineStr">
+      <c r="I340" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15304,12 +15245,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H341" s="11" t="inlineStr">
+      <c r="H341" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I341" s="8" t="inlineStr">
+      <c r="I341" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15344,12 +15285,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H342" s="11" t="inlineStr">
+      <c r="H342" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I342" s="8" t="inlineStr">
+      <c r="I342" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15384,12 +15325,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H343" s="11" t="inlineStr">
+      <c r="H343" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I343" s="8" t="inlineStr">
+      <c r="I343" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15424,12 +15365,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H344" s="11" t="inlineStr">
+      <c r="H344" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I344" s="8" t="inlineStr">
+      <c r="I344" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15464,12 +15405,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H345" s="11" t="inlineStr">
+      <c r="H345" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I345" s="8" t="inlineStr">
+      <c r="I345" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15504,12 +15445,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H346" s="11" t="inlineStr">
+      <c r="H346" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I346" s="8" t="inlineStr">
+      <c r="I346" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15544,12 +15485,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H347" s="11" t="inlineStr">
+      <c r="H347" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I347" s="8" t="inlineStr">
+      <c r="I347" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15584,12 +15525,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H348" s="11" t="inlineStr">
+      <c r="H348" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I348" s="8" t="inlineStr">
+      <c r="I348" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15624,12 +15565,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H349" s="11" t="inlineStr">
+      <c r="H349" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I349" s="8" t="inlineStr">
+      <c r="I349" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15664,12 +15605,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H350" s="11" t="inlineStr">
+      <c r="H350" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I350" s="8" t="inlineStr">
+      <c r="I350" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15704,12 +15645,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H351" s="11" t="inlineStr">
+      <c r="H351" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I351" s="8" t="inlineStr">
+      <c r="I351" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15744,12 +15685,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H352" s="11" t="inlineStr">
+      <c r="H352" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I352" s="8" t="inlineStr">
+      <c r="I352" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15784,12 +15725,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H353" s="11" t="inlineStr">
+      <c r="H353" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I353" s="8" t="inlineStr">
+      <c r="I353" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15824,12 +15765,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H354" s="11" t="inlineStr">
+      <c r="H354" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I354" s="8" t="inlineStr">
+      <c r="I354" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15864,12 +15805,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H355" s="11" t="inlineStr">
+      <c r="H355" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I355" s="8" t="inlineStr">
+      <c r="I355" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15904,12 +15845,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H356" s="11" t="inlineStr">
+      <c r="H356" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I356" s="8" t="inlineStr">
+      <c r="I356" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15944,12 +15885,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H357" s="11" t="inlineStr">
+      <c r="H357" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I357" s="8" t="inlineStr">
+      <c r="I357" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15984,12 +15925,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H358" s="11" t="inlineStr">
+      <c r="H358" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I358" s="8" t="inlineStr">
+      <c r="I358" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16024,12 +15965,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H359" s="11" t="inlineStr">
+      <c r="H359" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I359" s="8" t="inlineStr">
+      <c r="I359" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16064,12 +16005,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H360" s="11" t="inlineStr">
+      <c r="H360" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I360" s="8" t="inlineStr">
+      <c r="I360" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16104,12 +16045,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H361" s="11" t="inlineStr">
+      <c r="H361" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I361" s="8" t="inlineStr">
+      <c r="I361" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16144,12 +16085,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H362" s="11" t="inlineStr">
+      <c r="H362" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I362" s="8" t="inlineStr">
+      <c r="I362" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16184,12 +16125,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H363" s="11" t="inlineStr">
+      <c r="H363" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I363" s="8" t="inlineStr">
+      <c r="I363" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16224,12 +16165,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H364" s="11" t="inlineStr">
+      <c r="H364" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I364" s="8" t="inlineStr">
+      <c r="I364" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16264,12 +16205,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H365" s="11" t="inlineStr">
+      <c r="H365" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I365" s="8" t="inlineStr">
+      <c r="I365" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16304,12 +16245,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H366" s="11" t="inlineStr">
+      <c r="H366" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I366" s="8" t="inlineStr">
+      <c r="I366" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16344,12 +16285,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H367" s="11" t="inlineStr">
+      <c r="H367" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I367" s="8" t="inlineStr">
+      <c r="I367" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16368,12 +16309,12 @@
         </is>
       </c>
       <c r="C368" s="3" t="n">
-        <v>204872</v>
+        <v>202880</v>
       </c>
       <c r="D368" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E368" s="10" t="n">
+      <c r="E368" s="9" t="n">
         <v>207020</v>
       </c>
       <c r="F368" s="3" t="n">
@@ -16384,17 +16325,17 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H368" s="11" t="inlineStr">
+      <c r="H368" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I368" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J368" s="8" t="inlineStr">
+      <c r="I368" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J368" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -16428,12 +16369,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H369" s="11" t="inlineStr">
+      <c r="H369" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I369" s="8" t="inlineStr">
+      <c r="I369" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16468,12 +16409,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H370" s="11" t="inlineStr">
+      <c r="H370" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I370" s="8" t="inlineStr">
+      <c r="I370" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16508,12 +16449,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H371" s="11" t="inlineStr">
+      <c r="H371" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I371" s="8" t="inlineStr">
+      <c r="I371" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16548,12 +16489,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H372" s="11" t="inlineStr">
+      <c r="H372" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I372" s="8" t="inlineStr">
+      <c r="I372" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16588,12 +16529,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H373" s="11" t="inlineStr">
+      <c r="H373" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I373" s="8" t="inlineStr">
+      <c r="I373" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16628,12 +16569,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H374" s="11" t="inlineStr">
+      <c r="H374" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I374" s="8" t="inlineStr">
+      <c r="I374" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16668,12 +16609,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H375" s="11" t="inlineStr">
+      <c r="H375" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I375" s="8" t="inlineStr">
+      <c r="I375" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16708,12 +16649,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H376" s="11" t="inlineStr">
+      <c r="H376" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I376" s="8" t="inlineStr">
+      <c r="I376" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16748,12 +16689,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H377" s="11" t="inlineStr">
+      <c r="H377" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I377" s="8" t="inlineStr">
+      <c r="I377" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16788,12 +16729,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H378" s="11" t="inlineStr">
+      <c r="H378" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I378" s="8" t="inlineStr">
+      <c r="I378" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16812,37 +16753,33 @@
         </is>
       </c>
       <c r="C379" s="3" t="n">
-        <v>11538941.4</v>
+        <v>11421197</v>
       </c>
       <c r="D379" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E379" s="10" t="n">
-        <v>11774430</v>
+      <c r="E379" s="3" t="n">
+        <v>11774429.89690722</v>
       </c>
       <c r="F379" s="3" t="n">
-        <v>12127662.9</v>
+        <v>12127662.79381443</v>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H379" s="11" t="inlineStr">
+      <c r="H379" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I379" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J379" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I379" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -16856,37 +16793,33 @@
         </is>
       </c>
       <c r="C380" s="3" t="n">
-        <v>13528723.6</v>
+        <v>13390675</v>
       </c>
       <c r="D380" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E380" s="10" t="n">
-        <v>13804820</v>
+      <c r="E380" s="3" t="n">
+        <v>13804819.58762887</v>
       </c>
       <c r="F380" s="3" t="n">
-        <v>14218964.6</v>
+        <v>14218964.17525773</v>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H380" s="11" t="inlineStr">
+      <c r="H380" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I380" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J380" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I380" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -16900,37 +16833,33 @@
         </is>
       </c>
       <c r="C381" s="3" t="n">
-        <v>17281153.4</v>
+        <v>17104815</v>
       </c>
       <c r="D381" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E381" s="10" t="n">
-        <v>17633830</v>
+      <c r="E381" s="3" t="n">
+        <v>17633829.89690722</v>
       </c>
       <c r="F381" s="3" t="n">
-        <v>18162844.9</v>
+        <v>18162844.79381444</v>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H381" s="11" t="inlineStr">
+      <c r="H381" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I381" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J381" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I381" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -16944,37 +16873,33 @@
         </is>
       </c>
       <c r="C382" s="3" t="n">
-        <v>7043289.4</v>
+        <v>6971419</v>
       </c>
       <c r="D382" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E382" s="10" t="n">
-        <v>7187030</v>
+      <c r="E382" s="3" t="n">
+        <v>7187029.896907217</v>
       </c>
       <c r="F382" s="3" t="n">
-        <v>7402640.9</v>
+        <v>7402640.793814434</v>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H382" s="11" t="inlineStr">
+      <c r="H382" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I382" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J382" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I382" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -16988,12 +16913,12 @@
         </is>
       </c>
       <c r="C383" s="3" t="n">
-        <v>8563347.800000001</v>
+        <v>8475967</v>
       </c>
       <c r="D383" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E383" s="10" t="n">
+      <c r="E383" s="9" t="n">
         <v>8738110</v>
       </c>
       <c r="F383" s="3" t="n">
@@ -17004,17 +16929,17 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H383" s="11" t="inlineStr">
+      <c r="H383" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I383" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J383" s="8" t="inlineStr">
+      <c r="I383" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J383" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17032,37 +16957,33 @@
         </is>
       </c>
       <c r="C384" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="D384" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E384" s="10" t="n">
-        <v>8631560</v>
+      <c r="E384" s="3" t="n">
+        <v>8631559.793814434</v>
       </c>
       <c r="F384" s="3" t="n">
-        <v>8890506.800000001</v>
+        <v>8890506.587628867</v>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H384" s="11" t="inlineStr">
+      <c r="H384" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I384" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J384" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I384" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -17076,37 +16997,33 @@
         </is>
       </c>
       <c r="C385" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="D385" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E385" s="10" t="n">
-        <v>8631560</v>
+      <c r="E385" s="3" t="n">
+        <v>8631559.793814434</v>
       </c>
       <c r="F385" s="3" t="n">
-        <v>8890506.800000001</v>
+        <v>8890506.587628867</v>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H385" s="11" t="inlineStr">
+      <c r="H385" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I385" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J385" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I385" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -17120,37 +17037,33 @@
         </is>
       </c>
       <c r="C386" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="D386" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E386" s="10" t="n">
-        <v>10927020</v>
+      <c r="E386" s="3" t="n">
+        <v>10927019.58762887</v>
       </c>
       <c r="F386" s="3" t="n">
-        <v>11254830.6</v>
+        <v>11254830.17525773</v>
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H386" s="11" t="inlineStr">
+      <c r="H386" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I386" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J386" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I386" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -17164,37 +17077,33 @@
         </is>
       </c>
       <c r="C387" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="D387" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E387" s="10" t="n">
-        <v>10927020</v>
+      <c r="E387" s="3" t="n">
+        <v>10927019.58762887</v>
       </c>
       <c r="F387" s="3" t="n">
-        <v>11254830.6</v>
+        <v>11254830.17525773</v>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H387" s="11" t="inlineStr">
+      <c r="H387" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I387" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J387" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I387" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -17208,37 +17117,33 @@
         </is>
       </c>
       <c r="C388" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="D388" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E388" s="10" t="n">
-        <v>14163130</v>
+      <c r="E388" s="3" t="n">
+        <v>14163129.89690722</v>
       </c>
       <c r="F388" s="3" t="n">
-        <v>14588023.9</v>
+        <v>14588023.79381444</v>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H388" s="11" t="inlineStr">
+      <c r="H388" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I388" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J388" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I388" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -17252,37 +17157,33 @@
         </is>
       </c>
       <c r="C389" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="D389" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E389" s="10" t="n">
-        <v>14163130</v>
+      <c r="E389" s="3" t="n">
+        <v>14163129.89690722</v>
       </c>
       <c r="F389" s="3" t="n">
-        <v>14588023.9</v>
+        <v>14588023.79381444</v>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H389" s="11" t="inlineStr">
+      <c r="H389" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I389" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J389" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I389" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -17296,12 +17197,12 @@
         </is>
       </c>
       <c r="C390" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="D390" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E390" s="10" t="n">
+      <c r="E390" s="9" t="n">
         <v>3494770</v>
       </c>
       <c r="F390" s="3" t="n">
@@ -17312,17 +17213,17 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H390" s="11" t="inlineStr">
+      <c r="H390" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I390" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J390" s="8" t="inlineStr">
+      <c r="I390" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J390" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17340,12 +17241,12 @@
         </is>
       </c>
       <c r="C391" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="D391" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E391" s="10" t="n">
+      <c r="E391" s="9" t="n">
         <v>3494770</v>
       </c>
       <c r="F391" s="3" t="n">
@@ -17356,17 +17257,17 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H391" s="11" t="inlineStr">
+      <c r="H391" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I391" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J391" s="8" t="inlineStr">
+      <c r="I391" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J391" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17384,37 +17285,33 @@
         </is>
       </c>
       <c r="C392" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="D392" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E392" s="10" t="n">
-        <v>4919190</v>
+      <c r="E392" s="3" t="n">
+        <v>4919189.69072165</v>
       </c>
       <c r="F392" s="3" t="n">
-        <v>5066765.7</v>
+        <v>5066765.381443299</v>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H392" s="11" t="inlineStr">
+      <c r="H392" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I392" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J392" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I392" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -17428,37 +17325,33 @@
         </is>
       </c>
       <c r="C393" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="D393" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E393" s="10" t="n">
-        <v>4919190</v>
+      <c r="E393" s="3" t="n">
+        <v>4919189.69072165</v>
       </c>
       <c r="F393" s="3" t="n">
-        <v>5066765.7</v>
+        <v>5066765.381443299</v>
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H393" s="11" t="inlineStr">
+      <c r="H393" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I393" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J393" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I393" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -17472,12 +17365,12 @@
         </is>
       </c>
       <c r="C394" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="D394" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E394" s="10" t="n">
+      <c r="E394" s="9" t="n">
         <v>6542350</v>
       </c>
       <c r="F394" s="3" t="n">
@@ -17488,17 +17381,17 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H394" s="11" t="inlineStr">
+      <c r="H394" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I394" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J394" s="8" t="inlineStr">
+      <c r="I394" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J394" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17516,12 +17409,12 @@
         </is>
       </c>
       <c r="C395" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="D395" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E395" s="10" t="n">
+      <c r="E395" s="9" t="n">
         <v>6542350</v>
       </c>
       <c r="F395" s="3" t="n">
@@ -17532,17 +17425,17 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H395" s="11" t="inlineStr">
+      <c r="H395" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I395" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J395" s="8" t="inlineStr">
+      <c r="I395" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J395" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17576,12 +17469,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H396" s="11" t="inlineStr">
+      <c r="H396" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I396" s="8" t="inlineStr">
+      <c r="I396" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17616,12 +17509,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H397" s="11" t="inlineStr">
+      <c r="H397" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I397" s="8" t="inlineStr">
+      <c r="I397" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17656,12 +17549,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H398" s="11" t="inlineStr">
+      <c r="H398" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I398" s="8" t="inlineStr">
+      <c r="I398" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17685,7 +17578,7 @@
       <c r="D399" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E399" s="10" t="n">
+      <c r="E399" s="9" t="n">
         <v>728710</v>
       </c>
       <c r="F399" s="3" t="n">
@@ -17696,17 +17589,17 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H399" s="11" t="inlineStr">
+      <c r="H399" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I399" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J399" s="8" t="inlineStr">
+      <c r="I399" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J399" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17729,7 +17622,7 @@
       <c r="D400" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E400" s="10" t="n">
+      <c r="E400" s="9" t="n">
         <v>903010</v>
       </c>
       <c r="F400" s="3" t="n">
@@ -17740,17 +17633,17 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H400" s="11" t="inlineStr">
+      <c r="H400" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I400" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J400" s="8" t="inlineStr">
+      <c r="I400" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J400" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17784,12 +17677,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H401" s="11" t="inlineStr">
+      <c r="H401" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I401" s="8" t="inlineStr">
+      <c r="I401" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17824,12 +17717,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H402" s="11" t="inlineStr">
+      <c r="H402" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I402" s="8" t="inlineStr">
+      <c r="I402" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17864,12 +17757,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H403" s="11" t="inlineStr">
+      <c r="H403" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I403" s="8" t="inlineStr">
+      <c r="I403" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17904,12 +17797,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H404" s="11" t="inlineStr">
+      <c r="H404" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I404" s="8" t="inlineStr">
+      <c r="I404" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17944,12 +17837,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H405" s="11" t="inlineStr">
+      <c r="H405" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I405" s="8" t="inlineStr">
+      <c r="I405" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17984,12 +17877,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H406" s="11" t="inlineStr">
+      <c r="H406" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I406" s="8" t="inlineStr">
+      <c r="I406" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18024,12 +17917,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H407" s="11" t="inlineStr">
+      <c r="H407" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I407" s="8" t="inlineStr">
+      <c r="I407" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18064,12 +17957,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H408" s="11" t="inlineStr">
+      <c r="H408" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I408" s="8" t="inlineStr">
+      <c r="I408" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18104,12 +17997,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H409" s="11" t="inlineStr">
+      <c r="H409" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I409" s="8" t="inlineStr">
+      <c r="I409" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18144,12 +18037,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H410" s="11" t="inlineStr">
+      <c r="H410" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I410" s="8" t="inlineStr">
+      <c r="I410" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18184,12 +18077,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H411" s="11" t="inlineStr">
+      <c r="H411" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I411" s="8" t="inlineStr">
+      <c r="I411" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18224,12 +18117,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H412" s="11" t="inlineStr">
+      <c r="H412" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I412" s="8" t="inlineStr">
+      <c r="I412" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18264,12 +18157,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H413" s="11" t="inlineStr">
+      <c r="H413" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I413" s="8" t="inlineStr">
+      <c r="I413" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18304,12 +18197,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H414" s="11" t="inlineStr">
+      <c r="H414" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I414" s="8" t="inlineStr">
+      <c r="I414" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18344,12 +18237,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H415" s="11" t="inlineStr">
+      <c r="H415" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I415" s="8" t="inlineStr">
+      <c r="I415" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18384,12 +18277,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H416" s="11" t="inlineStr">
+      <c r="H416" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I416" s="8" t="inlineStr">
+      <c r="I416" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18424,12 +18317,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H417" s="11" t="inlineStr">
+      <c r="H417" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I417" s="8" t="inlineStr">
+      <c r="I417" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18464,12 +18357,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H418" s="11" t="inlineStr">
+      <c r="H418" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I418" s="8" t="inlineStr">
+      <c r="I418" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18504,12 +18397,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H419" s="11" t="inlineStr">
+      <c r="H419" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I419" s="8" t="inlineStr">
+      <c r="I419" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18544,12 +18437,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H420" s="11" t="inlineStr">
+      <c r="H420" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I420" s="8" t="inlineStr">
+      <c r="I420" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18584,12 +18477,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H421" s="11" t="inlineStr">
+      <c r="H421" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I421" s="8" t="inlineStr">
+      <c r="I421" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18624,12 +18517,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H422" s="11" t="inlineStr">
+      <c r="H422" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I422" s="8" t="inlineStr">
+      <c r="I422" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18664,12 +18557,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H423" s="11" t="inlineStr">
+      <c r="H423" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I423" s="8" t="inlineStr">
+      <c r="I423" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18704,12 +18597,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H424" s="11" t="inlineStr">
+      <c r="H424" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I424" s="8" t="inlineStr">
+      <c r="I424" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18744,12 +18637,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H425" s="11" t="inlineStr">
+      <c r="H425" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I425" s="8" t="inlineStr">
+      <c r="I425" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18784,12 +18677,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H426" s="11" t="inlineStr">
+      <c r="H426" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I426" s="8" t="inlineStr">
+      <c r="I426" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18824,12 +18717,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H427" s="11" t="inlineStr">
+      <c r="H427" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I427" s="8" t="inlineStr">
+      <c r="I427" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18864,12 +18757,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H428" s="11" t="inlineStr">
+      <c r="H428" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I428" s="8" t="inlineStr">
+      <c r="I428" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18904,12 +18797,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H429" s="11" t="inlineStr">
+      <c r="H429" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I429" s="8" t="inlineStr">
+      <c r="I429" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18944,12 +18837,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H430" s="11" t="inlineStr">
+      <c r="H430" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I430" s="8" t="inlineStr">
+      <c r="I430" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18984,12 +18877,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H431" s="11" t="inlineStr">
+      <c r="H431" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I431" s="8" t="inlineStr">
+      <c r="I431" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19024,12 +18917,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H432" s="11" t="inlineStr">
+      <c r="H432" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I432" s="8" t="inlineStr">
+      <c r="I432" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19064,12 +18957,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H433" s="11" t="inlineStr">
+      <c r="H433" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I433" s="8" t="inlineStr">
+      <c r="I433" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19104,12 +18997,12 @@
           <t>SFP/커넥터/서지(패턴)</t>
         </is>
       </c>
-      <c r="H434" s="11" t="inlineStr">
+      <c r="H434" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I434" s="8" t="inlineStr">
+      <c r="I434" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19144,12 +19037,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H435" s="11" t="inlineStr">
+      <c r="H435" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I435" s="8" t="inlineStr">
+      <c r="I435" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19184,12 +19077,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H436" s="11" t="inlineStr">
+      <c r="H436" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I436" s="8" t="inlineStr">
+      <c r="I436" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19224,12 +19117,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H437" s="11" t="inlineStr">
+      <c r="H437" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I437" s="8" t="inlineStr">
+      <c r="I437" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19264,12 +19157,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H438" s="11" t="inlineStr">
+      <c r="H438" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I438" s="8" t="inlineStr">
+      <c r="I438" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19304,12 +19197,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H439" s="11" t="inlineStr">
+      <c r="H439" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I439" s="8" t="inlineStr">
+      <c r="I439" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19344,12 +19237,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H440" s="11" t="inlineStr">
+      <c r="H440" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I440" s="8" t="inlineStr">
+      <c r="I440" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19384,12 +19277,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H441" s="11" t="inlineStr">
+      <c r="H441" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I441" s="8" t="inlineStr">
+      <c r="I441" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19424,12 +19317,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H442" s="11" t="inlineStr">
+      <c r="H442" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I442" s="8" t="inlineStr">
+      <c r="I442" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19464,12 +19357,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H443" s="11" t="inlineStr">
+      <c r="H443" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I443" s="8" t="inlineStr">
+      <c r="I443" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19504,12 +19397,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H444" s="11" t="inlineStr">
+      <c r="H444" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I444" s="8" t="inlineStr">
+      <c r="I444" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19544,12 +19437,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H445" s="11" t="inlineStr">
+      <c r="H445" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I445" s="8" t="inlineStr">
+      <c r="I445" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19584,12 +19477,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H446" s="11" t="inlineStr">
+      <c r="H446" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I446" s="8" t="inlineStr">
+      <c r="I446" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19624,12 +19517,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H447" s="11" t="inlineStr">
+      <c r="H447" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I447" s="8" t="inlineStr">
+      <c r="I447" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19664,12 +19557,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H448" s="11" t="inlineStr">
+      <c r="H448" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I448" s="8" t="inlineStr">
+      <c r="I448" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19704,12 +19597,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H449" s="11" t="inlineStr">
+      <c r="H449" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I449" s="8" t="inlineStr">
+      <c r="I449" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19744,12 +19637,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H450" s="11" t="inlineStr">
+      <c r="H450" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I450" s="8" t="inlineStr">
+      <c r="I450" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19784,12 +19677,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H451" s="11" t="inlineStr">
+      <c r="H451" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I451" s="8" t="inlineStr">
+      <c r="I451" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19824,12 +19717,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H452" s="11" t="inlineStr">
+      <c r="H452" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I452" s="8" t="inlineStr">
+      <c r="I452" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19864,12 +19757,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H453" s="11" t="inlineStr">
+      <c r="H453" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I453" s="8" t="inlineStr">
+      <c r="I453" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19904,12 +19797,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H454" s="11" t="inlineStr">
+      <c r="H454" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I454" s="8" t="inlineStr">
+      <c r="I454" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19944,12 +19837,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H455" s="11" t="inlineStr">
+      <c r="H455" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I455" s="8" t="inlineStr">
+      <c r="I455" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19984,12 +19877,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H456" s="11" t="inlineStr">
+      <c r="H456" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I456" s="8" t="inlineStr">
+      <c r="I456" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20024,12 +19917,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H457" s="11" t="inlineStr">
+      <c r="H457" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I457" s="8" t="inlineStr">
+      <c r="I457" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20064,12 +19957,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H458" s="11" t="inlineStr">
+      <c r="H458" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I458" s="8" t="inlineStr">
+      <c r="I458" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20104,12 +19997,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H459" s="11" t="inlineStr">
+      <c r="H459" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I459" s="8" t="inlineStr">
+      <c r="I459" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20144,12 +20037,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H460" s="11" t="inlineStr">
+      <c r="H460" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I460" s="8" t="inlineStr">
+      <c r="I460" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20184,12 +20077,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H461" s="11" t="inlineStr">
+      <c r="H461" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I461" s="8" t="inlineStr">
+      <c r="I461" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20224,12 +20117,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H462" s="11" t="inlineStr">
+      <c r="H462" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I462" s="8" t="inlineStr">
+      <c r="I462" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20264,12 +20157,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H463" s="11" t="inlineStr">
+      <c r="H463" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I463" s="8" t="inlineStr">
+      <c r="I463" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20304,12 +20197,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H464" s="11" t="inlineStr">
+      <c r="H464" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I464" s="8" t="inlineStr">
+      <c r="I464" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20344,12 +20237,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H465" s="11" t="inlineStr">
+      <c r="H465" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I465" s="8" t="inlineStr">
+      <c r="I465" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20384,12 +20277,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H466" s="11" t="inlineStr">
+      <c r="H466" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I466" s="8" t="inlineStr">
+      <c r="I466" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20424,12 +20317,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H467" s="11" t="inlineStr">
+      <c r="H467" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I467" s="8" t="inlineStr">
+      <c r="I467" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20464,12 +20357,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H468" s="11" t="inlineStr">
+      <c r="H468" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I468" s="8" t="inlineStr">
+      <c r="I468" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20504,12 +20397,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H469" s="11" t="inlineStr">
+      <c r="H469" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I469" s="8" t="inlineStr">
+      <c r="I469" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20544,12 +20437,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H470" s="11" t="inlineStr">
+      <c r="H470" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I470" s="8" t="inlineStr">
+      <c r="I470" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20584,12 +20477,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H471" s="11" t="inlineStr">
+      <c r="H471" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I471" s="8" t="inlineStr">
+      <c r="I471" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20624,12 +20517,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H472" s="11" t="inlineStr">
+      <c r="H472" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I472" s="8" t="inlineStr">
+      <c r="I472" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20664,12 +20557,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H473" s="11" t="inlineStr">
+      <c r="H473" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I473" s="8" t="inlineStr">
+      <c r="I473" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20704,12 +20597,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H474" s="11" t="inlineStr">
+      <c r="H474" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I474" s="8" t="inlineStr">
+      <c r="I474" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20744,12 +20637,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H475" s="11" t="inlineStr">
+      <c r="H475" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I475" s="8" t="inlineStr">
+      <c r="I475" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20784,12 +20677,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H476" s="11" t="inlineStr">
+      <c r="H476" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I476" s="8" t="inlineStr">
+      <c r="I476" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20824,12 +20717,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H477" s="11" t="inlineStr">
+      <c r="H477" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I477" s="8" t="inlineStr">
+      <c r="I477" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20864,12 +20757,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H478" s="11" t="inlineStr">
+      <c r="H478" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I478" s="8" t="inlineStr">
+      <c r="I478" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20904,12 +20797,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H479" s="11" t="inlineStr">
+      <c r="H479" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I479" s="8" t="inlineStr">
+      <c r="I479" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20944,12 +20837,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H480" s="11" t="inlineStr">
+      <c r="H480" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I480" s="8" t="inlineStr">
+      <c r="I480" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20984,12 +20877,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H481" s="11" t="inlineStr">
+      <c r="H481" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I481" s="8" t="inlineStr">
+      <c r="I481" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21024,12 +20917,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H482" s="11" t="inlineStr">
+      <c r="H482" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I482" s="8" t="inlineStr">
+      <c r="I482" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21064,12 +20957,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H483" s="11" t="inlineStr">
+      <c r="H483" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I483" s="8" t="inlineStr">
+      <c r="I483" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21104,12 +20997,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H484" s="11" t="inlineStr">
+      <c r="H484" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I484" s="8" t="inlineStr">
+      <c r="I484" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21144,12 +21037,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H485" s="11" t="inlineStr">
+      <c r="H485" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I485" s="8" t="inlineStr">
+      <c r="I485" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21184,12 +21077,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H486" s="11" t="inlineStr">
+      <c r="H486" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I486" s="8" t="inlineStr">
+      <c r="I486" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21224,12 +21117,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H487" s="11" t="inlineStr">
+      <c r="H487" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I487" s="8" t="inlineStr">
+      <c r="I487" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21248,12 +21141,12 @@
         </is>
       </c>
       <c r="C488" s="3" t="n">
-        <v>2963892.4</v>
+        <v>2933649</v>
       </c>
       <c r="D488" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E488" s="10" t="n">
+      <c r="E488" s="9" t="n">
         <v>3024380</v>
       </c>
       <c r="F488" s="3" t="n">
@@ -21264,17 +21157,17 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H488" s="11" t="inlineStr">
+      <c r="H488" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I488" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J488" s="8" t="inlineStr">
+      <c r="I488" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J488" s="7" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -21308,12 +21201,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H489" s="11" t="inlineStr">
+      <c r="H489" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I489" s="8" t="inlineStr">
+      <c r="I489" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21332,37 +21225,33 @@
         </is>
       </c>
       <c r="C490" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="D490" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E490" s="10" t="n">
-        <v>5343190</v>
+      <c r="E490" s="3" t="n">
+        <v>5343189.69072165</v>
       </c>
       <c r="F490" s="3" t="n">
-        <v>5503485.7</v>
+        <v>5503485.381443299</v>
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H490" s="11" t="inlineStr">
+      <c r="H490" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I490" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J490" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I490" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J490" s="2" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -21376,37 +21265,33 @@
         </is>
       </c>
       <c r="C491" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="D491" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E491" s="10" t="n">
-        <v>5343190</v>
+      <c r="E491" s="3" t="n">
+        <v>5343189.69072165</v>
       </c>
       <c r="F491" s="3" t="n">
-        <v>5503485.7</v>
+        <v>5503485.381443299</v>
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H491" s="11" t="inlineStr">
+      <c r="H491" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I491" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J491" s="8" t="inlineStr">
-        <is>
-          <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
-        </is>
-      </c>
+      <c r="I491" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J491" s="2" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -21436,12 +21321,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H492" s="11" t="inlineStr">
+      <c r="H492" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I492" s="8" t="inlineStr">
+      <c r="I492" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21460,37 +21345,33 @@
         </is>
       </c>
       <c r="C493" s="3" t="n">
-        <v>634418</v>
+        <v>105110</v>
       </c>
       <c r="D493" s="6" t="n">
         <v>0.02</v>
       </c>
       <c r="E493" s="3" t="n">
-        <v>123210</v>
+        <v>107255.1020408163</v>
       </c>
       <c r="F493" s="3" t="n">
-        <v>126906.3</v>
+        <v>110472.7551020408</v>
       </c>
       <c r="G493" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H493" s="11" t="inlineStr">
+      <c r="H493" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I493" s="8" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J493" s="11" t="inlineStr">
-        <is>
-          <t>데이터 이상치(할인 후 가격이 정가보다 높음 - 공급사 확인 필요)</t>
-        </is>
-      </c>
+      <c r="I493" s="7" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J493" s="2" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
@@ -21520,12 +21401,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H494" s="11" t="inlineStr">
+      <c r="H494" s="10" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I494" s="8" t="inlineStr">
+      <c r="I494" s="7" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -22795,38 +22676,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>393069.6</v>
+        <v>377188</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>397040</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3970.400000000023</v>
+        <v>19852</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>408951.2</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>749034</v>
+        <v>718768</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>756600</v>
+      <c r="I12" s="3" t="n">
+        <v>756597.8947368421</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>7566</v>
+        <v>37829.89473684214</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>779298</v>
+        <v>779295.8315789474</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -22863,36 +22744,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>36333293.1781822</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>725287.8321821988</v>
+        <v>741169.4321822003</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>37423291.97352767</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>47710885.87800001</v>
+        <v>47680619.87800001</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>48679782.47111298</v>
+        <v>48679780.36584982</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>968896.5931129754</v>
+        <v>999160.4878498167</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>50140175.94524637</v>
+        <v>50140173.77682532</v>
       </c>
     </row>
   </sheetData>
@@ -23357,38 +23238,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>578476.8</v>
+        <v>555104</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>584320</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5843.199999999953</v>
+        <v>29216</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>601849.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1290405.6</v>
+        <v>1238264</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>1303440</v>
+      <c r="I12" s="3" t="n">
+        <v>1303435.789473684</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>13034.39999999991</v>
+        <v>65171.78947368427</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1342543.2</v>
+        <v>1342538.863157895</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -23425,36 +23306,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>55704470.07799999</v>
+        <v>55681097.278</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>56838259.00172523</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1133788.923725232</v>
+        <v>1157161.72372523</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>58543406.77177699</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>65924718.84</v>
+        <v>65872577.23999999</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>67260306.66717862</v>
+        <v>67260302.4566523</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1335587.82717862</v>
+        <v>1387725.216652304</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>69278115.86719398</v>
+        <v>69278111.53035188</v>
       </c>
     </row>
   </sheetData>
@@ -23919,38 +23800,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>763884.0000000001</v>
+        <v>733020</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>771600</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7715.999999999884</v>
+        <v>38580</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>794748</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1831777.2</v>
+        <v>1757760</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>1850280</v>
+      <c r="I12" s="3" t="n">
+        <v>1850273.684210526</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>18502.80000000028</v>
+        <v>92513.68421052629</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1905788.4</v>
+        <v>1905781.894736842</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -23987,36 +23868,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>75626915.888</v>
+        <v>75596051.888</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>77167201.85102041</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1540285.963020414</v>
+        <v>1571149.963020414</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>79482217.90655102</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>83890988.12600002</v>
+        <v>83816970.92600001</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>85589762.22164948</v>
+        <v>85589755.90586001</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1698774.095649466</v>
+        <v>1772784.979859993</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>88157455.08829896</v>
+        <v>88157448.5830358</v>
       </c>
     </row>
   </sheetData>
@@ -24481,38 +24362,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>949291.2000000001</v>
+        <v>910936</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>958880</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>9588.79999999993</v>
+        <v>47944</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>987646.4</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>2373148.8</v>
+        <v>2277256</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>2397120</v>
+      <c r="I12" s="3" t="n">
+        <v>2397111.578947369</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>23971.19999999972</v>
+        <v>119855.5789473685</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>2469033.6</v>
+        <v>2469024.92631579</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -24549,36 +24430,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>91513678.52200001</v>
+        <v>91475323.32200001</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>93376553.28884916</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1862874.766849145</v>
+        <v>1901229.966849148</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>96177849.88751461</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>103910327.142</v>
+        <v>103814434.342</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>106012639.5340417</v>
+        <v>106012631.112989</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>2102312.392041653</v>
+        <v>2198196.770989016</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>109193018.7200629</v>
+        <v>109193010.0463787</v>
       </c>
     </row>
   </sheetData>
@@ -25035,38 +24916,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>393069.6</v>
+        <v>377188</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>397040</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>3970.400000000023</v>
+        <v>19852</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>408951.2</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>749034</v>
+        <v>718768</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>756600</v>
+      <c r="I12" s="3" t="n">
+        <v>756597.8947368421</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>7566</v>
+        <v>37829.89473684214</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>779298</v>
+        <v>779295.8315789474</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -25103,36 +24984,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>36333293.1781822</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>725287.8321821988</v>
+        <v>741169.4321822003</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>37423291.97352767</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>47709791.642</v>
+        <v>47679525.642</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>48678665.90376604</v>
+        <v>48678663.79850288</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>968874.2617660388</v>
+        <v>999138.1565028802</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>50139025.88087902</v>
+        <v>50139023.71245797</v>
       </c>
     </row>
   </sheetData>
@@ -25597,38 +25478,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>578476.8</v>
+        <v>555104</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>584320</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>5843.199999999953</v>
+        <v>29216</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>601849.6</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1290405.6</v>
+        <v>1238264</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>1303440</v>
+      <c r="I12" s="3" t="n">
+        <v>1303435.789473684</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>13034.39999999991</v>
+        <v>65171.78947368427</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1342543.2</v>
+        <v>1342538.863157895</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -25665,36 +25546,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>55702281.606</v>
+        <v>55678908.806</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>56836025.86703135</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1133744.261031352</v>
+        <v>1157117.061031349</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>58541106.6430423</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>65922530.36799999</v>
+        <v>65870388.76799999</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>67258073.53248474</v>
+        <v>67258069.32195842</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1335543.164484747</v>
+        <v>1387680.553958431</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>69275815.73845929</v>
+        <v>69275811.40161718</v>
       </c>
     </row>
   </sheetData>
@@ -26159,38 +26040,38 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>763884.0000000001</v>
+        <v>733020</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="3" t="n">
         <v>771600</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7715.999999999884</v>
+        <v>38580</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>794748</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1831777.2</v>
+        <v>1757760</v>
       </c>
       <c r="H12" s="6" t="n">
         <v>0.05</v>
       </c>
-      <c r="I12" s="7" t="n">
-        <v>1850280</v>
+      <c r="I12" s="3" t="n">
+        <v>1850273.684210526</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>18502.80000000028</v>
+        <v>92513.68421052629</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>1905788.4</v>
+        <v>1905781.894736842</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -26227,36 +26108,36 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="8" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
-        <v>75623633.18000001</v>
+        <v>75592769.18000001</v>
       </c>
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="3" t="n">
         <v>77163852.14897959</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>1540218.968979582</v>
+        <v>1571082.968979582</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>79478767.71344897</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>83887705.41800001</v>
+        <v>83813688.21800001</v>
       </c>
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="3" t="n">
-        <v>85586412.51960868</v>
+        <v>85586406.2038192</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>1698707.101608664</v>
+        <v>1772717.985819191</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>88154004.89519693</v>
+        <v>88153998.38993376</v>
       </c>
     </row>
   </sheetData>

--- a/output/15_매입판매가_제시안.xlsx
+++ b/output/15_매입판매가_제시안.xlsx
@@ -21,7 +21,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체카탈로그_단가제시안(493종)" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안내'!$A$1:$B$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'안내'!$A$1:$B$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'마진구조_검증(01번 전수)'!$A$1:$F$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'8GHz_2+0_제시안'!$A$1:$K$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'8GHz_4+0_제시안'!$A$1:$K$14</definedName>
@@ -111,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -129,6 +129,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -508,7 +511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -671,8 +674,20 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>버퍼 재상한 버그 수정(2026-09-15) - 중요한 버그 수정</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>돈현님이 전송망설계팀向 K코드별 단가표에서 다수 품목의 '신규(판매)단가'가 '기존단가(정가)'보다 높다는 걸 발견했다. 원인: 정가상한에 걸려 목표가가 이미 정가에 근접한 품목은, 그 위에 버퍼(+3%p)를 얹는 순간 결과값이 다시 정가를 넘어버렸다 - capped_sale()은 목표가 단계에서만 정가 상한을 걸고, 버퍼를 곱한 뒤에는 재확인을 하지 않았던 게 원인. capped_anchor() 함수를 추가해 버퍼 적용 후 최종값도 다시 정가로 상한을 걸도록 고쳤다(품목별로 먼저 상한을 걸고 카테고리 합계를 내는 방식은 기존 capped_sale과 동일). 이 경우로 새로 상한이 걸린 품목은 '가격 이상 여부' 열에 '버퍼상한 적용'으로 표시했다 - 일부러 '정가상한'이라는 문구를 쓰지 않았는데, 16번이 '정가상한'이 포함된 문자열을 대성에 매입가 재협상을 요청할 대상으로 간주해 필터링하기 때문이다(이 항목은 애초에 목표가 자체는 정가 이내라 대성에 요청할 이유가 없는, 순수하게 KT 내부 버퍼 계산의 문제).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B13"/>
+  <autoFilter ref="A1:B14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -849,7 +864,7 @@
         <v>264484.4927346949</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>13620951.37583674</v>
+        <v>13620951.37583673</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>13488196.144</v>
@@ -1144,8 +1159,8 @@
       <c r="E12" s="3" t="n">
         <v>47944</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>987646.4</v>
+      <c r="F12" s="7" t="n">
+        <v>958880</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>2277256</v>
@@ -1159,12 +1174,12 @@
       <c r="J12" s="3" t="n">
         <v>119855.5789473685</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>2469024.92631579</v>
+      <c r="K12" s="7" t="n">
+        <v>2397120</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -1182,7 +1197,7 @@
         <v>14797.50321649492</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>508047.6104329898</v>
+        <v>508047.6104329897</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>584987.7320000001</v>
@@ -1197,11 +1212,11 @@
         <v>18092.4040824743</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>621172.5401649487</v>
+        <v>621172.5401649486</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -1217,7 +1232,7 @@
         <v>1901140.641461387</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>96173249.63004522</v>
+        <v>96144483.23004521</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>103810057.398</v>
@@ -1230,7 +1245,7 @@
         <v>2198107.44560127</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>109188409.7889093</v>
+        <v>109116504.8625935</v>
       </c>
     </row>
   </sheetData>
@@ -1322,7 +1337,7 @@
         <v>741169.4321822003</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>37423291.97352767</v>
+        <v>37411380.77352767</v>
       </c>
       <c r="F2" s="3" t="n">
         <v>47680619.87800001</v>
@@ -1334,7 +1349,7 @@
         <v>999160.4878498167</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>50140173.77682532</v>
+        <v>50117477.94524637</v>
       </c>
     </row>
     <row r="3">
@@ -1353,7 +1368,7 @@
         <v>1157161.72372523</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>58543406.77177699</v>
+        <v>58525877.17177699</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>65872577.23999999</v>
@@ -1365,7 +1380,7 @@
         <v>1387725.216652304</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>69278111.53035188</v>
+        <v>69239012.66719398</v>
       </c>
     </row>
     <row r="4">
@@ -1384,7 +1399,7 @@
         <v>1571149.963020414</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>79482217.90655102</v>
+        <v>79459069.90655102</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>83816970.92600001</v>
@@ -1396,7 +1411,7 @@
         <v>1772784.979859993</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>88157448.5830358</v>
+        <v>88101946.68829896</v>
       </c>
     </row>
     <row r="5">
@@ -1415,7 +1430,7 @@
         <v>1901229.966849148</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>96177849.88751461</v>
+        <v>96149083.4875146</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>103814434.342</v>
@@ -1427,7 +1442,7 @@
         <v>2198196.770989016</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>109193010.0463787</v>
+        <v>109121105.1200629</v>
       </c>
     </row>
     <row r="6">
@@ -1446,7 +1461,7 @@
         <v>741169.4321822003</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>37423291.97352767</v>
+        <v>37411380.77352767</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>47679525.642</v>
@@ -1458,7 +1473,7 @@
         <v>999138.1565028802</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>50139023.71245797</v>
+        <v>50116327.88087902</v>
       </c>
     </row>
     <row r="7">
@@ -1477,7 +1492,7 @@
         <v>1157117.061031349</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>58541106.6430423</v>
+        <v>58523577.04304229</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>65870388.76799999</v>
@@ -1489,7 +1504,7 @@
         <v>1387680.553958431</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>69275811.40161718</v>
+        <v>69236712.53845929</v>
       </c>
     </row>
     <row r="8">
@@ -1508,7 +1523,7 @@
         <v>1571082.968979582</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>79478767.71344897</v>
+        <v>79455619.71344897</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>83813688.21800001</v>
@@ -1520,7 +1535,7 @@
         <v>1772717.985819191</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>88153998.38993376</v>
+        <v>88098496.49519692</v>
       </c>
     </row>
     <row r="9">
@@ -1539,7 +1554,7 @@
         <v>1901140.641461387</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>96173249.63004522</v>
+        <v>96144483.23004521</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>103810057.398</v>
@@ -1551,7 +1566,7 @@
         <v>2198107.44560127</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>109188409.7889093</v>
+        <v>109116504.8625935</v>
       </c>
     </row>
   </sheetData>
@@ -1578,7 +1593,7 @@
     <col width="27" customWidth="1" min="7" max="7"/>
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="41" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1653,8 +1668,8 @@
       <c r="E2" s="3" t="n">
         <v>43069.47368421053</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>44361.55789473684</v>
+      <c r="F2" s="10" t="n">
+        <v>43070</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1681,16 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1693,8 +1712,8 @@
       <c r="E3" s="3" t="n">
         <v>26220</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>27006.6</v>
+      <c r="F3" s="10" t="n">
+        <v>26220</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -1706,12 +1725,16 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1733,8 +1756,8 @@
       <c r="E4" s="3" t="n">
         <v>46820</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>48224.6</v>
+      <c r="F4" s="10" t="n">
+        <v>46820</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -1746,12 +1769,16 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1813,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1826,7 +1853,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1866,7 +1893,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1906,7 +1933,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1946,7 +1973,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -1986,7 +2013,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2026,7 +2053,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2066,7 +2093,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2106,7 +2133,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2146,7 +2173,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2186,7 +2213,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2226,7 +2253,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2266,7 +2293,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2306,7 +2333,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2346,7 +2373,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2386,7 +2413,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2426,7 +2453,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2466,7 +2493,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2506,7 +2533,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2546,7 +2573,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2586,7 +2613,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2626,7 +2653,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2666,7 +2693,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2706,7 +2733,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2746,7 +2773,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2786,7 +2813,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2826,7 +2853,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2866,7 +2893,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2906,7 +2933,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2946,7 +2973,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -2986,7 +3013,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3026,7 +3053,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3066,7 +3093,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="I37" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3106,7 +3133,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3146,7 +3173,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3186,7 +3213,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="I40" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3226,7 +3253,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3266,7 +3293,7 @@
           <t>8/11GHz 현재세대(확인됨)</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>확인됨</t>
         </is>
@@ -3306,7 +3333,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I43" s="7" t="inlineStr">
+      <c r="I43" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3346,7 +3373,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I44" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3386,7 +3413,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I45" s="7" t="inlineStr">
+      <c r="I45" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3426,7 +3453,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3466,7 +3493,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I47" s="7" t="inlineStr">
+      <c r="I47" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3506,7 +3533,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I48" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3546,7 +3573,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I49" s="7" t="inlineStr">
+      <c r="I49" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3586,7 +3613,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3626,7 +3653,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I51" s="7" t="inlineStr">
+      <c r="I51" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3666,7 +3693,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3706,7 +3733,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I53" s="7" t="inlineStr">
+      <c r="I53" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3746,7 +3773,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3786,7 +3813,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I55" s="7" t="inlineStr">
+      <c r="I55" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3826,7 +3853,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3866,7 +3893,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I57" s="7" t="inlineStr">
+      <c r="I57" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3906,7 +3933,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3946,7 +3973,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I59" s="7" t="inlineStr">
+      <c r="I59" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -3986,7 +4013,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="I60" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4026,7 +4053,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I61" s="7" t="inlineStr">
+      <c r="I61" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4066,7 +4093,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I62" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4106,7 +4133,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I63" s="7" t="inlineStr">
+      <c r="I63" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4146,7 +4173,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I64" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4186,7 +4213,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I65" s="7" t="inlineStr">
+      <c r="I65" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4226,7 +4253,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="I66" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4266,7 +4293,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I67" s="7" t="inlineStr">
+      <c r="I67" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4306,7 +4333,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I68" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4346,7 +4373,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I69" s="7" t="inlineStr">
+      <c r="I69" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4386,7 +4413,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I70" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4426,7 +4453,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I71" s="7" t="inlineStr">
+      <c r="I71" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4466,7 +4493,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I72" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4506,7 +4533,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I73" s="7" t="inlineStr">
+      <c r="I73" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4546,7 +4573,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4586,7 +4613,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I75" s="7" t="inlineStr">
+      <c r="I75" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4626,7 +4653,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="I76" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4666,7 +4693,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I77" s="7" t="inlineStr">
+      <c r="I77" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4706,7 +4733,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I78" s="7" t="inlineStr">
+      <c r="I78" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4746,7 +4773,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I79" s="7" t="inlineStr">
+      <c r="I79" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -4773,8 +4800,8 @@
       <c r="E80" s="3" t="n">
         <v>8631559.793814434</v>
       </c>
-      <c r="F80" s="3" t="n">
-        <v>8890506.587628867</v>
+      <c r="F80" s="10" t="n">
+        <v>8631560</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -4786,12 +4813,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I80" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr"/>
+      <c r="I80" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J80" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4813,8 +4844,8 @@
       <c r="E81" s="3" t="n">
         <v>8631559.793814434</v>
       </c>
-      <c r="F81" s="3" t="n">
-        <v>8890506.587628867</v>
+      <c r="F81" s="10" t="n">
+        <v>8631560</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
@@ -4826,12 +4857,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I81" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr"/>
+      <c r="I81" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J81" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4853,8 +4888,8 @@
       <c r="E82" s="3" t="n">
         <v>10927019.58762887</v>
       </c>
-      <c r="F82" s="3" t="n">
-        <v>11254830.17525773</v>
+      <c r="F82" s="10" t="n">
+        <v>10927020</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
@@ -4866,12 +4901,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I82" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr"/>
+      <c r="I82" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J82" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4893,8 +4932,8 @@
       <c r="E83" s="3" t="n">
         <v>10927019.58762887</v>
       </c>
-      <c r="F83" s="3" t="n">
-        <v>11254830.17525773</v>
+      <c r="F83" s="10" t="n">
+        <v>10927020</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -4906,12 +4945,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I83" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr"/>
+      <c r="I83" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J83" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4933,8 +4976,8 @@
       <c r="E84" s="3" t="n">
         <v>14163129.89690722</v>
       </c>
-      <c r="F84" s="3" t="n">
-        <v>14588023.79381444</v>
+      <c r="F84" s="10" t="n">
+        <v>14163130</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -4946,12 +4989,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I84" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr"/>
+      <c r="I84" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J84" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4973,8 +5020,8 @@
       <c r="E85" s="3" t="n">
         <v>14163129.89690722</v>
       </c>
-      <c r="F85" s="3" t="n">
-        <v>14588023.79381444</v>
+      <c r="F85" s="10" t="n">
+        <v>14163130</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -4986,12 +5033,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I85" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr"/>
+      <c r="I85" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J85" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -5010,11 +5061,11 @@
       <c r="D86" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E86" s="9" t="n">
+      <c r="E86" s="10" t="n">
         <v>3494770</v>
       </c>
       <c r="F86" s="3" t="n">
-        <v>3599613.1</v>
+        <v>3494770</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -5026,12 +5077,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I86" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J86" s="7" t="inlineStr">
+      <c r="I86" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J86" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5054,11 +5105,11 @@
       <c r="D87" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E87" s="9" t="n">
+      <c r="E87" s="10" t="n">
         <v>3494770</v>
       </c>
       <c r="F87" s="3" t="n">
-        <v>3599613.1</v>
+        <v>3494770</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -5070,12 +5121,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I87" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J87" s="7" t="inlineStr">
+      <c r="I87" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J87" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5101,8 +5152,8 @@
       <c r="E88" s="3" t="n">
         <v>4919189.69072165</v>
       </c>
-      <c r="F88" s="3" t="n">
-        <v>5066765.381443299</v>
+      <c r="F88" s="10" t="n">
+        <v>4919190</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -5114,12 +5165,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I88" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr"/>
+      <c r="I88" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J88" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -5141,8 +5196,8 @@
       <c r="E89" s="3" t="n">
         <v>4919189.69072165</v>
       </c>
-      <c r="F89" s="3" t="n">
-        <v>5066765.381443299</v>
+      <c r="F89" s="10" t="n">
+        <v>4919190</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -5154,12 +5209,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I89" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr"/>
+      <c r="I89" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J89" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -5178,11 +5237,11 @@
       <c r="D90" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E90" s="9" t="n">
+      <c r="E90" s="10" t="n">
         <v>6542350</v>
       </c>
       <c r="F90" s="3" t="n">
-        <v>6738620.5</v>
+        <v>6542350</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -5194,12 +5253,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I90" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr">
+      <c r="I90" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J90" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5222,11 +5281,11 @@
       <c r="D91" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E91" s="9" t="n">
+      <c r="E91" s="10" t="n">
         <v>6542350</v>
       </c>
       <c r="F91" s="3" t="n">
-        <v>6738620.5</v>
+        <v>6542350</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5238,12 +5297,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I91" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J91" s="7" t="inlineStr">
+      <c r="I91" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J91" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -5282,7 +5341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I92" s="7" t="inlineStr">
+      <c r="I92" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5322,7 +5381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I93" s="7" t="inlineStr">
+      <c r="I93" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5362,7 +5421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I94" s="7" t="inlineStr">
+      <c r="I94" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5402,7 +5461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I95" s="7" t="inlineStr">
+      <c r="I95" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5442,7 +5501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I96" s="7" t="inlineStr">
+      <c r="I96" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5482,7 +5541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I97" s="7" t="inlineStr">
+      <c r="I97" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5522,7 +5581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I98" s="7" t="inlineStr">
+      <c r="I98" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5562,7 +5621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I99" s="7" t="inlineStr">
+      <c r="I99" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5602,7 +5661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I100" s="7" t="inlineStr">
+      <c r="I100" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5642,7 +5701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I101" s="7" t="inlineStr">
+      <c r="I101" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5682,7 +5741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I102" s="7" t="inlineStr">
+      <c r="I102" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5722,7 +5781,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I103" s="7" t="inlineStr">
+      <c r="I103" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5762,7 +5821,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I104" s="7" t="inlineStr">
+      <c r="I104" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5802,7 +5861,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I105" s="7" t="inlineStr">
+      <c r="I105" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5842,7 +5901,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I106" s="7" t="inlineStr">
+      <c r="I106" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5882,7 +5941,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I107" s="7" t="inlineStr">
+      <c r="I107" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5922,7 +5981,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I108" s="7" t="inlineStr">
+      <c r="I108" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -5962,7 +6021,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I109" s="7" t="inlineStr">
+      <c r="I109" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6002,7 +6061,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I110" s="7" t="inlineStr">
+      <c r="I110" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6042,7 +6101,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I111" s="7" t="inlineStr">
+      <c r="I111" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6082,7 +6141,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I112" s="7" t="inlineStr">
+      <c r="I112" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6122,7 +6181,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I113" s="7" t="inlineStr">
+      <c r="I113" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6162,7 +6221,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I114" s="7" t="inlineStr">
+      <c r="I114" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6202,7 +6261,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I115" s="7" t="inlineStr">
+      <c r="I115" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6242,7 +6301,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I116" s="7" t="inlineStr">
+      <c r="I116" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6282,7 +6341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I117" s="7" t="inlineStr">
+      <c r="I117" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6322,7 +6381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I118" s="7" t="inlineStr">
+      <c r="I118" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6362,7 +6421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I119" s="7" t="inlineStr">
+      <c r="I119" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6402,7 +6461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I120" s="7" t="inlineStr">
+      <c r="I120" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6442,7 +6501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I121" s="7" t="inlineStr">
+      <c r="I121" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6482,7 +6541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I122" s="7" t="inlineStr">
+      <c r="I122" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6522,7 +6581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I123" s="7" t="inlineStr">
+      <c r="I123" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6562,7 +6621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I124" s="7" t="inlineStr">
+      <c r="I124" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6602,7 +6661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I125" s="7" t="inlineStr">
+      <c r="I125" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6642,7 +6701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I126" s="7" t="inlineStr">
+      <c r="I126" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6682,7 +6741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I127" s="7" t="inlineStr">
+      <c r="I127" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6722,7 +6781,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I128" s="7" t="inlineStr">
+      <c r="I128" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6762,7 +6821,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I129" s="7" t="inlineStr">
+      <c r="I129" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6802,7 +6861,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I130" s="7" t="inlineStr">
+      <c r="I130" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6842,7 +6901,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I131" s="7" t="inlineStr">
+      <c r="I131" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6882,7 +6941,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I132" s="7" t="inlineStr">
+      <c r="I132" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6922,7 +6981,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I133" s="7" t="inlineStr">
+      <c r="I133" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -6962,7 +7021,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I134" s="7" t="inlineStr">
+      <c r="I134" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7002,7 +7061,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I135" s="7" t="inlineStr">
+      <c r="I135" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7042,7 +7101,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I136" s="7" t="inlineStr">
+      <c r="I136" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7082,7 +7141,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I137" s="7" t="inlineStr">
+      <c r="I137" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7122,7 +7181,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I138" s="7" t="inlineStr">
+      <c r="I138" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7162,7 +7221,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I139" s="7" t="inlineStr">
+      <c r="I139" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7202,7 +7261,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I140" s="7" t="inlineStr">
+      <c r="I140" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7242,7 +7301,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I141" s="7" t="inlineStr">
+      <c r="I141" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7282,7 +7341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I142" s="7" t="inlineStr">
+      <c r="I142" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7322,7 +7381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I143" s="7" t="inlineStr">
+      <c r="I143" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7362,7 +7421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I144" s="7" t="inlineStr">
+      <c r="I144" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7402,7 +7461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I145" s="7" t="inlineStr">
+      <c r="I145" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7442,7 +7501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I146" s="7" t="inlineStr">
+      <c r="I146" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7482,7 +7541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I147" s="7" t="inlineStr">
+      <c r="I147" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7522,7 +7581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I148" s="7" t="inlineStr">
+      <c r="I148" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7562,7 +7621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I149" s="7" t="inlineStr">
+      <c r="I149" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7602,7 +7661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I150" s="7" t="inlineStr">
+      <c r="I150" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7642,7 +7701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I151" s="7" t="inlineStr">
+      <c r="I151" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7682,7 +7741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I152" s="7" t="inlineStr">
+      <c r="I152" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7722,7 +7781,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I153" s="7" t="inlineStr">
+      <c r="I153" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7762,7 +7821,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I154" s="7" t="inlineStr">
+      <c r="I154" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7802,7 +7861,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I155" s="7" t="inlineStr">
+      <c r="I155" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7842,7 +7901,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I156" s="7" t="inlineStr">
+      <c r="I156" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7882,7 +7941,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I157" s="7" t="inlineStr">
+      <c r="I157" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7922,7 +7981,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I158" s="7" t="inlineStr">
+      <c r="I158" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -7962,7 +8021,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I159" s="7" t="inlineStr">
+      <c r="I159" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8002,7 +8061,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I160" s="7" t="inlineStr">
+      <c r="I160" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8042,7 +8101,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I161" s="7" t="inlineStr">
+      <c r="I161" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8082,7 +8141,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I162" s="7" t="inlineStr">
+      <c r="I162" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8122,7 +8181,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I163" s="7" t="inlineStr">
+      <c r="I163" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8162,7 +8221,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I164" s="7" t="inlineStr">
+      <c r="I164" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8202,7 +8261,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I165" s="7" t="inlineStr">
+      <c r="I165" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8242,7 +8301,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I166" s="7" t="inlineStr">
+      <c r="I166" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8282,7 +8341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I167" s="7" t="inlineStr">
+      <c r="I167" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8322,7 +8381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I168" s="7" t="inlineStr">
+      <c r="I168" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8362,7 +8421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I169" s="7" t="inlineStr">
+      <c r="I169" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8402,7 +8461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I170" s="7" t="inlineStr">
+      <c r="I170" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8442,7 +8501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I171" s="7" t="inlineStr">
+      <c r="I171" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8482,7 +8541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I172" s="7" t="inlineStr">
+      <c r="I172" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8522,7 +8581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I173" s="7" t="inlineStr">
+      <c r="I173" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8562,7 +8621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I174" s="7" t="inlineStr">
+      <c r="I174" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8602,7 +8661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I175" s="7" t="inlineStr">
+      <c r="I175" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8642,7 +8701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I176" s="7" t="inlineStr">
+      <c r="I176" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8682,7 +8741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I177" s="7" t="inlineStr">
+      <c r="I177" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8722,7 +8781,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I178" s="7" t="inlineStr">
+      <c r="I178" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8762,7 +8821,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I179" s="7" t="inlineStr">
+      <c r="I179" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8802,7 +8861,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I180" s="7" t="inlineStr">
+      <c r="I180" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8842,7 +8901,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I181" s="7" t="inlineStr">
+      <c r="I181" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8882,7 +8941,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I182" s="7" t="inlineStr">
+      <c r="I182" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8922,7 +8981,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I183" s="7" t="inlineStr">
+      <c r="I183" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -8962,7 +9021,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I184" s="7" t="inlineStr">
+      <c r="I184" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9002,7 +9061,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I185" s="7" t="inlineStr">
+      <c r="I185" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9042,7 +9101,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I186" s="7" t="inlineStr">
+      <c r="I186" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9082,7 +9141,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I187" s="7" t="inlineStr">
+      <c r="I187" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9122,7 +9181,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I188" s="7" t="inlineStr">
+      <c r="I188" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9162,7 +9221,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I189" s="7" t="inlineStr">
+      <c r="I189" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9202,7 +9261,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I190" s="7" t="inlineStr">
+      <c r="I190" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9242,7 +9301,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I191" s="7" t="inlineStr">
+      <c r="I191" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9282,7 +9341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I192" s="7" t="inlineStr">
+      <c r="I192" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9322,7 +9381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I193" s="7" t="inlineStr">
+      <c r="I193" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9362,7 +9421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I194" s="7" t="inlineStr">
+      <c r="I194" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9402,7 +9461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I195" s="7" t="inlineStr">
+      <c r="I195" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9442,7 +9501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I196" s="7" t="inlineStr">
+      <c r="I196" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9482,7 +9541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I197" s="7" t="inlineStr">
+      <c r="I197" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9522,7 +9581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I198" s="7" t="inlineStr">
+      <c r="I198" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9562,7 +9621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I199" s="7" t="inlineStr">
+      <c r="I199" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9602,7 +9661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I200" s="7" t="inlineStr">
+      <c r="I200" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9642,7 +9701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I201" s="7" t="inlineStr">
+      <c r="I201" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9682,7 +9741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I202" s="7" t="inlineStr">
+      <c r="I202" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9722,7 +9781,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I203" s="7" t="inlineStr">
+      <c r="I203" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9762,7 +9821,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I204" s="7" t="inlineStr">
+      <c r="I204" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9802,7 +9861,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I205" s="7" t="inlineStr">
+      <c r="I205" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9842,7 +9901,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I206" s="7" t="inlineStr">
+      <c r="I206" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9882,7 +9941,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I207" s="7" t="inlineStr">
+      <c r="I207" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9922,7 +9981,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I208" s="7" t="inlineStr">
+      <c r="I208" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -9962,7 +10021,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I209" s="7" t="inlineStr">
+      <c r="I209" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10002,7 +10061,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I210" s="7" t="inlineStr">
+      <c r="I210" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10042,7 +10101,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I211" s="7" t="inlineStr">
+      <c r="I211" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10082,7 +10141,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I212" s="7" t="inlineStr">
+      <c r="I212" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10122,7 +10181,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I213" s="7" t="inlineStr">
+      <c r="I213" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10162,7 +10221,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I214" s="7" t="inlineStr">
+      <c r="I214" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10202,7 +10261,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I215" s="7" t="inlineStr">
+      <c r="I215" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10242,7 +10301,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I216" s="7" t="inlineStr">
+      <c r="I216" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10282,7 +10341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I217" s="7" t="inlineStr">
+      <c r="I217" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10322,7 +10381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I218" s="7" t="inlineStr">
+      <c r="I218" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10362,7 +10421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I219" s="7" t="inlineStr">
+      <c r="I219" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10402,7 +10461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I220" s="7" t="inlineStr">
+      <c r="I220" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10442,7 +10501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I221" s="7" t="inlineStr">
+      <c r="I221" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10482,7 +10541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I222" s="7" t="inlineStr">
+      <c r="I222" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10522,7 +10581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I223" s="7" t="inlineStr">
+      <c r="I223" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10562,7 +10621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I224" s="7" t="inlineStr">
+      <c r="I224" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10602,7 +10661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I225" s="7" t="inlineStr">
+      <c r="I225" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10642,7 +10701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I226" s="7" t="inlineStr">
+      <c r="I226" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10682,7 +10741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I227" s="7" t="inlineStr">
+      <c r="I227" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10722,7 +10781,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I228" s="7" t="inlineStr">
+      <c r="I228" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10762,7 +10821,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I229" s="7" t="inlineStr">
+      <c r="I229" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10802,7 +10861,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I230" s="7" t="inlineStr">
+      <c r="I230" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10842,7 +10901,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I231" s="7" t="inlineStr">
+      <c r="I231" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10882,7 +10941,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I232" s="7" t="inlineStr">
+      <c r="I232" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10922,7 +10981,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I233" s="7" t="inlineStr">
+      <c r="I233" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -10962,7 +11021,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I234" s="7" t="inlineStr">
+      <c r="I234" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11002,7 +11061,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I235" s="7" t="inlineStr">
+      <c r="I235" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11042,7 +11101,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I236" s="7" t="inlineStr">
+      <c r="I236" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11082,7 +11141,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I237" s="7" t="inlineStr">
+      <c r="I237" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11122,7 +11181,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I238" s="7" t="inlineStr">
+      <c r="I238" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11162,7 +11221,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I239" s="7" t="inlineStr">
+      <c r="I239" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11202,7 +11261,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I240" s="7" t="inlineStr">
+      <c r="I240" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11242,7 +11301,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I241" s="7" t="inlineStr">
+      <c r="I241" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11282,7 +11341,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I242" s="7" t="inlineStr">
+      <c r="I242" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11322,7 +11381,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I243" s="7" t="inlineStr">
+      <c r="I243" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11362,7 +11421,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I244" s="7" t="inlineStr">
+      <c r="I244" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11402,7 +11461,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I245" s="7" t="inlineStr">
+      <c r="I245" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11442,7 +11501,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I246" s="7" t="inlineStr">
+      <c r="I246" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11482,7 +11541,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I247" s="7" t="inlineStr">
+      <c r="I247" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11522,7 +11581,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I248" s="7" t="inlineStr">
+      <c r="I248" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11562,7 +11621,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I249" s="7" t="inlineStr">
+      <c r="I249" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11602,7 +11661,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I250" s="7" t="inlineStr">
+      <c r="I250" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11642,7 +11701,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I251" s="7" t="inlineStr">
+      <c r="I251" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11682,7 +11741,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I252" s="7" t="inlineStr">
+      <c r="I252" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11706,11 +11765,11 @@
       <c r="D253" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E253" s="9" t="n">
+      <c r="E253" s="10" t="n">
         <v>3024380</v>
       </c>
       <c r="F253" s="3" t="n">
-        <v>3115111.4</v>
+        <v>3024380</v>
       </c>
       <c r="G253" s="2" t="inlineStr">
         <is>
@@ -11722,12 +11781,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I253" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J253" s="7" t="inlineStr">
+      <c r="I253" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J253" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -11750,11 +11809,11 @@
       <c r="D254" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E254" s="9" t="n">
+      <c r="E254" s="10" t="n">
         <v>3024380</v>
       </c>
       <c r="F254" s="3" t="n">
-        <v>3115111.4</v>
+        <v>3024380</v>
       </c>
       <c r="G254" s="2" t="inlineStr">
         <is>
@@ -11766,12 +11825,12 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I254" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J254" s="7" t="inlineStr">
+      <c r="I254" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J254" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -11797,8 +11856,8 @@
       <c r="E255" s="3" t="n">
         <v>5343189.69072165</v>
       </c>
-      <c r="F255" s="3" t="n">
-        <v>5503485.381443299</v>
+      <c r="F255" s="10" t="n">
+        <v>5343190</v>
       </c>
       <c r="G255" s="2" t="inlineStr">
         <is>
@@ -11810,12 +11869,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I255" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J255" s="2" t="inlineStr"/>
+      <c r="I255" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J255" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="inlineStr">
@@ -11837,8 +11900,8 @@
       <c r="E256" s="3" t="n">
         <v>5343189.69072165</v>
       </c>
-      <c r="F256" s="3" t="n">
-        <v>5503485.381443299</v>
+      <c r="F256" s="10" t="n">
+        <v>5343190</v>
       </c>
       <c r="G256" s="2" t="inlineStr">
         <is>
@@ -11850,12 +11913,16 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I256" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J256" s="2" t="inlineStr"/>
+      <c r="I256" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J256" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="inlineStr">
@@ -11890,7 +11957,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I257" s="7" t="inlineStr">
+      <c r="I257" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11930,7 +11997,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I258" s="7" t="inlineStr">
+      <c r="I258" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -11970,7 +12037,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I259" s="7" t="inlineStr">
+      <c r="I259" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12010,7 +12077,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I260" s="7" t="inlineStr">
+      <c r="I260" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12050,7 +12117,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I261" s="7" t="inlineStr">
+      <c r="I261" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12090,7 +12157,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I262" s="7" t="inlineStr">
+      <c r="I262" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12130,7 +12197,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I263" s="7" t="inlineStr">
+      <c r="I263" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12170,7 +12237,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I264" s="7" t="inlineStr">
+      <c r="I264" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12210,7 +12277,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I265" s="7" t="inlineStr">
+      <c r="I265" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12250,7 +12317,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I266" s="7" t="inlineStr">
+      <c r="I266" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12290,7 +12357,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I267" s="7" t="inlineStr">
+      <c r="I267" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12330,7 +12397,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I268" s="7" t="inlineStr">
+      <c r="I268" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12370,7 +12437,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I269" s="7" t="inlineStr">
+      <c r="I269" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12410,7 +12477,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I270" s="7" t="inlineStr">
+      <c r="I270" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12450,7 +12517,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I271" s="7" t="inlineStr">
+      <c r="I271" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12490,7 +12557,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I272" s="7" t="inlineStr">
+      <c r="I272" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12530,7 +12597,7 @@
           <t>8/11GHz 현재세대 추정</t>
         </is>
       </c>
-      <c r="I273" s="7" t="inlineStr">
+      <c r="I273" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12565,12 +12632,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H274" s="10" t="inlineStr">
+      <c r="H274" s="11" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I274" s="7" t="inlineStr">
+      <c r="I274" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12605,12 +12672,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H275" s="10" t="inlineStr">
+      <c r="H275" s="11" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I275" s="7" t="inlineStr">
+      <c r="I275" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12645,12 +12712,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H276" s="10" t="inlineStr">
+      <c r="H276" s="11" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I276" s="7" t="inlineStr">
+      <c r="I276" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12685,12 +12752,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H277" s="10" t="inlineStr">
+      <c r="H277" s="11" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I277" s="7" t="inlineStr">
+      <c r="I277" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12725,12 +12792,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H278" s="10" t="inlineStr">
+      <c r="H278" s="11" t="inlineStr">
         <is>
           <t>비무선 제품(확인 필요)</t>
         </is>
       </c>
-      <c r="I278" s="7" t="inlineStr">
+      <c r="I278" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12765,12 +12832,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H279" s="10" t="inlineStr">
+      <c r="H279" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I279" s="7" t="inlineStr">
+      <c r="I279" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12805,12 +12872,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H280" s="10" t="inlineStr">
+      <c r="H280" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I280" s="7" t="inlineStr">
+      <c r="I280" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12845,12 +12912,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H281" s="10" t="inlineStr">
+      <c r="H281" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I281" s="7" t="inlineStr">
+      <c r="I281" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12885,12 +12952,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H282" s="10" t="inlineStr">
+      <c r="H282" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I282" s="7" t="inlineStr">
+      <c r="I282" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12925,12 +12992,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H283" s="10" t="inlineStr">
+      <c r="H283" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I283" s="7" t="inlineStr">
+      <c r="I283" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -12965,12 +13032,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H284" s="10" t="inlineStr">
+      <c r="H284" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I284" s="7" t="inlineStr">
+      <c r="I284" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13005,12 +13072,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H285" s="10" t="inlineStr">
+      <c r="H285" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I285" s="7" t="inlineStr">
+      <c r="I285" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13045,12 +13112,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H286" s="10" t="inlineStr">
+      <c r="H286" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I286" s="7" t="inlineStr">
+      <c r="I286" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13085,12 +13152,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H287" s="10" t="inlineStr">
+      <c r="H287" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I287" s="7" t="inlineStr">
+      <c r="I287" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13125,12 +13192,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H288" s="10" t="inlineStr">
+      <c r="H288" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I288" s="7" t="inlineStr">
+      <c r="I288" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13165,12 +13232,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H289" s="10" t="inlineStr">
+      <c r="H289" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I289" s="7" t="inlineStr">
+      <c r="I289" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13205,12 +13272,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H290" s="10" t="inlineStr">
+      <c r="H290" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I290" s="7" t="inlineStr">
+      <c r="I290" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13245,12 +13312,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H291" s="10" t="inlineStr">
+      <c r="H291" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I291" s="7" t="inlineStr">
+      <c r="I291" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13285,12 +13352,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H292" s="10" t="inlineStr">
+      <c r="H292" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I292" s="7" t="inlineStr">
+      <c r="I292" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13325,12 +13392,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H293" s="10" t="inlineStr">
+      <c r="H293" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I293" s="7" t="inlineStr">
+      <c r="I293" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13365,12 +13432,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H294" s="10" t="inlineStr">
+      <c r="H294" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I294" s="7" t="inlineStr">
+      <c r="I294" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13405,12 +13472,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H295" s="10" t="inlineStr">
+      <c r="H295" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I295" s="7" t="inlineStr">
+      <c r="I295" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13445,12 +13512,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H296" s="10" t="inlineStr">
+      <c r="H296" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I296" s="7" t="inlineStr">
+      <c r="I296" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13485,12 +13552,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H297" s="10" t="inlineStr">
+      <c r="H297" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I297" s="7" t="inlineStr">
+      <c r="I297" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13525,12 +13592,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H298" s="10" t="inlineStr">
+      <c r="H298" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I298" s="7" t="inlineStr">
+      <c r="I298" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13565,12 +13632,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H299" s="10" t="inlineStr">
+      <c r="H299" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I299" s="7" t="inlineStr">
+      <c r="I299" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13605,12 +13672,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H300" s="10" t="inlineStr">
+      <c r="H300" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I300" s="7" t="inlineStr">
+      <c r="I300" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13645,12 +13712,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H301" s="10" t="inlineStr">
+      <c r="H301" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I301" s="7" t="inlineStr">
+      <c r="I301" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13685,12 +13752,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H302" s="10" t="inlineStr">
+      <c r="H302" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I302" s="7" t="inlineStr">
+      <c r="I302" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13725,12 +13792,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H303" s="10" t="inlineStr">
+      <c r="H303" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I303" s="7" t="inlineStr">
+      <c r="I303" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13765,12 +13832,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H304" s="10" t="inlineStr">
+      <c r="H304" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I304" s="7" t="inlineStr">
+      <c r="I304" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13805,12 +13872,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H305" s="10" t="inlineStr">
+      <c r="H305" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I305" s="7" t="inlineStr">
+      <c r="I305" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13845,12 +13912,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H306" s="10" t="inlineStr">
+      <c r="H306" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I306" s="7" t="inlineStr">
+      <c r="I306" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13885,12 +13952,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H307" s="10" t="inlineStr">
+      <c r="H307" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I307" s="7" t="inlineStr">
+      <c r="I307" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13925,12 +13992,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H308" s="10" t="inlineStr">
+      <c r="H308" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I308" s="7" t="inlineStr">
+      <c r="I308" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -13965,12 +14032,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H309" s="10" t="inlineStr">
+      <c r="H309" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I309" s="7" t="inlineStr">
+      <c r="I309" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14005,12 +14072,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H310" s="10" t="inlineStr">
+      <c r="H310" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I310" s="7" t="inlineStr">
+      <c r="I310" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14045,12 +14112,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H311" s="10" t="inlineStr">
+      <c r="H311" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I311" s="7" t="inlineStr">
+      <c r="I311" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14085,12 +14152,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H312" s="10" t="inlineStr">
+      <c r="H312" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I312" s="7" t="inlineStr">
+      <c r="I312" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14125,12 +14192,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H313" s="10" t="inlineStr">
+      <c r="H313" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I313" s="7" t="inlineStr">
+      <c r="I313" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14165,12 +14232,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H314" s="10" t="inlineStr">
+      <c r="H314" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I314" s="7" t="inlineStr">
+      <c r="I314" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14205,12 +14272,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H315" s="10" t="inlineStr">
+      <c r="H315" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I315" s="7" t="inlineStr">
+      <c r="I315" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14245,12 +14312,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H316" s="10" t="inlineStr">
+      <c r="H316" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I316" s="7" t="inlineStr">
+      <c r="I316" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14285,12 +14352,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H317" s="10" t="inlineStr">
+      <c r="H317" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I317" s="7" t="inlineStr">
+      <c r="I317" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14325,12 +14392,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H318" s="10" t="inlineStr">
+      <c r="H318" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I318" s="7" t="inlineStr">
+      <c r="I318" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14365,12 +14432,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H319" s="10" t="inlineStr">
+      <c r="H319" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I319" s="7" t="inlineStr">
+      <c r="I319" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14405,12 +14472,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H320" s="10" t="inlineStr">
+      <c r="H320" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I320" s="7" t="inlineStr">
+      <c r="I320" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14445,12 +14512,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H321" s="10" t="inlineStr">
+      <c r="H321" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I321" s="7" t="inlineStr">
+      <c r="I321" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14485,12 +14552,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H322" s="10" t="inlineStr">
+      <c r="H322" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I322" s="7" t="inlineStr">
+      <c r="I322" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14525,12 +14592,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H323" s="10" t="inlineStr">
+      <c r="H323" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I323" s="7" t="inlineStr">
+      <c r="I323" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14565,12 +14632,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H324" s="10" t="inlineStr">
+      <c r="H324" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I324" s="7" t="inlineStr">
+      <c r="I324" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14605,12 +14672,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H325" s="10" t="inlineStr">
+      <c r="H325" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I325" s="7" t="inlineStr">
+      <c r="I325" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14645,12 +14712,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H326" s="10" t="inlineStr">
+      <c r="H326" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I326" s="7" t="inlineStr">
+      <c r="I326" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14685,12 +14752,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H327" s="10" t="inlineStr">
+      <c r="H327" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I327" s="7" t="inlineStr">
+      <c r="I327" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14725,12 +14792,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H328" s="10" t="inlineStr">
+      <c r="H328" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I328" s="7" t="inlineStr">
+      <c r="I328" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14765,12 +14832,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H329" s="10" t="inlineStr">
+      <c r="H329" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I329" s="7" t="inlineStr">
+      <c r="I329" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14805,12 +14872,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H330" s="10" t="inlineStr">
+      <c r="H330" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I330" s="7" t="inlineStr">
+      <c r="I330" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14845,12 +14912,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H331" s="10" t="inlineStr">
+      <c r="H331" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I331" s="7" t="inlineStr">
+      <c r="I331" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14885,12 +14952,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H332" s="10" t="inlineStr">
+      <c r="H332" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I332" s="7" t="inlineStr">
+      <c r="I332" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14925,12 +14992,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H333" s="10" t="inlineStr">
+      <c r="H333" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I333" s="7" t="inlineStr">
+      <c r="I333" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -14965,12 +15032,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H334" s="10" t="inlineStr">
+      <c r="H334" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I334" s="7" t="inlineStr">
+      <c r="I334" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15005,12 +15072,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H335" s="10" t="inlineStr">
+      <c r="H335" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I335" s="7" t="inlineStr">
+      <c r="I335" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15045,12 +15112,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H336" s="10" t="inlineStr">
+      <c r="H336" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I336" s="7" t="inlineStr">
+      <c r="I336" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15085,12 +15152,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H337" s="10" t="inlineStr">
+      <c r="H337" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I337" s="7" t="inlineStr">
+      <c r="I337" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15125,12 +15192,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H338" s="10" t="inlineStr">
+      <c r="H338" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I338" s="7" t="inlineStr">
+      <c r="I338" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15165,12 +15232,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H339" s="10" t="inlineStr">
+      <c r="H339" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I339" s="7" t="inlineStr">
+      <c r="I339" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15205,12 +15272,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H340" s="10" t="inlineStr">
+      <c r="H340" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I340" s="7" t="inlineStr">
+      <c r="I340" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15245,12 +15312,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H341" s="10" t="inlineStr">
+      <c r="H341" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I341" s="7" t="inlineStr">
+      <c r="I341" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15285,12 +15352,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H342" s="10" t="inlineStr">
+      <c r="H342" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I342" s="7" t="inlineStr">
+      <c r="I342" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15325,12 +15392,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H343" s="10" t="inlineStr">
+      <c r="H343" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I343" s="7" t="inlineStr">
+      <c r="I343" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15365,12 +15432,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H344" s="10" t="inlineStr">
+      <c r="H344" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I344" s="7" t="inlineStr">
+      <c r="I344" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15405,12 +15472,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H345" s="10" t="inlineStr">
+      <c r="H345" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I345" s="7" t="inlineStr">
+      <c r="I345" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15445,12 +15512,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H346" s="10" t="inlineStr">
+      <c r="H346" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I346" s="7" t="inlineStr">
+      <c r="I346" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15485,12 +15552,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H347" s="10" t="inlineStr">
+      <c r="H347" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I347" s="7" t="inlineStr">
+      <c r="I347" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15525,12 +15592,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H348" s="10" t="inlineStr">
+      <c r="H348" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I348" s="7" t="inlineStr">
+      <c r="I348" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15565,12 +15632,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H349" s="10" t="inlineStr">
+      <c r="H349" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I349" s="7" t="inlineStr">
+      <c r="I349" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15605,12 +15672,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H350" s="10" t="inlineStr">
+      <c r="H350" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I350" s="7" t="inlineStr">
+      <c r="I350" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15645,12 +15712,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H351" s="10" t="inlineStr">
+      <c r="H351" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I351" s="7" t="inlineStr">
+      <c r="I351" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15685,12 +15752,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H352" s="10" t="inlineStr">
+      <c r="H352" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I352" s="7" t="inlineStr">
+      <c r="I352" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15725,12 +15792,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H353" s="10" t="inlineStr">
+      <c r="H353" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I353" s="7" t="inlineStr">
+      <c r="I353" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15765,12 +15832,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H354" s="10" t="inlineStr">
+      <c r="H354" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I354" s="7" t="inlineStr">
+      <c r="I354" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15805,12 +15872,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H355" s="10" t="inlineStr">
+      <c r="H355" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I355" s="7" t="inlineStr">
+      <c r="I355" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15845,12 +15912,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H356" s="10" t="inlineStr">
+      <c r="H356" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I356" s="7" t="inlineStr">
+      <c r="I356" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15885,12 +15952,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H357" s="10" t="inlineStr">
+      <c r="H357" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I357" s="7" t="inlineStr">
+      <c r="I357" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15925,12 +15992,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H358" s="10" t="inlineStr">
+      <c r="H358" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I358" s="7" t="inlineStr">
+      <c r="I358" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -15965,12 +16032,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H359" s="10" t="inlineStr">
+      <c r="H359" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I359" s="7" t="inlineStr">
+      <c r="I359" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16005,12 +16072,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H360" s="10" t="inlineStr">
+      <c r="H360" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I360" s="7" t="inlineStr">
+      <c r="I360" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16045,12 +16112,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H361" s="10" t="inlineStr">
+      <c r="H361" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I361" s="7" t="inlineStr">
+      <c r="I361" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16085,12 +16152,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H362" s="10" t="inlineStr">
+      <c r="H362" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I362" s="7" t="inlineStr">
+      <c r="I362" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16125,12 +16192,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H363" s="10" t="inlineStr">
+      <c r="H363" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I363" s="7" t="inlineStr">
+      <c r="I363" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16165,12 +16232,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H364" s="10" t="inlineStr">
+      <c r="H364" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I364" s="7" t="inlineStr">
+      <c r="I364" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16205,12 +16272,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H365" s="10" t="inlineStr">
+      <c r="H365" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I365" s="7" t="inlineStr">
+      <c r="I365" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16245,12 +16312,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H366" s="10" t="inlineStr">
+      <c r="H366" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I366" s="7" t="inlineStr">
+      <c r="I366" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16285,12 +16352,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H367" s="10" t="inlineStr">
+      <c r="H367" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I367" s="7" t="inlineStr">
+      <c r="I367" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16314,28 +16381,28 @@
       <c r="D368" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E368" s="9" t="n">
+      <c r="E368" s="10" t="n">
         <v>207020</v>
       </c>
       <c r="F368" s="3" t="n">
-        <v>213230.6</v>
+        <v>207020</v>
       </c>
       <c r="G368" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H368" s="10" t="inlineStr">
+      <c r="H368" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I368" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J368" s="7" t="inlineStr">
+      <c r="I368" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J368" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -16369,12 +16436,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H369" s="10" t="inlineStr">
+      <c r="H369" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I369" s="7" t="inlineStr">
+      <c r="I369" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16409,12 +16476,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H370" s="10" t="inlineStr">
+      <c r="H370" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I370" s="7" t="inlineStr">
+      <c r="I370" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16449,12 +16516,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H371" s="10" t="inlineStr">
+      <c r="H371" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I371" s="7" t="inlineStr">
+      <c r="I371" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16489,12 +16556,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H372" s="10" t="inlineStr">
+      <c r="H372" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I372" s="7" t="inlineStr">
+      <c r="I372" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16529,12 +16596,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H373" s="10" t="inlineStr">
+      <c r="H373" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I373" s="7" t="inlineStr">
+      <c r="I373" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16569,12 +16636,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H374" s="10" t="inlineStr">
+      <c r="H374" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I374" s="7" t="inlineStr">
+      <c r="I374" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16609,12 +16676,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H375" s="10" t="inlineStr">
+      <c r="H375" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I375" s="7" t="inlineStr">
+      <c r="I375" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16649,12 +16716,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H376" s="10" t="inlineStr">
+      <c r="H376" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I376" s="7" t="inlineStr">
+      <c r="I376" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16689,12 +16756,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H377" s="10" t="inlineStr">
+      <c r="H377" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I377" s="7" t="inlineStr">
+      <c r="I377" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16729,12 +16796,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H378" s="10" t="inlineStr">
+      <c r="H378" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I378" s="7" t="inlineStr">
+      <c r="I378" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -16761,25 +16828,29 @@
       <c r="E379" s="3" t="n">
         <v>11774429.89690722</v>
       </c>
-      <c r="F379" s="3" t="n">
-        <v>12127662.79381443</v>
+      <c r="F379" s="10" t="n">
+        <v>11774430</v>
       </c>
       <c r="G379" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H379" s="10" t="inlineStr">
+      <c r="H379" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I379" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J379" s="2" t="inlineStr"/>
+      <c r="I379" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J379" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="2" t="inlineStr">
@@ -16801,25 +16872,29 @@
       <c r="E380" s="3" t="n">
         <v>13804819.58762887</v>
       </c>
-      <c r="F380" s="3" t="n">
-        <v>14218964.17525773</v>
+      <c r="F380" s="10" t="n">
+        <v>13804820</v>
       </c>
       <c r="G380" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H380" s="10" t="inlineStr">
+      <c r="H380" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I380" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J380" s="2" t="inlineStr"/>
+      <c r="I380" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J380" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="2" t="inlineStr">
@@ -16841,25 +16916,29 @@
       <c r="E381" s="3" t="n">
         <v>17633829.89690722</v>
       </c>
-      <c r="F381" s="3" t="n">
-        <v>18162844.79381444</v>
+      <c r="F381" s="10" t="n">
+        <v>17633830</v>
       </c>
       <c r="G381" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H381" s="10" t="inlineStr">
+      <c r="H381" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I381" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J381" s="2" t="inlineStr"/>
+      <c r="I381" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J381" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="2" t="inlineStr">
@@ -16881,25 +16960,29 @@
       <c r="E382" s="3" t="n">
         <v>7187029.896907217</v>
       </c>
-      <c r="F382" s="3" t="n">
-        <v>7402640.793814434</v>
+      <c r="F382" s="10" t="n">
+        <v>7187030</v>
       </c>
       <c r="G382" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H382" s="10" t="inlineStr">
+      <c r="H382" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I382" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J382" s="2" t="inlineStr"/>
+      <c r="I382" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J382" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="2" t="inlineStr">
@@ -16918,28 +17001,28 @@
       <c r="D383" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E383" s="9" t="n">
+      <c r="E383" s="10" t="n">
         <v>8738110</v>
       </c>
       <c r="F383" s="3" t="n">
-        <v>9000253.300000001</v>
+        <v>8738110</v>
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H383" s="10" t="inlineStr">
+      <c r="H383" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I383" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J383" s="7" t="inlineStr">
+      <c r="I383" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J383" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -16965,25 +17048,29 @@
       <c r="E384" s="3" t="n">
         <v>8631559.793814434</v>
       </c>
-      <c r="F384" s="3" t="n">
-        <v>8890506.587628867</v>
+      <c r="F384" s="10" t="n">
+        <v>8631560</v>
       </c>
       <c r="G384" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H384" s="10" t="inlineStr">
+      <c r="H384" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I384" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J384" s="2" t="inlineStr"/>
+      <c r="I384" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J384" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="2" t="inlineStr">
@@ -17005,25 +17092,29 @@
       <c r="E385" s="3" t="n">
         <v>8631559.793814434</v>
       </c>
-      <c r="F385" s="3" t="n">
-        <v>8890506.587628867</v>
+      <c r="F385" s="10" t="n">
+        <v>8631560</v>
       </c>
       <c r="G385" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H385" s="10" t="inlineStr">
+      <c r="H385" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I385" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J385" s="2" t="inlineStr"/>
+      <c r="I385" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J385" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="2" t="inlineStr">
@@ -17045,25 +17136,29 @@
       <c r="E386" s="3" t="n">
         <v>10927019.58762887</v>
       </c>
-      <c r="F386" s="3" t="n">
-        <v>11254830.17525773</v>
+      <c r="F386" s="10" t="n">
+        <v>10927020</v>
       </c>
       <c r="G386" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H386" s="10" t="inlineStr">
+      <c r="H386" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I386" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J386" s="2" t="inlineStr"/>
+      <c r="I386" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J386" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="2" t="inlineStr">
@@ -17085,25 +17180,29 @@
       <c r="E387" s="3" t="n">
         <v>10927019.58762887</v>
       </c>
-      <c r="F387" s="3" t="n">
-        <v>11254830.17525773</v>
+      <c r="F387" s="10" t="n">
+        <v>10927020</v>
       </c>
       <c r="G387" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H387" s="10" t="inlineStr">
+      <c r="H387" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I387" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J387" s="2" t="inlineStr"/>
+      <c r="I387" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J387" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="2" t="inlineStr">
@@ -17125,25 +17224,29 @@
       <c r="E388" s="3" t="n">
         <v>14163129.89690722</v>
       </c>
-      <c r="F388" s="3" t="n">
-        <v>14588023.79381444</v>
+      <c r="F388" s="10" t="n">
+        <v>14163130</v>
       </c>
       <c r="G388" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H388" s="10" t="inlineStr">
+      <c r="H388" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I388" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J388" s="2" t="inlineStr"/>
+      <c r="I388" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J388" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="2" t="inlineStr">
@@ -17165,25 +17268,29 @@
       <c r="E389" s="3" t="n">
         <v>14163129.89690722</v>
       </c>
-      <c r="F389" s="3" t="n">
-        <v>14588023.79381444</v>
+      <c r="F389" s="10" t="n">
+        <v>14163130</v>
       </c>
       <c r="G389" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H389" s="10" t="inlineStr">
+      <c r="H389" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I389" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J389" s="2" t="inlineStr"/>
+      <c r="I389" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J389" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="2" t="inlineStr">
@@ -17202,28 +17309,28 @@
       <c r="D390" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E390" s="9" t="n">
+      <c r="E390" s="10" t="n">
         <v>3494770</v>
       </c>
       <c r="F390" s="3" t="n">
-        <v>3599613.1</v>
+        <v>3494770</v>
       </c>
       <c r="G390" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H390" s="10" t="inlineStr">
+      <c r="H390" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I390" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J390" s="7" t="inlineStr">
+      <c r="I390" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J390" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17246,28 +17353,28 @@
       <c r="D391" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E391" s="9" t="n">
+      <c r="E391" s="10" t="n">
         <v>3494770</v>
       </c>
       <c r="F391" s="3" t="n">
-        <v>3599613.1</v>
+        <v>3494770</v>
       </c>
       <c r="G391" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H391" s="10" t="inlineStr">
+      <c r="H391" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I391" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J391" s="7" t="inlineStr">
+      <c r="I391" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J391" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17293,25 +17400,29 @@
       <c r="E392" s="3" t="n">
         <v>4919189.69072165</v>
       </c>
-      <c r="F392" s="3" t="n">
-        <v>5066765.381443299</v>
+      <c r="F392" s="10" t="n">
+        <v>4919190</v>
       </c>
       <c r="G392" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H392" s="10" t="inlineStr">
+      <c r="H392" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I392" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J392" s="2" t="inlineStr"/>
+      <c r="I392" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J392" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="2" t="inlineStr">
@@ -17333,25 +17444,29 @@
       <c r="E393" s="3" t="n">
         <v>4919189.69072165</v>
       </c>
-      <c r="F393" s="3" t="n">
-        <v>5066765.381443299</v>
+      <c r="F393" s="10" t="n">
+        <v>4919190</v>
       </c>
       <c r="G393" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H393" s="10" t="inlineStr">
+      <c r="H393" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I393" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J393" s="2" t="inlineStr"/>
+      <c r="I393" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J393" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="2" t="inlineStr">
@@ -17370,28 +17485,28 @@
       <c r="D394" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E394" s="9" t="n">
+      <c r="E394" s="10" t="n">
         <v>6542350</v>
       </c>
       <c r="F394" s="3" t="n">
-        <v>6738620.5</v>
+        <v>6542350</v>
       </c>
       <c r="G394" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H394" s="10" t="inlineStr">
+      <c r="H394" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I394" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J394" s="7" t="inlineStr">
+      <c r="I394" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J394" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17414,28 +17529,28 @@
       <c r="D395" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E395" s="9" t="n">
+      <c r="E395" s="10" t="n">
         <v>6542350</v>
       </c>
       <c r="F395" s="3" t="n">
-        <v>6738620.5</v>
+        <v>6542350</v>
       </c>
       <c r="G395" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H395" s="10" t="inlineStr">
+      <c r="H395" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I395" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J395" s="7" t="inlineStr">
+      <c r="I395" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J395" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17469,12 +17584,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H396" s="10" t="inlineStr">
+      <c r="H396" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I396" s="7" t="inlineStr">
+      <c r="I396" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17509,12 +17624,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H397" s="10" t="inlineStr">
+      <c r="H397" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I397" s="7" t="inlineStr">
+      <c r="I397" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17549,12 +17664,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H398" s="10" t="inlineStr">
+      <c r="H398" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I398" s="7" t="inlineStr">
+      <c r="I398" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17578,28 +17693,28 @@
       <c r="D399" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E399" s="9" t="n">
+      <c r="E399" s="10" t="n">
         <v>728710</v>
       </c>
       <c r="F399" s="3" t="n">
-        <v>750571.3</v>
+        <v>728710</v>
       </c>
       <c r="G399" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H399" s="10" t="inlineStr">
+      <c r="H399" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I399" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J399" s="7" t="inlineStr">
+      <c r="I399" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J399" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17622,28 +17737,28 @@
       <c r="D400" s="6" t="n">
         <v>0.02</v>
       </c>
-      <c r="E400" s="9" t="n">
+      <c r="E400" s="10" t="n">
         <v>903010</v>
       </c>
       <c r="F400" s="3" t="n">
-        <v>930100.3</v>
+        <v>903010</v>
       </c>
       <c r="G400" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H400" s="10" t="inlineStr">
+      <c r="H400" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I400" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J400" s="7" t="inlineStr">
+      <c r="I400" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J400" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -17669,25 +17784,29 @@
       <c r="E401" s="3" t="n">
         <v>2143500</v>
       </c>
-      <c r="F401" s="3" t="n">
-        <v>2207805</v>
+      <c r="F401" s="10" t="n">
+        <v>2143500</v>
       </c>
       <c r="G401" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H401" s="10" t="inlineStr">
+      <c r="H401" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I401" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J401" s="2" t="inlineStr"/>
+      <c r="I401" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J401" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="2" t="inlineStr">
@@ -17709,25 +17828,29 @@
       <c r="E402" s="3" t="n">
         <v>3675100</v>
       </c>
-      <c r="F402" s="3" t="n">
-        <v>3785353</v>
+      <c r="F402" s="10" t="n">
+        <v>3675100</v>
       </c>
       <c r="G402" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H402" s="10" t="inlineStr">
+      <c r="H402" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I402" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J402" s="2" t="inlineStr"/>
+      <c r="I402" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J402" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="2" t="inlineStr">
@@ -17749,25 +17872,29 @@
       <c r="E403" s="3" t="n">
         <v>5447760</v>
       </c>
-      <c r="F403" s="3" t="n">
-        <v>5611192.8</v>
+      <c r="F403" s="10" t="n">
+        <v>5447760</v>
       </c>
       <c r="G403" s="2" t="inlineStr">
         <is>
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H403" s="10" t="inlineStr">
+      <c r="H403" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I403" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J403" s="2" t="inlineStr"/>
+      <c r="I403" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J403" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="2" t="inlineStr">
@@ -17797,12 +17924,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H404" s="10" t="inlineStr">
+      <c r="H404" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I404" s="7" t="inlineStr">
+      <c r="I404" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17837,12 +17964,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H405" s="10" t="inlineStr">
+      <c r="H405" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I405" s="7" t="inlineStr">
+      <c r="I405" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17877,12 +18004,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H406" s="10" t="inlineStr">
+      <c r="H406" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I406" s="7" t="inlineStr">
+      <c r="I406" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17917,12 +18044,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H407" s="10" t="inlineStr">
+      <c r="H407" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I407" s="7" t="inlineStr">
+      <c r="I407" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17957,12 +18084,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H408" s="10" t="inlineStr">
+      <c r="H408" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I408" s="7" t="inlineStr">
+      <c r="I408" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -17997,12 +18124,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H409" s="10" t="inlineStr">
+      <c r="H409" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I409" s="7" t="inlineStr">
+      <c r="I409" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18037,12 +18164,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H410" s="10" t="inlineStr">
+      <c r="H410" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I410" s="7" t="inlineStr">
+      <c r="I410" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18077,12 +18204,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H411" s="10" t="inlineStr">
+      <c r="H411" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I411" s="7" t="inlineStr">
+      <c r="I411" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18117,12 +18244,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H412" s="10" t="inlineStr">
+      <c r="H412" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I412" s="7" t="inlineStr">
+      <c r="I412" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18157,12 +18284,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H413" s="10" t="inlineStr">
+      <c r="H413" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I413" s="7" t="inlineStr">
+      <c r="I413" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18197,12 +18324,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H414" s="10" t="inlineStr">
+      <c r="H414" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I414" s="7" t="inlineStr">
+      <c r="I414" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18237,12 +18364,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H415" s="10" t="inlineStr">
+      <c r="H415" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I415" s="7" t="inlineStr">
+      <c r="I415" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18277,12 +18404,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H416" s="10" t="inlineStr">
+      <c r="H416" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I416" s="7" t="inlineStr">
+      <c r="I416" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18317,12 +18444,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H417" s="10" t="inlineStr">
+      <c r="H417" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I417" s="7" t="inlineStr">
+      <c r="I417" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18357,12 +18484,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H418" s="10" t="inlineStr">
+      <c r="H418" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I418" s="7" t="inlineStr">
+      <c r="I418" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18397,12 +18524,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H419" s="10" t="inlineStr">
+      <c r="H419" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I419" s="7" t="inlineStr">
+      <c r="I419" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18437,12 +18564,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H420" s="10" t="inlineStr">
+      <c r="H420" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I420" s="7" t="inlineStr">
+      <c r="I420" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18477,12 +18604,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H421" s="10" t="inlineStr">
+      <c r="H421" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I421" s="7" t="inlineStr">
+      <c r="I421" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18517,12 +18644,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H422" s="10" t="inlineStr">
+      <c r="H422" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I422" s="7" t="inlineStr">
+      <c r="I422" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18557,12 +18684,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H423" s="10" t="inlineStr">
+      <c r="H423" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I423" s="7" t="inlineStr">
+      <c r="I423" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18597,12 +18724,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H424" s="10" t="inlineStr">
+      <c r="H424" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I424" s="7" t="inlineStr">
+      <c r="I424" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18637,12 +18764,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H425" s="10" t="inlineStr">
+      <c r="H425" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I425" s="7" t="inlineStr">
+      <c r="I425" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18677,12 +18804,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H426" s="10" t="inlineStr">
+      <c r="H426" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I426" s="7" t="inlineStr">
+      <c r="I426" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18717,12 +18844,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H427" s="10" t="inlineStr">
+      <c r="H427" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I427" s="7" t="inlineStr">
+      <c r="I427" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18757,12 +18884,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H428" s="10" t="inlineStr">
+      <c r="H428" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I428" s="7" t="inlineStr">
+      <c r="I428" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18797,12 +18924,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H429" s="10" t="inlineStr">
+      <c r="H429" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I429" s="7" t="inlineStr">
+      <c r="I429" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18837,12 +18964,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H430" s="10" t="inlineStr">
+      <c r="H430" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I430" s="7" t="inlineStr">
+      <c r="I430" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18877,12 +19004,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H431" s="10" t="inlineStr">
+      <c r="H431" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I431" s="7" t="inlineStr">
+      <c r="I431" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18917,12 +19044,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H432" s="10" t="inlineStr">
+      <c r="H432" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I432" s="7" t="inlineStr">
+      <c r="I432" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18957,12 +19084,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H433" s="10" t="inlineStr">
+      <c r="H433" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I433" s="7" t="inlineStr">
+      <c r="I433" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -18997,12 +19124,12 @@
           <t>SFP/커넥터/서지(패턴)</t>
         </is>
       </c>
-      <c r="H434" s="10" t="inlineStr">
+      <c r="H434" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I434" s="7" t="inlineStr">
+      <c r="I434" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19037,12 +19164,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H435" s="10" t="inlineStr">
+      <c r="H435" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I435" s="7" t="inlineStr">
+      <c r="I435" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19077,12 +19204,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H436" s="10" t="inlineStr">
+      <c r="H436" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I436" s="7" t="inlineStr">
+      <c r="I436" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19117,12 +19244,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H437" s="10" t="inlineStr">
+      <c r="H437" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I437" s="7" t="inlineStr">
+      <c r="I437" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19157,12 +19284,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H438" s="10" t="inlineStr">
+      <c r="H438" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I438" s="7" t="inlineStr">
+      <c r="I438" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19197,12 +19324,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H439" s="10" t="inlineStr">
+      <c r="H439" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I439" s="7" t="inlineStr">
+      <c r="I439" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19237,12 +19364,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H440" s="10" t="inlineStr">
+      <c r="H440" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I440" s="7" t="inlineStr">
+      <c r="I440" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19277,12 +19404,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H441" s="10" t="inlineStr">
+      <c r="H441" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I441" s="7" t="inlineStr">
+      <c r="I441" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19317,12 +19444,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H442" s="10" t="inlineStr">
+      <c r="H442" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I442" s="7" t="inlineStr">
+      <c r="I442" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19357,12 +19484,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H443" s="10" t="inlineStr">
+      <c r="H443" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I443" s="7" t="inlineStr">
+      <c r="I443" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19397,12 +19524,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H444" s="10" t="inlineStr">
+      <c r="H444" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I444" s="7" t="inlineStr">
+      <c r="I444" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19437,12 +19564,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H445" s="10" t="inlineStr">
+      <c r="H445" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I445" s="7" t="inlineStr">
+      <c r="I445" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19477,12 +19604,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H446" s="10" t="inlineStr">
+      <c r="H446" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I446" s="7" t="inlineStr">
+      <c r="I446" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19517,12 +19644,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H447" s="10" t="inlineStr">
+      <c r="H447" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I447" s="7" t="inlineStr">
+      <c r="I447" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19557,12 +19684,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H448" s="10" t="inlineStr">
+      <c r="H448" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I448" s="7" t="inlineStr">
+      <c r="I448" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19597,12 +19724,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H449" s="10" t="inlineStr">
+      <c r="H449" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I449" s="7" t="inlineStr">
+      <c r="I449" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19637,12 +19764,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H450" s="10" t="inlineStr">
+      <c r="H450" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I450" s="7" t="inlineStr">
+      <c r="I450" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19677,12 +19804,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H451" s="10" t="inlineStr">
+      <c r="H451" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I451" s="7" t="inlineStr">
+      <c r="I451" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19717,12 +19844,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H452" s="10" t="inlineStr">
+      <c r="H452" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I452" s="7" t="inlineStr">
+      <c r="I452" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19757,12 +19884,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H453" s="10" t="inlineStr">
+      <c r="H453" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I453" s="7" t="inlineStr">
+      <c r="I453" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19797,12 +19924,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H454" s="10" t="inlineStr">
+      <c r="H454" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I454" s="7" t="inlineStr">
+      <c r="I454" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19837,12 +19964,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H455" s="10" t="inlineStr">
+      <c r="H455" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I455" s="7" t="inlineStr">
+      <c r="I455" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19877,12 +20004,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H456" s="10" t="inlineStr">
+      <c r="H456" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I456" s="7" t="inlineStr">
+      <c r="I456" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19917,12 +20044,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H457" s="10" t="inlineStr">
+      <c r="H457" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I457" s="7" t="inlineStr">
+      <c r="I457" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19957,12 +20084,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H458" s="10" t="inlineStr">
+      <c r="H458" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I458" s="7" t="inlineStr">
+      <c r="I458" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -19997,12 +20124,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H459" s="10" t="inlineStr">
+      <c r="H459" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I459" s="7" t="inlineStr">
+      <c r="I459" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20037,12 +20164,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H460" s="10" t="inlineStr">
+      <c r="H460" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I460" s="7" t="inlineStr">
+      <c r="I460" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20077,12 +20204,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H461" s="10" t="inlineStr">
+      <c r="H461" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I461" s="7" t="inlineStr">
+      <c r="I461" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20117,12 +20244,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H462" s="10" t="inlineStr">
+      <c r="H462" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I462" s="7" t="inlineStr">
+      <c r="I462" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20157,12 +20284,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H463" s="10" t="inlineStr">
+      <c r="H463" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I463" s="7" t="inlineStr">
+      <c r="I463" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20197,12 +20324,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H464" s="10" t="inlineStr">
+      <c r="H464" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I464" s="7" t="inlineStr">
+      <c r="I464" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20237,12 +20364,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H465" s="10" t="inlineStr">
+      <c r="H465" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I465" s="7" t="inlineStr">
+      <c r="I465" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20277,12 +20404,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H466" s="10" t="inlineStr">
+      <c r="H466" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I466" s="7" t="inlineStr">
+      <c r="I466" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20317,12 +20444,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H467" s="10" t="inlineStr">
+      <c r="H467" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I467" s="7" t="inlineStr">
+      <c r="I467" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20357,12 +20484,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H468" s="10" t="inlineStr">
+      <c r="H468" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I468" s="7" t="inlineStr">
+      <c r="I468" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20397,12 +20524,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H469" s="10" t="inlineStr">
+      <c r="H469" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I469" s="7" t="inlineStr">
+      <c r="I469" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20437,12 +20564,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H470" s="10" t="inlineStr">
+      <c r="H470" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I470" s="7" t="inlineStr">
+      <c r="I470" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20477,12 +20604,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H471" s="10" t="inlineStr">
+      <c r="H471" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I471" s="7" t="inlineStr">
+      <c r="I471" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20517,12 +20644,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H472" s="10" t="inlineStr">
+      <c r="H472" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I472" s="7" t="inlineStr">
+      <c r="I472" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20557,12 +20684,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H473" s="10" t="inlineStr">
+      <c r="H473" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I473" s="7" t="inlineStr">
+      <c r="I473" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20597,12 +20724,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H474" s="10" t="inlineStr">
+      <c r="H474" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I474" s="7" t="inlineStr">
+      <c r="I474" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20637,12 +20764,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H475" s="10" t="inlineStr">
+      <c r="H475" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I475" s="7" t="inlineStr">
+      <c r="I475" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20677,12 +20804,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H476" s="10" t="inlineStr">
+      <c r="H476" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I476" s="7" t="inlineStr">
+      <c r="I476" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20717,12 +20844,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H477" s="10" t="inlineStr">
+      <c r="H477" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I477" s="7" t="inlineStr">
+      <c r="I477" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20757,12 +20884,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H478" s="10" t="inlineStr">
+      <c r="H478" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I478" s="7" t="inlineStr">
+      <c r="I478" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20797,12 +20924,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H479" s="10" t="inlineStr">
+      <c r="H479" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I479" s="7" t="inlineStr">
+      <c r="I479" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20837,12 +20964,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H480" s="10" t="inlineStr">
+      <c r="H480" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I480" s="7" t="inlineStr">
+      <c r="I480" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20877,12 +21004,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H481" s="10" t="inlineStr">
+      <c r="H481" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I481" s="7" t="inlineStr">
+      <c r="I481" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20917,12 +21044,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H482" s="10" t="inlineStr">
+      <c r="H482" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I482" s="7" t="inlineStr">
+      <c r="I482" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20957,12 +21084,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H483" s="10" t="inlineStr">
+      <c r="H483" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I483" s="7" t="inlineStr">
+      <c r="I483" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -20997,12 +21124,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H484" s="10" t="inlineStr">
+      <c r="H484" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I484" s="7" t="inlineStr">
+      <c r="I484" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21037,12 +21164,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H485" s="10" t="inlineStr">
+      <c r="H485" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I485" s="7" t="inlineStr">
+      <c r="I485" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21077,12 +21204,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H486" s="10" t="inlineStr">
+      <c r="H486" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I486" s="7" t="inlineStr">
+      <c r="I486" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21117,12 +21244,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H487" s="10" t="inlineStr">
+      <c r="H487" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I487" s="7" t="inlineStr">
+      <c r="I487" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21146,28 +21273,28 @@
       <c r="D488" s="6" t="n">
         <v>0.03</v>
       </c>
-      <c r="E488" s="9" t="n">
+      <c r="E488" s="10" t="n">
         <v>3024380</v>
       </c>
       <c r="F488" s="3" t="n">
-        <v>3115111.4</v>
+        <v>3024380</v>
       </c>
       <c r="G488" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H488" s="10" t="inlineStr">
+      <c r="H488" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I488" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J488" s="7" t="inlineStr">
+      <c r="I488" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J488" s="8" t="inlineStr">
         <is>
           <t>정가상한 적용(대성 할인율&lt;마진율이라 정가로 상한)</t>
         </is>
@@ -21201,12 +21328,12 @@
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H489" s="10" t="inlineStr">
+      <c r="H489" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I489" s="7" t="inlineStr">
+      <c r="I489" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21233,25 +21360,29 @@
       <c r="E490" s="3" t="n">
         <v>5343189.69072165</v>
       </c>
-      <c r="F490" s="3" t="n">
-        <v>5503485.381443299</v>
+      <c r="F490" s="10" t="n">
+        <v>5343190</v>
       </c>
       <c r="G490" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H490" s="10" t="inlineStr">
+      <c r="H490" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I490" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J490" s="2" t="inlineStr"/>
+      <c r="I490" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J490" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
@@ -21273,25 +21404,29 @@
       <c r="E491" s="3" t="n">
         <v>5343189.69072165</v>
       </c>
-      <c r="F491" s="3" t="n">
-        <v>5503485.381443299</v>
+      <c r="F491" s="10" t="n">
+        <v>5343190</v>
       </c>
       <c r="G491" s="2" t="inlineStr">
         <is>
           <t>안테나/마운트/방수(패턴)</t>
         </is>
       </c>
-      <c r="H491" s="10" t="inlineStr">
+      <c r="H491" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I491" s="7" t="inlineStr">
-        <is>
-          <t>패턴 매칭 추정</t>
-        </is>
-      </c>
-      <c r="J491" s="2" t="inlineStr"/>
+      <c r="I491" s="8" t="inlineStr">
+        <is>
+          <t>패턴 매칭 추정</t>
+        </is>
+      </c>
+      <c r="J491" s="8" t="inlineStr">
+        <is>
+          <t>버퍼상한 적용(목표가+버퍼가 정가 초과해 정가로 재상한, 대성과 무관)</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
@@ -21321,12 +21456,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H492" s="10" t="inlineStr">
+      <c r="H492" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I492" s="7" t="inlineStr">
+      <c r="I492" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21361,12 +21496,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H493" s="10" t="inlineStr">
+      <c r="H493" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I493" s="7" t="inlineStr">
+      <c r="I493" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -21401,12 +21536,12 @@
           <t>핵심장비(패턴, 기본값)</t>
         </is>
       </c>
-      <c r="H494" s="10" t="inlineStr">
+      <c r="H494" s="11" t="inlineStr">
         <is>
           <t>타대역/구세대 추정(계약범위 확인 필요)</t>
         </is>
       </c>
-      <c r="I494" s="7" t="inlineStr">
+      <c r="I494" s="8" t="inlineStr">
         <is>
           <t>패턴 매칭 추정</t>
         </is>
@@ -22687,8 +22822,8 @@
       <c r="E12" s="3" t="n">
         <v>19852</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>408951.2</v>
+      <c r="F12" s="7" t="n">
+        <v>397040</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>718768</v>
@@ -22702,12 +22837,12 @@
       <c r="J12" s="3" t="n">
         <v>37829.89473684214</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>779295.8315789474</v>
+      <c r="K12" s="7" t="n">
+        <v>756600</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -22744,7 +22879,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -22760,7 +22895,7 @@
         <v>741169.4321822003</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>37423291.97352767</v>
+        <v>37411380.77352767</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>47680619.87800001</v>
@@ -22773,7 +22908,7 @@
         <v>999160.4878498167</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>50140173.77682532</v>
+        <v>50117477.94524637</v>
       </c>
     </row>
   </sheetData>
@@ -22969,7 +23104,7 @@
         <v>137679.3172244895</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>7090484.837061225</v>
+        <v>7090484.837061224</v>
       </c>
     </row>
     <row r="5">
@@ -23065,7 +23200,7 @@
         <v>148133.0757551026</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7628853.401387756</v>
+        <v>7628853.401387757</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10260287.378</v>
@@ -23249,8 +23384,8 @@
       <c r="E12" s="3" t="n">
         <v>29216</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>601849.6</v>
+      <c r="F12" s="7" t="n">
+        <v>584320</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1238264</v>
@@ -23264,12 +23399,12 @@
       <c r="J12" s="3" t="n">
         <v>65171.78947368427</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>1342538.863157895</v>
+      <c r="K12" s="7" t="n">
+        <v>1303440</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -23306,7 +23441,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -23322,7 +23457,7 @@
         <v>1157161.72372523</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58543406.77177699</v>
+        <v>58525877.17177699</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>65872577.23999999</v>
@@ -23335,7 +23470,7 @@
         <v>1387725.216652304</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>69278111.53035188</v>
+        <v>69239012.66719398</v>
       </c>
     </row>
   </sheetData>
@@ -23811,8 +23946,8 @@
       <c r="E12" s="3" t="n">
         <v>38580</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>794748</v>
+      <c r="F12" s="7" t="n">
+        <v>771600</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1757760</v>
@@ -23826,12 +23961,12 @@
       <c r="J12" s="3" t="n">
         <v>92513.68421052629</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>1905781.894736842</v>
+      <c r="K12" s="7" t="n">
+        <v>1850280</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -23868,7 +24003,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -23884,7 +24019,7 @@
         <v>1571149.963020414</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>79482217.90655102</v>
+        <v>79459069.90655102</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>83816970.92600001</v>
@@ -23897,7 +24032,7 @@
         <v>1772784.979859993</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>88157448.5830358</v>
+        <v>88101946.68829896</v>
       </c>
     </row>
   </sheetData>
@@ -24373,8 +24508,8 @@
       <c r="E12" s="3" t="n">
         <v>47944</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>987646.4</v>
+      <c r="F12" s="7" t="n">
+        <v>958880</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>2277256</v>
@@ -24388,12 +24523,12 @@
       <c r="J12" s="3" t="n">
         <v>119855.5789473685</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>2469024.92631579</v>
+      <c r="K12" s="7" t="n">
+        <v>2397120</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -24411,7 +24546,7 @@
         <v>14797.50321649492</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>508047.6104329898</v>
+        <v>508047.6104329897</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>584987.7320000001</v>
@@ -24426,11 +24561,11 @@
         <v>18092.4040824743</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>621172.5401649487</v>
+        <v>621172.5401649486</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -24446,7 +24581,7 @@
         <v>1901229.966849148</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>96177849.88751461</v>
+        <v>96149083.4875146</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>103814434.342</v>
@@ -24459,7 +24594,7 @@
         <v>2198196.770989016</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>109193010.0463787</v>
+        <v>109121105.1200629</v>
       </c>
     </row>
   </sheetData>
@@ -24927,8 +25062,8 @@
       <c r="E12" s="3" t="n">
         <v>19852</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>408951.2</v>
+      <c r="F12" s="7" t="n">
+        <v>397040</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>718768</v>
@@ -24942,12 +25077,12 @@
       <c r="J12" s="3" t="n">
         <v>37829.89473684214</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>779295.8315789474</v>
+      <c r="K12" s="7" t="n">
+        <v>756600</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -24984,7 +25119,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -25000,7 +25135,7 @@
         <v>741169.4321822003</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>37423291.97352767</v>
+        <v>37411380.77352767</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>47679525.642</v>
@@ -25013,7 +25148,7 @@
         <v>999138.1565028802</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>50139023.71245797</v>
+        <v>50116327.88087902</v>
       </c>
     </row>
   </sheetData>
@@ -25194,7 +25329,7 @@
         <v>132242.2463673474</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>6810475.687918368</v>
+        <v>6810475.687918367</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>6744098.072</v>
@@ -25305,7 +25440,7 @@
         <v>148133.0757551026</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>7628853.401387756</v>
+        <v>7628853.401387757</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>10260287.378</v>
@@ -25489,8 +25624,8 @@
       <c r="E12" s="3" t="n">
         <v>29216</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>601849.6</v>
+      <c r="F12" s="7" t="n">
+        <v>584320</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1238264</v>
@@ -25504,12 +25639,12 @@
       <c r="J12" s="3" t="n">
         <v>65171.78947368427</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>1342538.863157895</v>
+      <c r="K12" s="7" t="n">
+        <v>1303440</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -25546,7 +25681,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -25562,7 +25697,7 @@
         <v>1157117.061031349</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>58541106.6430423</v>
+        <v>58523577.04304229</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>65870388.76799999</v>
@@ -25575,7 +25710,7 @@
         <v>1387680.553958431</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>69275811.40161718</v>
+        <v>69236712.53845929</v>
       </c>
     </row>
   </sheetData>
@@ -25771,7 +25906,7 @@
         <v>206451.9817959182</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>10632277.06248979</v>
+        <v>10632277.0624898</v>
       </c>
     </row>
     <row r="5">
@@ -26051,8 +26186,8 @@
       <c r="E12" s="3" t="n">
         <v>38580</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>794748</v>
+      <c r="F12" s="7" t="n">
+        <v>771600</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>1757760</v>
@@ -26066,12 +26201,12 @@
       <c r="J12" s="3" t="n">
         <v>92513.68421052629</v>
       </c>
-      <c r="K12" s="3" t="n">
-        <v>1905781.894736842</v>
+      <c r="K12" s="7" t="n">
+        <v>1850280</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>⑫ 기타(케이블/커넥터/접지 등)</t>
         </is>
@@ -26108,7 +26243,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
@@ -26124,7 +26259,7 @@
         <v>1571082.968979582</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>79478767.71344897</v>
+        <v>79455619.71344897</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>83813688.21800001</v>
@@ -26137,7 +26272,7 @@
         <v>1772717.985819191</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>88153998.38993376</v>
+        <v>88098496.49519692</v>
       </c>
     </row>
   </sheetData>
